--- a/state_of_the_day.xlsx
+++ b/state_of_the_day.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Develop\StockTrading\AnalyzeFinData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C37252D-3883-4520-8359-83C24DA73088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16960648-7939-422B-B64E-9CE55C50607E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="2235" windowWidth="18945" windowHeight="18420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="450" yWindow="3000" windowWidth="18945" windowHeight="18420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Short_Long" sheetId="3" r:id="rId1"/>
@@ -2866,7 +2866,7 @@
         <v>606</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -2916,7 +2916,7 @@
         <v>561</v>
       </c>
       <c r="N4" s="34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -2965,9 +2965,8 @@
       <c r="M5" t="s">
         <v>606</v>
       </c>
-      <c r="N5"/>
-      <c r="O5">
-        <v>2</v>
+      <c r="N5">
+        <v>1</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -3016,8 +3015,7 @@
       <c r="M6" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="N6"/>
-      <c r="O6">
+      <c r="N6">
         <v>1</v>
       </c>
       <c r="P6">
@@ -3069,7 +3067,7 @@
       </c>
       <c r="N7"/>
       <c r="O7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -3118,8 +3116,8 @@
       <c r="M8" s="7" t="s">
         <v>543</v>
       </c>
-      <c r="N8">
-        <v>2</v>
+      <c r="N8" s="34">
+        <v>3</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -3168,9 +3166,8 @@
       <c r="M9" s="7" t="s">
         <v>567</v>
       </c>
-      <c r="N9"/>
-      <c r="O9">
-        <v>2</v>
+      <c r="N9">
+        <v>1</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -3219,8 +3216,7 @@
       <c r="M10" t="s">
         <v>606</v>
       </c>
-      <c r="N10"/>
-      <c r="O10">
+      <c r="N10">
         <v>1</v>
       </c>
       <c r="P10">
@@ -3268,7 +3264,7 @@
         <v>695</v>
       </c>
       <c r="N11" s="34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -3317,8 +3313,9 @@
       <c r="M12" t="s">
         <v>384</v>
       </c>
-      <c r="N12">
-        <v>2</v>
+      <c r="N12"/>
+      <c r="O12">
+        <v>1</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -3368,7 +3365,7 @@
         <v>698</v>
       </c>
       <c r="N13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -3418,7 +3415,7 @@
         <v>543</v>
       </c>
       <c r="N14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -3468,7 +3465,7 @@
         <v>561</v>
       </c>
       <c r="N15" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P15">
         <v>1</v>
@@ -3518,7 +3515,7 @@
         <v>606</v>
       </c>
       <c r="N16" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -3568,7 +3565,7 @@
         <v>561</v>
       </c>
       <c r="N17" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -3617,8 +3614,8 @@
       <c r="M18" t="s">
         <v>384</v>
       </c>
-      <c r="N18" s="8">
-        <v>2</v>
+      <c r="O18">
+        <v>1</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -3667,8 +3664,8 @@
       <c r="M19" t="s">
         <v>561</v>
       </c>
-      <c r="N19" s="8">
-        <v>2</v>
+      <c r="N19" s="34">
+        <v>3</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -3717,11 +3714,11 @@
       <c r="M20" s="7" t="s">
         <v>702</v>
       </c>
-      <c r="O20">
-        <v>2</v>
+      <c r="N20" s="8">
+        <v>1</v>
       </c>
       <c r="P20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:20">
@@ -3777,7 +3774,7 @@
         <v>598</v>
       </c>
       <c r="N27" s="34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -3826,8 +3823,8 @@
       <c r="M28" s="7" t="s">
         <v>598</v>
       </c>
-      <c r="N28">
-        <v>2</v>
+      <c r="N28" s="34">
+        <v>3</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -3882,8 +3879,7 @@
       <c r="M29" s="49" t="s">
         <v>614</v>
       </c>
-      <c r="N29"/>
-      <c r="O29">
+      <c r="N29">
         <v>1</v>
       </c>
       <c r="P29">
@@ -3931,7 +3927,7 @@
         <v>335</v>
       </c>
       <c r="N30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -3981,7 +3977,7 @@
         <v>543</v>
       </c>
       <c r="N31" s="34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -4030,9 +4026,8 @@
       <c r="M32" t="s">
         <v>561</v>
       </c>
-      <c r="N32"/>
-      <c r="O32">
-        <v>2</v>
+      <c r="N32">
+        <v>1</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -4081,9 +4076,8 @@
       <c r="M33" t="s">
         <v>614</v>
       </c>
-      <c r="N33"/>
-      <c r="O33">
-        <v>2</v>
+      <c r="N33">
+        <v>1</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -4132,9 +4126,8 @@
       <c r="M34" s="7" t="s">
         <v>598</v>
       </c>
-      <c r="N34"/>
-      <c r="O34">
-        <v>4</v>
+      <c r="N34">
+        <v>1</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -4183,8 +4176,8 @@
       <c r="M35" t="s">
         <v>561</v>
       </c>
-      <c r="N35">
-        <v>2</v>
+      <c r="N35" s="34">
+        <v>3</v>
       </c>
       <c r="P35">
         <v>0</v>
@@ -4234,7 +4227,7 @@
         <v>561</v>
       </c>
       <c r="N36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P36">
         <v>0</v>
@@ -4284,7 +4277,7 @@
         <v>561</v>
       </c>
       <c r="N37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P37">
         <v>0</v>
@@ -4333,8 +4326,9 @@
       <c r="M38" t="s">
         <v>200</v>
       </c>
-      <c r="N38">
-        <v>2</v>
+      <c r="N38"/>
+      <c r="O38">
+        <v>1</v>
       </c>
       <c r="P38">
         <v>0</v>
@@ -4384,8 +4378,8 @@
       <c r="M39" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="N39">
-        <v>2</v>
+      <c r="N39" s="34">
+        <v>3</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -4434,9 +4428,8 @@
       <c r="M40" t="s">
         <v>614</v>
       </c>
-      <c r="N40"/>
-      <c r="O40">
-        <v>2</v>
+      <c r="N40">
+        <v>1</v>
       </c>
       <c r="P40">
         <v>0</v>
@@ -4485,9 +4478,8 @@
       <c r="M41" t="s">
         <v>200</v>
       </c>
-      <c r="N41"/>
-      <c r="O41">
-        <v>2</v>
+      <c r="N41">
+        <v>1</v>
       </c>
       <c r="P41">
         <v>0</v>
@@ -4536,9 +4528,8 @@
       <c r="M42" s="7" t="s">
         <v>543</v>
       </c>
-      <c r="N42"/>
-      <c r="O42">
-        <v>2</v>
+      <c r="N42">
+        <v>1</v>
       </c>
       <c r="P42">
         <v>0</v>
@@ -4587,8 +4578,8 @@
       <c r="M43" t="s">
         <v>384</v>
       </c>
-      <c r="N43">
-        <v>2</v>
+      <c r="N43" s="34">
+        <v>3</v>
       </c>
       <c r="P43">
         <v>0</v>
@@ -4608,7 +4599,7 @@
         <v>92.51</v>
       </c>
       <c r="E44">
-        <v>98.12</v>
+        <v>105.2</v>
       </c>
       <c r="F44" s="12">
         <v>125</v>
@@ -4618,11 +4609,11 @@
       </c>
       <c r="H44" s="22">
         <f t="shared" ref="H44:H45" si="30">E44*0.92</f>
-        <v>90.270400000000009</v>
+        <v>96.784000000000006</v>
       </c>
       <c r="I44" s="9">
         <f t="shared" ref="I44:I45" si="31">F44/E44 -1</f>
-        <v>0.27395026498165498</v>
+        <v>0.18821292775665399</v>
       </c>
       <c r="J44" s="26">
         <f t="shared" ref="J44:J45" si="32">C44*D44</f>
@@ -4637,7 +4628,8 @@
       <c r="M44" s="7" t="s">
         <v>543</v>
       </c>
-      <c r="N44">
+      <c r="N44"/>
+      <c r="O44">
         <v>1</v>
       </c>
       <c r="P44">
@@ -4688,7 +4680,7 @@
         <v>561</v>
       </c>
       <c r="N45" s="34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P45">
         <v>0</v>
@@ -4737,8 +4729,8 @@
       <c r="M46" s="7" t="s">
         <v>543</v>
       </c>
-      <c r="N46">
-        <v>2</v>
+      <c r="N46" s="34">
+        <v>3</v>
       </c>
       <c r="P46">
         <v>0</v>
@@ -4837,8 +4829,8 @@
       <c r="M48" t="s">
         <v>614</v>
       </c>
-      <c r="N48">
-        <v>2</v>
+      <c r="N48" s="34">
+        <v>3</v>
       </c>
       <c r="P48">
         <v>0</v>
@@ -4888,7 +4880,7 @@
         <v>598</v>
       </c>
       <c r="N49" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P49">
         <v>1</v>
@@ -4937,7 +4929,7 @@
       <c r="M50" t="s">
         <v>384</v>
       </c>
-      <c r="N50" s="8">
+      <c r="O50">
         <v>1</v>
       </c>
       <c r="P50">
@@ -4988,7 +4980,7 @@
         <v>543</v>
       </c>
       <c r="N51" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P51">
         <v>0</v>

--- a/state_of_the_day.xlsx
+++ b/state_of_the_day.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Develop\StockTrading\AnalyzeFinData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8085171E-1F61-4790-8380-2C13092AAB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2BBF47-1491-4C8A-8567-74CBF6AA4163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="660" yWindow="1605" windowWidth="18825" windowHeight="18420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4111" uniqueCount="720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4114" uniqueCount="720">
   <si>
     <t>Symb</t>
   </si>
@@ -2894,7 +2894,8 @@
       <c r="M3" s="49" t="s">
         <v>606</v>
       </c>
-      <c r="N3">
+      <c r="N3"/>
+      <c r="O3">
         <v>1</v>
       </c>
       <c r="P3">
@@ -2945,7 +2946,7 @@
         <v>561</v>
       </c>
       <c r="N4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -2994,8 +2995,7 @@
       <c r="M5" t="s">
         <v>606</v>
       </c>
-      <c r="N5"/>
-      <c r="O5">
+      <c r="N5">
         <v>1</v>
       </c>
       <c r="P5">
@@ -3046,7 +3046,7 @@
         <v>672</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -3095,8 +3095,8 @@
       <c r="M7" t="s">
         <v>384</v>
       </c>
-      <c r="N7">
-        <v>2</v>
+      <c r="N7" s="34">
+        <v>3</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="N9"/>
       <c r="O9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -3246,9 +3246,8 @@
       <c r="M10" t="s">
         <v>606</v>
       </c>
-      <c r="N10"/>
-      <c r="O10">
-        <v>2</v>
+      <c r="N10">
+        <v>1</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -3295,7 +3294,7 @@
         <v>695</v>
       </c>
       <c r="N11" s="34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -3346,7 +3345,7 @@
       </c>
       <c r="N12"/>
       <c r="O12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -3397,7 +3396,7 @@
       </c>
       <c r="N13"/>
       <c r="O13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -3448,10 +3447,10 @@
       </c>
       <c r="N14"/>
       <c r="O14">
+        <v>2</v>
+      </c>
+      <c r="P14">
         <v>1</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -3498,7 +3497,7 @@
         <v>561</v>
       </c>
       <c r="N15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -3547,7 +3546,7 @@
       <c r="M16" t="s">
         <v>384</v>
       </c>
-      <c r="N16" s="8">
+      <c r="O16">
         <v>1</v>
       </c>
       <c r="P16">
@@ -3568,7 +3567,7 @@
         <v>14.18</v>
       </c>
       <c r="E17">
-        <v>14.23</v>
+        <v>14.63</v>
       </c>
       <c r="F17" s="12">
         <v>17.5</v>
@@ -3577,15 +3576,15 @@
         <v>13</v>
       </c>
       <c r="H17" s="22">
-        <f t="shared" ref="H17:H19" si="12">E17*0.92</f>
-        <v>13.091600000000001</v>
+        <f t="shared" ref="H17:H20" si="12">E17*0.92</f>
+        <v>13.459600000000002</v>
       </c>
       <c r="I17" s="9">
-        <f t="shared" ref="I17:I19" si="13">F17/E17 -1</f>
-        <v>0.2297962052002811</v>
+        <f t="shared" ref="I17:I20" si="13">F17/E17 -1</f>
+        <v>0.19617224880382778</v>
       </c>
       <c r="J17" s="26">
-        <f t="shared" ref="J17:J19" si="14">C17*D17</f>
+        <f t="shared" ref="J17:J20" si="14">C17*D17</f>
         <v>1843.3999999999999</v>
       </c>
       <c r="K17" s="18">
@@ -3599,7 +3598,7 @@
       </c>
       <c r="N17"/>
       <c r="O17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P17">
         <v>1</v>
@@ -3648,12 +3647,11 @@
       <c r="M18" s="7" t="s">
         <v>702</v>
       </c>
-      <c r="N18"/>
-      <c r="O18">
+      <c r="N18">
         <v>1</v>
       </c>
       <c r="P18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -3699,7 +3697,7 @@
       <c r="M19" s="7" t="s">
         <v>567</v>
       </c>
-      <c r="O19">
+      <c r="N19" s="8">
         <v>1</v>
       </c>
       <c r="P19">
@@ -3710,6 +3708,51 @@
       <c r="A20">
         <v>18</v>
       </c>
+      <c r="B20" t="s">
+        <v>705</v>
+      </c>
+      <c r="C20" s="5">
+        <v>95</v>
+      </c>
+      <c r="D20">
+        <v>11.55</v>
+      </c>
+      <c r="E20">
+        <v>11.55</v>
+      </c>
+      <c r="F20" s="12">
+        <v>25</v>
+      </c>
+      <c r="G20" s="26">
+        <v>10</v>
+      </c>
+      <c r="H20" s="22">
+        <f t="shared" si="12"/>
+        <v>10.626000000000001</v>
+      </c>
+      <c r="I20" s="9">
+        <f t="shared" si="13"/>
+        <v>1.1645021645021645</v>
+      </c>
+      <c r="J20" s="26">
+        <f t="shared" si="14"/>
+        <v>1097.25</v>
+      </c>
+      <c r="K20" s="18">
+        <v>46197</v>
+      </c>
+      <c r="L20" t="s">
+        <v>276</v>
+      </c>
+      <c r="M20" t="s">
+        <v>200</v>
+      </c>
+      <c r="N20" s="8">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:20">
       <c r="T24" s="7"/>
@@ -3763,7 +3806,8 @@
       <c r="M27" s="7" t="s">
         <v>598</v>
       </c>
-      <c r="N27">
+      <c r="N27"/>
+      <c r="O27">
         <v>1</v>
       </c>
       <c r="P27">
@@ -3814,7 +3858,7 @@
         <v>598</v>
       </c>
       <c r="N28" s="34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -3870,7 +3914,7 @@
         <v>614</v>
       </c>
       <c r="N29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -3917,7 +3961,7 @@
         <v>335</v>
       </c>
       <c r="N30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -3968,7 +4012,7 @@
       </c>
       <c r="N31"/>
       <c r="O31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -4017,8 +4061,9 @@
       <c r="M32" t="s">
         <v>561</v>
       </c>
-      <c r="N32" s="34">
-        <v>3</v>
+      <c r="N32"/>
+      <c r="O32">
+        <v>1</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -4067,8 +4112,7 @@
       <c r="M33" t="s">
         <v>614</v>
       </c>
-      <c r="N33"/>
-      <c r="O33">
+      <c r="N33">
         <v>1</v>
       </c>
       <c r="P33">
@@ -4118,8 +4162,9 @@
       <c r="M34" s="7" t="s">
         <v>598</v>
       </c>
-      <c r="N34" s="34">
-        <v>3</v>
+      <c r="N34"/>
+      <c r="O34">
+        <v>1</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -4170,7 +4215,7 @@
       </c>
       <c r="N35"/>
       <c r="O35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P35">
         <v>0</v>
@@ -4220,7 +4265,7 @@
         <v>561</v>
       </c>
       <c r="N36" s="34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P36">
         <v>0</v>
@@ -4269,8 +4314,7 @@
       <c r="M37" t="s">
         <v>561</v>
       </c>
-      <c r="N37"/>
-      <c r="O37">
+      <c r="N37">
         <v>1</v>
       </c>
       <c r="P37">
@@ -4320,8 +4364,8 @@
       <c r="M38" t="s">
         <v>200</v>
       </c>
-      <c r="N38">
-        <v>2</v>
+      <c r="N38" s="34">
+        <v>3</v>
       </c>
       <c r="P38">
         <v>0</v>
@@ -4371,9 +4415,8 @@
       <c r="M39" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="N39"/>
-      <c r="O39">
-        <v>2</v>
+      <c r="N39">
+        <v>1</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -4423,7 +4466,7 @@
         <v>614</v>
       </c>
       <c r="N40" s="34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P40">
         <v>0</v>
@@ -4473,7 +4516,7 @@
         <v>200</v>
       </c>
       <c r="N41" s="34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P41">
         <v>0</v>
@@ -4524,7 +4567,7 @@
       </c>
       <c r="N42"/>
       <c r="O42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P42">
         <v>0</v>
@@ -4573,9 +4616,8 @@
       <c r="M43" t="s">
         <v>384</v>
       </c>
-      <c r="N43"/>
-      <c r="O43">
-        <v>2</v>
+      <c r="N43">
+        <v>1</v>
       </c>
       <c r="P43">
         <v>0</v>
@@ -4624,8 +4666,8 @@
       <c r="M44" s="7" t="s">
         <v>543</v>
       </c>
-      <c r="N44">
-        <v>2</v>
+      <c r="N44" s="34">
+        <v>3</v>
       </c>
       <c r="P44">
         <v>1</v>
@@ -4674,8 +4716,7 @@
       <c r="M45" t="s">
         <v>561</v>
       </c>
-      <c r="N45"/>
-      <c r="O45">
+      <c r="N45">
         <v>1</v>
       </c>
       <c r="P45">
@@ -4727,7 +4768,7 @@
       </c>
       <c r="N46"/>
       <c r="O46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P46">
         <v>0</v>
@@ -4777,7 +4818,7 @@
         <v>543</v>
       </c>
       <c r="O47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P47">
         <v>0</v>
@@ -4797,7 +4838,7 @@
         <v>57.3</v>
       </c>
       <c r="E48">
-        <v>57.43</v>
+        <v>57.81</v>
       </c>
       <c r="F48" s="12">
         <v>62</v>
@@ -4807,11 +4848,11 @@
       </c>
       <c r="H48" s="22">
         <f t="shared" si="36"/>
-        <v>52.835599999999999</v>
+        <v>53.185200000000002</v>
       </c>
       <c r="I48" s="9">
         <f t="shared" si="37"/>
-        <v>7.9575134946891835E-2</v>
+        <v>7.2478809894481966E-2</v>
       </c>
       <c r="J48" s="26">
         <f t="shared" si="38"/>
@@ -4828,7 +4869,7 @@
       </c>
       <c r="N48"/>
       <c r="O48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P48">
         <v>1</v>
@@ -4878,7 +4919,7 @@
         <v>598</v>
       </c>
       <c r="N49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P49">
         <v>0</v>
@@ -4928,7 +4969,7 @@
         <v>543</v>
       </c>
       <c r="N50" s="34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P50">
         <v>0</v>
@@ -14003,7 +14044,7 @@
     </row>
     <row r="179" spans="2:20">
       <c r="B179" s="14">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="C179" s="14"/>
       <c r="D179" t="s">

--- a/state_of_the_day.xlsx
+++ b/state_of_the_day.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Develop\StockTrading\AnalyzeFinData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFEB41B0-215A-43FC-B1BF-3455C626BDEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FAB885-1072-4869-9A38-6FA729B5A9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="465" yWindow="2865" windowWidth="18945" windowHeight="18420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15" yWindow="1425" windowWidth="18945" windowHeight="18420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Short_Long" sheetId="3" r:id="rId1"/>
@@ -2485,7 +2485,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2543,7 +2543,6 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2933,7 +2932,7 @@
         <v>559</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -2982,8 +2981,8 @@
       <c r="M4" t="s">
         <v>604</v>
       </c>
-      <c r="N4">
-        <v>2</v>
+      <c r="N4" s="34">
+        <v>3</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -3032,11 +3031,15 @@
       <c r="M5" s="7" t="s">
         <v>670</v>
       </c>
-      <c r="N5">
+      <c r="N5"/>
+      <c r="O5">
         <v>1</v>
       </c>
       <c r="P5">
         <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -3082,8 +3085,8 @@
       <c r="M6" t="s">
         <v>382</v>
       </c>
-      <c r="N6">
-        <v>2</v>
+      <c r="N6" s="34">
+        <v>3</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -3132,9 +3135,8 @@
       <c r="M7" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="N7"/>
-      <c r="O7">
-        <v>2</v>
+      <c r="N7">
+        <v>1</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -3183,9 +3185,8 @@
       <c r="M8" t="s">
         <v>604</v>
       </c>
-      <c r="N8"/>
-      <c r="O8">
-        <v>2</v>
+      <c r="N8">
+        <v>1</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -3231,8 +3232,8 @@
       <c r="L9" t="s">
         <v>693</v>
       </c>
-      <c r="N9">
-        <v>2</v>
+      <c r="N9" s="34">
+        <v>3</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -3281,9 +3282,8 @@
       <c r="M10" t="s">
         <v>382</v>
       </c>
-      <c r="N10"/>
-      <c r="O10">
-        <v>2</v>
+      <c r="N10">
+        <v>1</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -3312,15 +3312,15 @@
         <v>19</v>
       </c>
       <c r="H11" s="22">
-        <f t="shared" ref="H11:H20" si="9">E11*0.92</f>
+        <f t="shared" ref="H11:H12" si="9">E11*0.92</f>
         <v>46.156400000000005</v>
       </c>
       <c r="I11" s="36">
-        <f t="shared" ref="I11:I20" si="10">F11/E11 -1</f>
+        <f t="shared" ref="I11:I12" si="10">F11/E11 -1</f>
         <v>-3.3884791708193029E-3</v>
       </c>
       <c r="J11" s="26">
-        <f t="shared" ref="J11:J20" si="11">C11*D11</f>
+        <f t="shared" ref="J11:J12" si="11">C11*D11</f>
         <v>3046.4</v>
       </c>
       <c r="K11" s="18">
@@ -3333,7 +3333,7 @@
         <v>559</v>
       </c>
       <c r="N11" s="34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -3382,9 +3382,8 @@
       <c r="M12" s="7" t="s">
         <v>699</v>
       </c>
-      <c r="N12"/>
-      <c r="O12">
-        <v>2</v>
+      <c r="N12">
+        <v>1</v>
       </c>
       <c r="P12">
         <v>1</v>
@@ -3413,15 +3412,15 @@
         <v>10</v>
       </c>
       <c r="H13" s="22">
-        <f>E13*0.92</f>
+        <f t="shared" ref="H13:H19" si="12">E13*0.92</f>
         <v>11.251600000000002</v>
       </c>
       <c r="I13" s="9">
-        <f>F13/E13 -1</f>
+        <f t="shared" ref="I13:I19" si="13">F13/E13 -1</f>
         <v>1.0441537203597711</v>
       </c>
       <c r="J13" s="26">
-        <f>C13*D13</f>
+        <f t="shared" ref="J13:J19" si="14">C13*D13</f>
         <v>1097.25</v>
       </c>
       <c r="K13" s="18">
@@ -3433,8 +3432,8 @@
       <c r="M13" t="s">
         <v>199</v>
       </c>
-      <c r="N13">
-        <v>2</v>
+      <c r="N13" s="34">
+        <v>3</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -3463,15 +3462,15 @@
         <v>145</v>
       </c>
       <c r="H14" s="22">
-        <f>E14*0.92</f>
+        <f t="shared" si="12"/>
         <v>138</v>
       </c>
       <c r="I14" s="9">
-        <f>F14/E14 -1</f>
+        <f t="shared" si="13"/>
         <v>0.66666666666666674</v>
       </c>
       <c r="J14" s="26">
-        <f>C14*D14</f>
+        <f t="shared" si="14"/>
         <v>2076.06</v>
       </c>
       <c r="K14" s="18">
@@ -3483,11 +3482,15 @@
       <c r="M14" s="7" t="s">
         <v>565</v>
       </c>
-      <c r="N14">
+      <c r="N14"/>
+      <c r="O14">
         <v>1</v>
       </c>
       <c r="P14">
         <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -3513,15 +3516,15 @@
         <v>73</v>
       </c>
       <c r="H15" s="22">
-        <f>E15*0.92</f>
+        <f t="shared" si="12"/>
         <v>71.805999999999997</v>
       </c>
       <c r="I15" s="9">
-        <f>F15/E15 -1</f>
+        <f t="shared" si="13"/>
         <v>8.9045483664317748E-2</v>
       </c>
       <c r="J15" s="26">
-        <f>C15*D15</f>
+        <f t="shared" si="14"/>
         <v>3446.55</v>
       </c>
       <c r="K15" s="18">
@@ -3533,8 +3536,8 @@
       <c r="M15" s="7" t="s">
         <v>720</v>
       </c>
-      <c r="O15">
-        <v>5</v>
+      <c r="N15" s="8">
+        <v>1</v>
       </c>
       <c r="P15">
         <v>1</v>
@@ -3563,15 +3566,15 @@
         <v>22</v>
       </c>
       <c r="H16" s="22">
-        <f>E16*0.92</f>
+        <f t="shared" si="12"/>
         <v>22.172000000000001</v>
       </c>
       <c r="I16" s="9">
-        <f>F16/E16 -1</f>
+        <f t="shared" si="13"/>
         <v>0.36929460580912865</v>
       </c>
       <c r="J16" s="26">
-        <f>C16*D16</f>
+        <f t="shared" si="14"/>
         <v>637.20000000000005</v>
       </c>
       <c r="K16" s="18">
@@ -3583,8 +3586,8 @@
       <c r="M16" t="s">
         <v>604</v>
       </c>
-      <c r="O16">
-        <v>2</v>
+      <c r="N16" s="8">
+        <v>1</v>
       </c>
       <c r="P16">
         <v>1</v>
@@ -3613,15 +3616,15 @@
         <v>74</v>
       </c>
       <c r="H17" s="22">
-        <f>E17*0.92</f>
+        <f t="shared" si="12"/>
         <v>71.622</v>
       </c>
       <c r="I17" s="9">
-        <f>F17/E17 -1</f>
+        <f t="shared" si="13"/>
         <v>0.1560693641618498</v>
       </c>
       <c r="J17" s="26">
-        <f>C17*D17</f>
+        <f t="shared" si="14"/>
         <v>1217.1199999999999</v>
       </c>
       <c r="K17" s="18">
@@ -3633,8 +3636,8 @@
       <c r="M17" s="7" t="s">
         <v>724</v>
       </c>
-      <c r="O17">
-        <v>3</v>
+      <c r="N17" s="8">
+        <v>1</v>
       </c>
       <c r="P17">
         <v>1</v>
@@ -3663,15 +3666,15 @@
         <v>28</v>
       </c>
       <c r="H18" s="22">
-        <f>E18*0.92</f>
+        <f t="shared" si="12"/>
         <v>30.461200000000002</v>
       </c>
       <c r="I18" s="9">
-        <f>F18/E18 -1</f>
+        <f t="shared" si="13"/>
         <v>0.20809423135004534</v>
       </c>
       <c r="J18" s="26">
-        <f>C18*D18</f>
+        <f t="shared" si="14"/>
         <v>1390.4</v>
       </c>
       <c r="K18" s="18">
@@ -3683,8 +3686,8 @@
       <c r="M18" s="7" t="s">
         <v>699</v>
       </c>
-      <c r="O18">
-        <v>2</v>
+      <c r="N18" s="8">
+        <v>1</v>
       </c>
       <c r="P18">
         <v>1</v>
@@ -3713,15 +3716,15 @@
         <v>190</v>
       </c>
       <c r="H19" s="22">
-        <f>E19*0.92</f>
+        <f t="shared" si="12"/>
         <v>178.81120000000001</v>
       </c>
       <c r="I19" s="9">
-        <f>F19/E19 -1</f>
+        <f t="shared" si="13"/>
         <v>8.0469232352335718E-2</v>
       </c>
       <c r="J19" s="26">
-        <f>C19*D19</f>
+        <f t="shared" si="14"/>
         <v>1930.6999999999998</v>
       </c>
       <c r="K19" s="18">
@@ -3734,7 +3737,7 @@
         <v>559</v>
       </c>
       <c r="N19" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P19">
         <v>1</v>
@@ -3772,15 +3775,15 @@
         <v>200</v>
       </c>
       <c r="H27" s="22">
-        <f t="shared" ref="H27:H29" si="12">E27*0.92</f>
+        <f t="shared" ref="H27:H29" si="15">E27*0.92</f>
         <v>124.61399999999999</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" ref="I27:I29" si="13">F27/E27 -1</f>
+        <f t="shared" ref="I27:I29" si="16">F27/E27 -1</f>
         <v>0.84569952011812499</v>
       </c>
       <c r="J27" s="26">
-        <f t="shared" ref="J27:J29" si="14">C27*D27</f>
+        <f t="shared" ref="J27:J29" si="17">C27*D27</f>
         <v>15995.699999999999</v>
       </c>
       <c r="K27" s="18">
@@ -3792,8 +3795,9 @@
       <c r="M27" s="7" t="s">
         <v>596</v>
       </c>
-      <c r="N27">
-        <v>2</v>
+      <c r="N27"/>
+      <c r="O27">
+        <v>1</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -3822,15 +3826,15 @@
         <v>85</v>
       </c>
       <c r="H28" s="22">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>78.255200000000002</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.17564072419468602</v>
       </c>
       <c r="J28" s="26">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>7392.03</v>
       </c>
       <c r="K28" s="18">
@@ -3842,8 +3846,9 @@
       <c r="M28" s="7" t="s">
         <v>596</v>
       </c>
-      <c r="N28">
-        <v>2</v>
+      <c r="N28"/>
+      <c r="O28">
+        <v>1</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -3878,15 +3883,15 @@
         <v>3.8</v>
       </c>
       <c r="H29" s="22">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>3.6156000000000001</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.27226463104325704</v>
       </c>
       <c r="J29" s="26">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>5192.3</v>
       </c>
       <c r="K29" s="18">
@@ -3898,8 +3903,8 @@
       <c r="M29" s="49" t="s">
         <v>612</v>
       </c>
-      <c r="N29">
-        <v>2</v>
+      <c r="N29" s="34">
+        <v>3</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -3928,15 +3933,15 @@
         <v>19</v>
       </c>
       <c r="H30" s="22">
-        <f t="shared" ref="H30" si="15">E30*0.92</f>
+        <f t="shared" ref="H30" si="18">E30*0.92</f>
         <v>29.881599999999999</v>
       </c>
       <c r="I30" s="9">
-        <f t="shared" ref="I30" si="16">F30/E30 -1</f>
+        <f t="shared" ref="I30" si="19">F30/E30 -1</f>
         <v>7.7586206896551824E-2</v>
       </c>
       <c r="J30" s="26">
-        <f t="shared" ref="J30" si="17">C30*D30</f>
+        <f t="shared" ref="J30" si="20">C30*D30</f>
         <v>4151.04</v>
       </c>
       <c r="K30" s="18">
@@ -3946,7 +3951,7 @@
         <v>334</v>
       </c>
       <c r="N30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -3975,15 +3980,15 @@
         <v>400</v>
       </c>
       <c r="H31" s="22">
-        <f t="shared" ref="H31:H34" si="18">E31*0.92</f>
+        <f t="shared" ref="H31:H34" si="21">E31*0.92</f>
         <v>387.46720000000005</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" ref="I31:I34" si="19">F31/E31 -1</f>
+        <f t="shared" ref="I31:I34" si="22">F31/E31 -1</f>
         <v>6.8477538227751822E-2</v>
       </c>
       <c r="J31" s="26">
-        <f t="shared" ref="J31:J34" si="20">C31*D31</f>
+        <f t="shared" ref="J31:J34" si="23">C31*D31</f>
         <v>7226.7999999999993</v>
       </c>
       <c r="K31" s="18">
@@ -3995,9 +4000,8 @@
       <c r="M31" s="50" t="s">
         <v>541</v>
       </c>
-      <c r="N31"/>
-      <c r="O31">
-        <v>2</v>
+      <c r="N31">
+        <v>1</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -4026,15 +4030,15 @@
         <v>174</v>
       </c>
       <c r="H32" s="22">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>163.024</v>
       </c>
       <c r="I32" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0.12866817155756216</v>
       </c>
       <c r="J32" s="26">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>5866.3</v>
       </c>
       <c r="K32" s="18">
@@ -4046,9 +4050,8 @@
       <c r="M32" t="s">
         <v>559</v>
       </c>
-      <c r="N32"/>
-      <c r="O32">
-        <v>3</v>
+      <c r="N32">
+        <v>1</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -4077,15 +4080,15 @@
         <v>450</v>
       </c>
       <c r="H33" s="22">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>428.72</v>
       </c>
       <c r="I33" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0.18025751072961382</v>
       </c>
       <c r="J33" s="26">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>8205.5600000000013</v>
       </c>
       <c r="K33" s="18">
@@ -4099,7 +4102,7 @@
       </c>
       <c r="N33"/>
       <c r="O33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -4128,15 +4131,15 @@
         <v>75</v>
       </c>
       <c r="H34" s="22">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>72.22</v>
       </c>
       <c r="I34" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0.14649681528662417</v>
       </c>
       <c r="J34" s="26">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>5405.23</v>
       </c>
       <c r="K34" s="18">
@@ -4148,9 +4151,8 @@
       <c r="M34" s="7" t="s">
         <v>596</v>
       </c>
-      <c r="N34"/>
-      <c r="O34">
-        <v>2</v>
+      <c r="N34">
+        <v>1</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -4179,15 +4181,15 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="H35" s="22">
-        <f t="shared" ref="H35:H36" si="21">E35*0.92</f>
+        <f t="shared" ref="H35:H36" si="24">E35*0.92</f>
         <v>5.1980000000000004</v>
       </c>
       <c r="I35" s="9">
-        <f t="shared" ref="I35:I36" si="22">F35/E35 -1</f>
+        <f t="shared" ref="I35:I36" si="25">F35/E35 -1</f>
         <v>0.32743362831858391</v>
       </c>
       <c r="J35" s="26">
-        <f t="shared" ref="J35:J36" si="23">C35*D35</f>
+        <f t="shared" ref="J35:J36" si="26">C35*D35</f>
         <v>2235.8999999999996</v>
       </c>
       <c r="K35" s="18">
@@ -4229,15 +4231,15 @@
         <v>100</v>
       </c>
       <c r="H36" s="22">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>100.602</v>
       </c>
       <c r="I36" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.18884316415180624</v>
       </c>
       <c r="J36" s="26">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>7415.24</v>
       </c>
       <c r="K36" s="18">
@@ -4249,9 +4251,8 @@
       <c r="M36" t="s">
         <v>559</v>
       </c>
-      <c r="N36"/>
-      <c r="O36">
-        <v>2</v>
+      <c r="N36">
+        <v>1</v>
       </c>
       <c r="P36">
         <v>0</v>
@@ -4280,15 +4281,15 @@
         <v>470</v>
       </c>
       <c r="H37" s="22">
-        <f t="shared" ref="H37:H38" si="24">E37*0.92</f>
+        <f t="shared" ref="H37:H38" si="27">E37*0.92</f>
         <v>448.48160000000001</v>
       </c>
       <c r="I37" s="9">
-        <f t="shared" ref="I37:I38" si="25">F37/E37 -1</f>
+        <f t="shared" ref="I37:I38" si="28">F37/E37 -1</f>
         <v>0.12825141544268481</v>
       </c>
       <c r="J37" s="26">
-        <f t="shared" ref="J37:J38" si="26">C37*D37</f>
+        <f t="shared" ref="J37:J38" si="29">C37*D37</f>
         <v>4383</v>
       </c>
       <c r="K37" s="18">
@@ -4300,9 +4301,8 @@
       <c r="M37" t="s">
         <v>559</v>
       </c>
-      <c r="N37"/>
-      <c r="O37">
-        <v>2</v>
+      <c r="N37">
+        <v>1</v>
       </c>
       <c r="P37">
         <v>0</v>
@@ -4331,15 +4331,15 @@
         <v>25</v>
       </c>
       <c r="H38" s="22">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>26.523599999999998</v>
       </c>
       <c r="I38" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0.21401318071453357</v>
       </c>
       <c r="J38" s="26">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>4268.7</v>
       </c>
       <c r="K38" s="18">
@@ -4352,7 +4352,7 @@
         <v>199</v>
       </c>
       <c r="N38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P38">
         <v>0</v>
@@ -4402,8 +4402,9 @@
       <c r="M39" t="s">
         <v>199</v>
       </c>
-      <c r="N39">
-        <v>2</v>
+      <c r="N39"/>
+      <c r="O39">
+        <v>1</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -4454,7 +4455,7 @@
       </c>
       <c r="N40"/>
       <c r="O40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P40">
         <v>0</v>
@@ -4474,7 +4475,7 @@
         <v>19.420000000000002</v>
       </c>
       <c r="E41">
-        <v>20.2</v>
+        <v>20.32</v>
       </c>
       <c r="F41" s="12">
         <v>21</v>
@@ -4484,11 +4485,11 @@
       </c>
       <c r="H41" s="22">
         <f>E41*0.92</f>
-        <v>18.584</v>
-      </c>
-      <c r="I41" s="9">
+        <v>18.694400000000002</v>
+      </c>
+      <c r="I41" s="36">
         <f>F41/E41 -1</f>
-        <v>3.9603960396039639E-2</v>
+        <v>3.3464566929133799E-2</v>
       </c>
       <c r="J41" s="26">
         <f>C41*D41</f>
@@ -4505,7 +4506,7 @@
       </c>
       <c r="N41"/>
       <c r="O41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P41">
         <v>1</v>
@@ -4534,15 +4535,15 @@
         <v>160</v>
       </c>
       <c r="H42" s="22">
-        <f t="shared" ref="H42" si="27">E42*0.92</f>
+        <f t="shared" ref="H42" si="30">E42*0.92</f>
         <v>193.5772</v>
       </c>
       <c r="I42" s="9">
-        <f t="shared" ref="I42" si="28">F42/E42 -1</f>
+        <f t="shared" ref="I42" si="31">F42/E42 -1</f>
         <v>0.18815645644218426</v>
       </c>
       <c r="J42" s="26">
-        <f t="shared" ref="J42" si="29">C42*D42</f>
+        <f t="shared" ref="J42" si="32">C42*D42</f>
         <v>4418.6099999999997</v>
       </c>
       <c r="K42" s="18">
@@ -4554,8 +4555,7 @@
       <c r="M42" t="s">
         <v>559</v>
       </c>
-      <c r="N42"/>
-      <c r="O42">
+      <c r="N42">
         <v>1</v>
       </c>
       <c r="P42">
@@ -4585,15 +4585,15 @@
         <v>115</v>
       </c>
       <c r="H43" s="22">
-        <f t="shared" ref="H43" si="30">E43*0.92</f>
+        <f t="shared" ref="H43" si="33">E43*0.92</f>
         <v>145.11160000000001</v>
       </c>
       <c r="I43" s="9">
-        <f t="shared" ref="I43" si="31">F43/E43 -1</f>
+        <f t="shared" ref="I43" si="34">F43/E43 -1</f>
         <v>0.5849870031065747</v>
       </c>
       <c r="J43" s="26">
-        <f t="shared" ref="J43" si="32">C43*D43</f>
+        <f t="shared" ref="J43" si="35">C43*D43</f>
         <v>5830</v>
       </c>
       <c r="K43" s="18">
@@ -4605,9 +4605,8 @@
       <c r="M43" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="N43"/>
-      <c r="O43">
-        <v>2</v>
+      <c r="N43">
+        <v>1</v>
       </c>
       <c r="P43">
         <v>0</v>
@@ -4656,8 +4655,7 @@
       <c r="M44" t="s">
         <v>612</v>
       </c>
-      <c r="N44"/>
-      <c r="O44">
+      <c r="N44">
         <v>1</v>
       </c>
       <c r="P44">
@@ -4707,9 +4705,8 @@
       <c r="M45" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="N45"/>
-      <c r="O45">
-        <v>4</v>
+      <c r="N45">
+        <v>1</v>
       </c>
       <c r="P45">
         <v>1</v>
@@ -4758,8 +4755,8 @@
       <c r="M46" s="7" t="s">
         <v>596</v>
       </c>
-      <c r="N46" s="8">
-        <v>2</v>
+      <c r="N46" s="34">
+        <v>3</v>
       </c>
       <c r="P46">
         <v>0</v>
@@ -4806,7 +4803,7 @@
         <v>163</v>
       </c>
       <c r="N47" s="34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P47">
         <v>0</v>
@@ -4835,15 +4832,15 @@
         <v>70</v>
       </c>
       <c r="H48" s="22">
-        <f t="shared" ref="H48:H50" si="33">E48*0.92</f>
+        <f t="shared" ref="H48:H49" si="36">E48*0.92</f>
         <v>108.146</v>
       </c>
       <c r="I48" s="9">
-        <f t="shared" ref="I48:I50" si="34">F48/E48 -1</f>
+        <f t="shared" ref="I48:I49" si="37">F48/E48 -1</f>
         <v>6.3377286261165455E-2</v>
       </c>
       <c r="J48" s="26">
-        <f t="shared" ref="J48:J50" si="35">C48*D48</f>
+        <f t="shared" ref="J48:J49" si="38">C48*D48</f>
         <v>5673</v>
       </c>
       <c r="K48" s="18">
@@ -4856,7 +4853,7 @@
         <v>541</v>
       </c>
       <c r="N48" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P48">
         <v>0</v>
@@ -4885,15 +4882,15 @@
         <v>130</v>
       </c>
       <c r="H49" s="22">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>132.19480000000001</v>
       </c>
       <c r="I49" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>0.18310251235298214</v>
       </c>
       <c r="J49" s="26">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>5060.88</v>
       </c>
       <c r="K49" s="18">
@@ -4905,8 +4902,8 @@
       <c r="M49" t="s">
         <v>559</v>
       </c>
-      <c r="O49">
-        <v>3</v>
+      <c r="N49" s="8">
+        <v>1</v>
       </c>
       <c r="P49">
         <v>1</v>
@@ -4935,15 +4932,15 @@
         <v>138</v>
       </c>
       <c r="H50" s="22">
-        <f t="shared" ref="H50" si="36">E50*0.92</f>
+        <f t="shared" ref="H50" si="39">E50*0.92</f>
         <v>139.9228</v>
       </c>
       <c r="I50" s="9">
-        <f t="shared" ref="I50" si="37">F50/E50 -1</f>
+        <f t="shared" ref="I50" si="40">F50/E50 -1</f>
         <v>0.31501084883950292</v>
       </c>
       <c r="J50" s="26">
-        <f t="shared" ref="J50" si="38">C50*D50</f>
+        <f t="shared" ref="J50" si="41">C50*D50</f>
         <v>5776</v>
       </c>
       <c r="K50" s="18">
@@ -4955,8 +4952,8 @@
       <c r="M50" s="7" t="s">
         <v>699</v>
       </c>
-      <c r="N50" s="8">
-        <v>2</v>
+      <c r="O50">
+        <v>1</v>
       </c>
       <c r="P50">
         <v>0</v>
@@ -4985,15 +4982,15 @@
         <v>370</v>
       </c>
       <c r="H51" s="22">
-        <f t="shared" ref="H51" si="39">E51*0.92</f>
+        <f t="shared" ref="H51" si="42">E51*0.92</f>
         <v>364.33839999999998</v>
       </c>
       <c r="I51" s="9">
-        <f t="shared" ref="I51" si="40">F51/E51 -1</f>
+        <f t="shared" ref="I51" si="43">F51/E51 -1</f>
         <v>6.0552497348618894E-2</v>
       </c>
       <c r="J51" s="26">
-        <f t="shared" ref="J51" si="41">C51*D51</f>
+        <f t="shared" ref="J51" si="44">C51*D51</f>
         <v>3915</v>
       </c>
       <c r="K51" s="18">
@@ -5005,8 +5002,8 @@
       <c r="M51" t="s">
         <v>382</v>
       </c>
-      <c r="O51">
-        <v>2</v>
+      <c r="N51" s="8">
+        <v>1</v>
       </c>
       <c r="P51">
         <v>1</v>
@@ -5248,11 +5245,11 @@
         <v>100</v>
       </c>
       <c r="M3" s="10">
-        <f xml:space="preserve"> (L3 - K3)/(K3-J3)</f>
+        <f t="shared" ref="M3:M8" si="0" xml:space="preserve"> (L3 - K3)/(K3-J3)</f>
         <v>-2.0171646535282899</v>
       </c>
       <c r="N3" s="10">
-        <f>K3/L3</f>
+        <f t="shared" ref="N3:N8" si="1">K3/L3</f>
         <v>0.3654</v>
       </c>
       <c r="O3" s="4">
@@ -5304,11 +5301,11 @@
         <v>60</v>
       </c>
       <c r="M4" s="10">
-        <f xml:space="preserve"> (L4 - K4)/(K4-J4)</f>
+        <f t="shared" si="0"/>
         <v>-0.49622166246851374</v>
       </c>
       <c r="N4" s="10">
-        <f>K4/L4</f>
+        <f t="shared" si="1"/>
         <v>1.0656666666666665</v>
       </c>
       <c r="O4" s="4">
@@ -5357,11 +5354,11 @@
         <v>20</v>
       </c>
       <c r="M5" s="10">
-        <f xml:space="preserve"> (L5 - K5)/(K5-J5)</f>
+        <f t="shared" si="0"/>
         <v>-0.57020057306590266</v>
       </c>
       <c r="N5" s="10">
-        <f>K5/L5</f>
+        <f t="shared" si="1"/>
         <v>1.1990000000000001</v>
       </c>
       <c r="O5" s="4">
@@ -5413,11 +5410,11 @@
         <v>100</v>
       </c>
       <c r="M6" s="10">
-        <f xml:space="preserve"> (L6 - K6)/(K6-J6)</f>
+        <f t="shared" si="0"/>
         <v>2.1897926634768758</v>
       </c>
       <c r="N6" s="10">
-        <f>K6/L6</f>
+        <f t="shared" si="1"/>
         <v>0.86269999999999991</v>
       </c>
       <c r="O6" s="28">
@@ -5469,11 +5466,11 @@
         <v>57</v>
       </c>
       <c r="M7" s="10">
-        <f xml:space="preserve"> (L7 - K7)/(K7-J7)</f>
+        <f t="shared" si="0"/>
         <v>-3.0694668820678159E-2</v>
       </c>
       <c r="N7" s="10">
-        <f>K7/L7</f>
+        <f t="shared" si="1"/>
         <v>1.0033333333333332</v>
       </c>
       <c r="O7" s="4">
@@ -5527,11 +5524,11 @@
         <v>36</v>
       </c>
       <c r="M8" s="10">
-        <f xml:space="preserve"> (L8 - K8)/(K8-J8)</f>
+        <f t="shared" si="0"/>
         <v>-0.77973568281938321</v>
       </c>
       <c r="N8" s="10">
-        <f>K8/L8</f>
+        <f t="shared" si="1"/>
         <v>1.1966666666666665</v>
       </c>
       <c r="O8" s="4">
@@ -5672,11 +5669,11 @@
         <v>55</v>
       </c>
       <c r="M12" s="10">
-        <f xml:space="preserve"> (L12 - K12)/(K12-J12)</f>
+        <f t="shared" ref="M12:M17" si="2" xml:space="preserve"> (L12 - K12)/(K12-J12)</f>
         <v>-0.73821989528795806</v>
       </c>
       <c r="N12" s="10">
-        <f>K12/L12</f>
+        <f t="shared" ref="N12:N17" si="3">K12/L12</f>
         <v>1.2563636363636363</v>
       </c>
       <c r="O12" s="4">
@@ -5728,11 +5725,11 @@
         <v>94</v>
       </c>
       <c r="M13" s="10">
-        <f xml:space="preserve"> (L13 - K13)/(K13-J13)</f>
+        <f t="shared" si="2"/>
         <v>-0.55022488755622201</v>
       </c>
       <c r="N13" s="10">
-        <f>K13/L13</f>
+        <f t="shared" si="3"/>
         <v>1.1561702127659574</v>
       </c>
       <c r="O13" s="4">
@@ -5786,11 +5783,11 @@
         <v>50</v>
       </c>
       <c r="M14" s="10">
-        <f xml:space="preserve"> (L14 - K14)/(K14-J14)</f>
+        <f t="shared" si="2"/>
         <v>-0.56678700361010836</v>
       </c>
       <c r="N14" s="10">
-        <f>K14/L14</f>
+        <f t="shared" si="3"/>
         <v>1.157</v>
       </c>
       <c r="O14" s="4">
@@ -5842,11 +5839,11 @@
         <v>47.5</v>
       </c>
       <c r="M15" s="10">
-        <f xml:space="preserve"> (L15 - K15)/(K15-J15)</f>
+        <f t="shared" si="2"/>
         <v>6.6923076923077094</v>
       </c>
       <c r="N15" s="10">
-        <f>K15/L15</f>
+        <f t="shared" si="3"/>
         <v>0.81684210526315781</v>
       </c>
       <c r="O15" s="4">
@@ -5895,11 +5892,11 @@
         <v>45</v>
       </c>
       <c r="M16" s="10">
-        <f xml:space="preserve"> (L16 - K16)/(K16-J16)</f>
+        <f t="shared" si="2"/>
         <v>-0.20774647887323941</v>
       </c>
       <c r="N16" s="10">
-        <f>K16/L16</f>
+        <f t="shared" si="3"/>
         <v>1.0524444444444445</v>
       </c>
       <c r="O16" s="4">
@@ -5947,11 +5944,11 @@
         <v>104</v>
       </c>
       <c r="M17" s="10">
-        <f xml:space="preserve"> (L17 - K17)/(K17-J17)</f>
+        <f t="shared" si="2"/>
         <v>-0.34725848563968642</v>
       </c>
       <c r="N17" s="10">
-        <f>K17/L17</f>
+        <f t="shared" si="3"/>
         <v>1.0255769230769229</v>
       </c>
       <c r="O17" s="4">
@@ -6231,11 +6228,11 @@
         <v>24</v>
       </c>
       <c r="M23" s="10">
-        <f xml:space="preserve"> (L23 - K23)/(K23-J23)</f>
+        <f t="shared" ref="M23:M29" si="4" xml:space="preserve"> (L23 - K23)/(K23-J23)</f>
         <v>0.10091743119266069</v>
       </c>
       <c r="N23" s="10">
-        <f>K23/L23</f>
+        <f t="shared" ref="N23:N29" si="5">K23/L23</f>
         <v>0.9770833333333333</v>
       </c>
       <c r="O23" s="4">
@@ -6287,11 +6284,11 @@
         <v>360</v>
       </c>
       <c r="M24" s="10">
-        <f xml:space="preserve"> (L24 - K24)/(K24-J24)</f>
+        <f t="shared" si="4"/>
         <v>-0.70169289283317171</v>
       </c>
       <c r="N24" s="10">
-        <f>K24/L24</f>
+        <f t="shared" si="5"/>
         <v>1.2613611111111109</v>
       </c>
       <c r="O24" s="4">
@@ -6345,11 +6342,11 @@
         <v>130</v>
       </c>
       <c r="M25" s="10">
-        <f xml:space="preserve"> (L25 - K25)/(K25-J25)</f>
+        <f t="shared" si="4"/>
         <v>-0.77912755383765875</v>
       </c>
       <c r="N25" s="10">
-        <f>K25/L25</f>
+        <f t="shared" si="5"/>
         <v>1.5426923076923078</v>
       </c>
       <c r="O25" s="4">
@@ -6404,11 +6401,11 @@
         <v>70</v>
       </c>
       <c r="M26" s="10">
-        <f xml:space="preserve"> (L26 - K26)/(K26-J26)</f>
+        <f t="shared" si="4"/>
         <v>-0.16376306620209027</v>
       </c>
       <c r="N26" s="10">
-        <f>K26/L26</f>
+        <f t="shared" si="5"/>
         <v>1.0335714285714286</v>
       </c>
       <c r="O26" s="4">
@@ -6460,11 +6457,11 @@
         <v>120</v>
       </c>
       <c r="M27" s="10">
-        <f xml:space="preserve"> (L27 - K27)/(K27-J27)</f>
+        <f t="shared" si="4"/>
         <v>-0.35917975008010272</v>
       </c>
       <c r="N27" s="10">
-        <f>K27/L27</f>
+        <f t="shared" si="5"/>
         <v>1.0934166666666667</v>
       </c>
       <c r="O27" s="4">
@@ -6518,11 +6515,11 @@
         <v>260</v>
       </c>
       <c r="M28" s="10">
-        <f xml:space="preserve"> (L28 - K28)/(K28-J28)</f>
+        <f t="shared" si="4"/>
         <v>-10.633911368015418</v>
       </c>
       <c r="N28" s="10">
-        <f>K28/L28</f>
+        <f t="shared" si="5"/>
         <v>0.57546153846153847</v>
       </c>
       <c r="O28" s="4">
@@ -6576,11 +6573,11 @@
         <v>100</v>
       </c>
       <c r="M29" s="10">
-        <f xml:space="preserve"> (L29 - K29)/(K29-J29)</f>
+        <f t="shared" si="4"/>
         <v>-0.65681098204857435</v>
       </c>
       <c r="N29" s="10">
-        <f>K29/L29</f>
+        <f t="shared" si="5"/>
         <v>1.2487999999999999</v>
       </c>
       <c r="O29" s="4">
@@ -7192,7 +7189,7 @@
         <v>12</v>
       </c>
       <c r="M42" s="10">
-        <f xml:space="preserve"> (L42 - K42)/(K42-J42)</f>
+        <f t="shared" ref="M42:M47" si="6" xml:space="preserve"> (L42 - K42)/(K42-J42)</f>
         <v>-0.40594059405940602</v>
       </c>
       <c r="N42" s="10">
@@ -7249,7 +7246,7 @@
         <v>43</v>
       </c>
       <c r="M43" s="10">
-        <f xml:space="preserve"> (L43 - K43)/(K43-J43)</f>
+        <f t="shared" si="6"/>
         <v>-0.53216374269005851</v>
       </c>
       <c r="N43" s="10">
@@ -7308,7 +7305,7 @@
         <v>200</v>
       </c>
       <c r="M44" s="10">
-        <f xml:space="preserve"> (L44 - K44)/(K44-J44)</f>
+        <f t="shared" si="6"/>
         <v>-0.87066735644076565</v>
       </c>
       <c r="N44" s="10">
@@ -7364,7 +7361,7 @@
         <v>200</v>
       </c>
       <c r="M45" s="10">
-        <f xml:space="preserve"> (L45 - K45)/(K45-J45)</f>
+        <f t="shared" si="6"/>
         <v>-2.332445036642238</v>
       </c>
       <c r="N45" s="10"/>
@@ -7420,7 +7417,7 @@
         <v>140</v>
       </c>
       <c r="M46" s="10">
-        <f xml:space="preserve"> (L46 - K46)/(K46-J46)</f>
+        <f t="shared" si="6"/>
         <v>-0.71545101014891399</v>
       </c>
       <c r="N46" s="10">
@@ -7477,7 +7474,7 @@
         <v>100</v>
       </c>
       <c r="M47" s="10">
-        <f xml:space="preserve"> (L47 - K47)/(K47-J47)</f>
+        <f t="shared" si="6"/>
         <v>-0.85313555588192103</v>
       </c>
       <c r="N47" s="10">
@@ -8173,11 +8170,11 @@
         <v>20</v>
       </c>
       <c r="M65" s="10">
-        <f xml:space="preserve"> (L65 - K65)/(K65-J65)</f>
+        <f t="shared" ref="M65:M100" si="7" xml:space="preserve"> (L65 - K65)/(K65-J65)</f>
         <v>1.1551724137931032</v>
       </c>
       <c r="N65" s="10">
-        <f>K65/L65</f>
+        <f t="shared" ref="N65:N107" si="8">K65/L65</f>
         <v>0.86599999999999999</v>
       </c>
       <c r="O65" s="4">
@@ -8230,11 +8227,11 @@
         <v>170</v>
       </c>
       <c r="M66" s="10">
-        <f xml:space="preserve"> (L66 - K66)/(K66-J66)</f>
+        <f t="shared" si="7"/>
         <v>1.4570024570024562</v>
       </c>
       <c r="N66" s="10">
-        <f>K66/L66</f>
+        <f t="shared" si="8"/>
         <v>0.75582352941176478</v>
       </c>
       <c r="O66" s="4">
@@ -8284,11 +8281,11 @@
         <v>220</v>
       </c>
       <c r="M67" s="10">
-        <f xml:space="preserve"> (L67 - K67)/(K67-J67)</f>
+        <f t="shared" si="7"/>
         <v>-0.69590998935684967</v>
       </c>
       <c r="N67" s="10">
-        <f>K67/L67</f>
+        <f t="shared" si="8"/>
         <v>1.6241363636363637</v>
       </c>
       <c r="O67" s="4">
@@ -8338,11 +8335,11 @@
         <v>600</v>
       </c>
       <c r="M68" s="10">
-        <f xml:space="preserve"> (L68 - K68)/(K68-J68)</f>
+        <f t="shared" si="7"/>
         <v>-0.12145837909070933</v>
       </c>
       <c r="N68" s="10">
-        <f>K68/L68</f>
+        <f t="shared" si="8"/>
         <v>1.0460833333333333</v>
       </c>
       <c r="O68" s="4">
@@ -8392,11 +8389,11 @@
         <v>180</v>
       </c>
       <c r="M69" s="10">
-        <f xml:space="preserve"> (L69 - K69)/(K69-J69)</f>
+        <f t="shared" si="7"/>
         <v>-3.258652094717668</v>
       </c>
       <c r="N69" s="10">
-        <f>K69/L69</f>
+        <f t="shared" si="8"/>
         <v>0.50305555555555559</v>
       </c>
       <c r="O69" s="4">
@@ -8446,11 +8443,11 @@
         <v>1000</v>
       </c>
       <c r="M70" s="10">
-        <f xml:space="preserve"> (L70 - K70)/(K70-J70)</f>
+        <f t="shared" si="7"/>
         <v>-0.49014276002719237</v>
       </c>
       <c r="N70" s="10">
-        <f>K70/L70</f>
+        <f t="shared" si="8"/>
         <v>1.31724</v>
       </c>
       <c r="O70" s="4">
@@ -8500,11 +8497,11 @@
         <v>100</v>
       </c>
       <c r="M71" s="10">
-        <f xml:space="preserve"> (L71 - K71)/(K71-J71)</f>
+        <f t="shared" si="7"/>
         <v>-0.63433410315627403</v>
       </c>
       <c r="N71" s="10">
-        <f>K71/L71</f>
+        <f t="shared" si="8"/>
         <v>1.6591999999999998</v>
       </c>
       <c r="O71" s="4">
@@ -8554,11 +8551,11 @@
         <v>160</v>
       </c>
       <c r="M72" s="10">
-        <f xml:space="preserve"> (L72 - K72)/(K72-J72)</f>
+        <f t="shared" si="7"/>
         <v>-0.86798679867986794</v>
       </c>
       <c r="N72" s="10">
-        <f>K72/L72</f>
+        <f t="shared" si="8"/>
         <v>2.6437499999999998</v>
       </c>
       <c r="O72" s="4">
@@ -8608,11 +8605,11 @@
         <v>28.28</v>
       </c>
       <c r="M73" s="10">
-        <f xml:space="preserve"> (L73 - K73)/(K73-J73)</f>
+        <f t="shared" si="7"/>
         <v>-0.5896373056994817</v>
       </c>
       <c r="N73" s="10">
-        <f>K73/L73</f>
+        <f t="shared" si="8"/>
         <v>1.2012022630834511</v>
       </c>
       <c r="O73" s="4">
@@ -8665,11 +8662,11 @@
         <v>40</v>
       </c>
       <c r="M74" s="10">
-        <f xml:space="preserve"> (L74 - K74)/(K74-J74)</f>
+        <f t="shared" si="7"/>
         <v>-0.25492283129324106</v>
       </c>
       <c r="N74" s="10">
-        <f>K74/L74</f>
+        <f t="shared" si="8"/>
         <v>1.11975</v>
       </c>
       <c r="O74" s="4">
@@ -8721,11 +8718,11 @@
         <v>15</v>
       </c>
       <c r="M75" s="10">
-        <f xml:space="preserve"> (L75 - K75)/(K75-J75)</f>
+        <f t="shared" si="7"/>
         <v>0.2224938875305624</v>
       </c>
       <c r="N75" s="10">
-        <f>K75/L75</f>
+        <f t="shared" si="8"/>
         <v>0.93933333333333335</v>
       </c>
       <c r="O75" s="4">
@@ -8775,11 +8772,11 @@
         <v>180</v>
       </c>
       <c r="M76" s="10">
-        <f xml:space="preserve"> (L76 - K76)/(K76-J76)</f>
+        <f t="shared" si="7"/>
         <v>-0.46535500427715987</v>
       </c>
       <c r="N76" s="10">
-        <f>K76/L76</f>
+        <f t="shared" si="8"/>
         <v>1.1208888888888888</v>
       </c>
       <c r="O76" s="4">
@@ -8832,11 +8829,11 @@
         <v>100</v>
       </c>
       <c r="M77" s="10">
-        <f xml:space="preserve"> (L77 - K77)/(K77-J77)</f>
+        <f t="shared" si="7"/>
         <v>-1.418848167539267</v>
       </c>
       <c r="N77" s="10">
-        <f>K77/L77</f>
+        <f t="shared" si="8"/>
         <v>0.59350000000000003</v>
       </c>
       <c r="O77" s="4">
@@ -8889,11 +8886,11 @@
         <v>55</v>
       </c>
       <c r="M78" s="10">
-        <f xml:space="preserve"> (L78 - K78)/(K78-J78)</f>
+        <f t="shared" si="7"/>
         <v>1.0053475935828866</v>
       </c>
       <c r="N78" s="10">
-        <f>K78/L78</f>
+        <f t="shared" si="8"/>
         <v>0.93163636363636371</v>
       </c>
       <c r="O78" s="4">
@@ -8947,11 +8944,11 @@
         <v>150</v>
       </c>
       <c r="M79" s="10">
-        <f xml:space="preserve"> (L79 - K79)/(K79-J79)</f>
+        <f t="shared" si="7"/>
         <v>0.87617260787992057</v>
       </c>
       <c r="N79" s="10">
-        <f>K79/L79</f>
+        <f t="shared" si="8"/>
         <v>0.96886666666666676</v>
       </c>
       <c r="O79" s="4">
@@ -9003,11 +9000,11 @@
         <v>610</v>
       </c>
       <c r="M80" s="10">
-        <f xml:space="preserve"> (L80 - K80)/(K80-J80)</f>
+        <f t="shared" si="7"/>
         <v>1.0896656534954412</v>
       </c>
       <c r="N80" s="10">
-        <f>K80/L80</f>
+        <f t="shared" si="8"/>
         <v>0.90596721311475403</v>
       </c>
       <c r="O80" s="4">
@@ -9057,11 +9054,11 @@
         <v>10</v>
       </c>
       <c r="M81" s="10">
-        <f xml:space="preserve"> (L81 - K81)/(K81-J81)</f>
+        <f t="shared" si="7"/>
         <v>2.8461538461538449</v>
       </c>
       <c r="N81" s="10">
-        <f>K81/L81</f>
+        <f t="shared" si="8"/>
         <v>0.77800000000000002</v>
       </c>
       <c r="O81" s="4">
@@ -9112,11 +9109,11 @@
         <v>40</v>
       </c>
       <c r="M82" s="10">
-        <f xml:space="preserve"> (L82 - K82)/(K82-J82)</f>
+        <f t="shared" si="7"/>
         <v>-3.1220159151193636</v>
       </c>
       <c r="N82" s="10">
-        <f>K82/L82</f>
+        <f t="shared" si="8"/>
         <v>0.70574999999999999</v>
       </c>
       <c r="O82" s="4">
@@ -9168,11 +9165,11 @@
         <v>250</v>
       </c>
       <c r="M83" s="10">
-        <f xml:space="preserve"> (L83 - K83)/(K83-J83)</f>
+        <f t="shared" si="7"/>
         <v>-0.61303304697778804</v>
       </c>
       <c r="N83" s="10">
-        <f>K83/L83</f>
+        <f t="shared" si="8"/>
         <v>1.31684</v>
       </c>
       <c r="O83" s="4">
@@ -9222,11 +9219,11 @@
         <v>675</v>
       </c>
       <c r="M84" s="10">
-        <f xml:space="preserve"> (L84 - K84)/(K84-J84)</f>
+        <f t="shared" si="7"/>
         <v>-1.9191176470588234</v>
       </c>
       <c r="N84" s="10">
-        <f>K84/L84</f>
+        <f t="shared" si="8"/>
         <v>0.67520000000000002</v>
       </c>
       <c r="O84" s="4">
@@ -9279,11 +9276,11 @@
         <v>60</v>
       </c>
       <c r="M85" s="10">
-        <f xml:space="preserve"> (L85 - K85)/(K85-J85)</f>
+        <f t="shared" si="7"/>
         <v>-8.4283589489341452E-3</v>
       </c>
       <c r="N85" s="10">
-        <f>K85/L85</f>
+        <f t="shared" si="8"/>
         <v>1.0028333333333335</v>
       </c>
       <c r="O85" s="4">
@@ -9335,11 +9332,11 @@
         <v>200</v>
       </c>
       <c r="M86" s="10">
-        <f xml:space="preserve"> (L86 - K86)/(K86-J86)</f>
+        <f t="shared" si="7"/>
         <v>-0.14334665905197055</v>
       </c>
       <c r="N86" s="10">
-        <f>K86/L86</f>
+        <f t="shared" si="8"/>
         <v>1.0251000000000001</v>
       </c>
       <c r="O86" s="4">
@@ -9393,11 +9390,11 @@
         <v>175</v>
       </c>
       <c r="M87" s="10">
-        <f xml:space="preserve"> (L87 - K87)/(K87-J87)</f>
+        <f t="shared" si="7"/>
         <v>-0.57748398528008726</v>
       </c>
       <c r="N87" s="10">
-        <f>K87/L87</f>
+        <f t="shared" si="8"/>
         <v>1.4842285714285715</v>
       </c>
       <c r="O87" s="4">
@@ -9449,11 +9446,11 @@
         <v>50</v>
       </c>
       <c r="M88" s="10">
-        <f xml:space="preserve"> (L88 - K88)/(K88-J88)</f>
+        <f t="shared" si="7"/>
         <v>-0.73159509202453987</v>
       </c>
       <c r="N88" s="10">
-        <f>K88/L88</f>
+        <f t="shared" si="8"/>
         <v>1.3815999999999999</v>
       </c>
       <c r="O88" s="4">
@@ -9502,11 +9499,11 @@
         <v>90</v>
       </c>
       <c r="M89" s="11">
-        <f xml:space="preserve"> (L89 - K89)/(K89-J89)</f>
+        <f t="shared" si="7"/>
         <v>-1.7437709185570844</v>
       </c>
       <c r="N89" s="10">
-        <f>K89/L89</f>
+        <f t="shared" si="8"/>
         <v>0.47899999999999998</v>
       </c>
       <c r="O89" s="4">
@@ -9557,11 +9554,11 @@
         <v>90</v>
       </c>
       <c r="M90" s="10">
-        <f xml:space="preserve"> (L90 - K90)/(K90-J90)</f>
+        <f t="shared" si="7"/>
         <v>18.101123595505605</v>
       </c>
       <c r="N90" s="10">
-        <f>K90/L90</f>
+        <f t="shared" si="8"/>
         <v>0.82099999999999995</v>
       </c>
       <c r="O90" s="4">
@@ -9611,11 +9608,11 @@
         <v>22</v>
       </c>
       <c r="M91" s="10">
-        <f xml:space="preserve"> (L91 - K91)/(K91-J91)</f>
+        <f t="shared" si="7"/>
         <v>4.6337817638265867E-2</v>
       </c>
       <c r="N91" s="10">
-        <f>K91/L91</f>
+        <f t="shared" si="8"/>
         <v>0.98590909090909096</v>
       </c>
       <c r="O91" s="4">
@@ -9665,11 +9662,11 @@
         <v>160</v>
       </c>
       <c r="M92" s="10">
-        <f xml:space="preserve"> (L92 - K92)/(K92-J92)</f>
+        <f t="shared" si="7"/>
         <v>6.8431372549019258</v>
       </c>
       <c r="N92" s="10">
-        <f>K92/L92</f>
+        <f t="shared" si="8"/>
         <v>0.89093750000000005</v>
       </c>
       <c r="O92" s="4">
@@ -9719,11 +9716,11 @@
         <v>170</v>
       </c>
       <c r="M93" s="10">
-        <f xml:space="preserve"> (L93 - K93)/(K93-J93)</f>
+        <f t="shared" si="7"/>
         <v>11.779552715654971</v>
       </c>
       <c r="N93" s="10">
-        <f>K93/L93</f>
+        <f t="shared" si="8"/>
         <v>0.78311764705882347</v>
       </c>
       <c r="O93" s="4">
@@ -9773,11 +9770,11 @@
         <v>83</v>
       </c>
       <c r="M94" s="10">
-        <f xml:space="preserve"> (L94 - K94)/(K94-J94)</f>
+        <f t="shared" si="7"/>
         <v>-0.51477723864137626</v>
       </c>
       <c r="N94" s="10">
-        <f>K94/L94</f>
+        <f t="shared" si="8"/>
         <v>1.1406024096385543</v>
       </c>
       <c r="O94" s="4">
@@ -9827,11 +9824,11 @@
         <v>250</v>
       </c>
       <c r="M95" s="10">
-        <f xml:space="preserve"> (L95 - K95)/(K95-J95)</f>
+        <f t="shared" si="7"/>
         <v>-0.42343173431734338</v>
       </c>
       <c r="N95" s="10">
-        <f>K95/L95</f>
+        <f t="shared" si="8"/>
         <v>1.1468800000000001</v>
       </c>
       <c r="O95" s="4">
@@ -9881,11 +9878,11 @@
         <v>175</v>
       </c>
       <c r="M96" s="10">
-        <f xml:space="preserve"> (L96 - K96)/(K96-J96)</f>
+        <f t="shared" si="7"/>
         <v>-0.75854742128645936</v>
       </c>
       <c r="N96" s="10">
-        <f>K96/L96</f>
+        <f t="shared" si="8"/>
         <v>1.4487999999999999</v>
       </c>
       <c r="O96" s="4">
@@ -9939,11 +9936,11 @@
         <v>120</v>
       </c>
       <c r="M97" s="10">
-        <f xml:space="preserve"> (L97 - K97)/(K97-J97)</f>
+        <f t="shared" si="7"/>
         <v>-0.8146088246199481</v>
       </c>
       <c r="N97" s="10">
-        <f>K97/L97</f>
+        <f t="shared" si="8"/>
         <v>1.7323333333333333</v>
       </c>
       <c r="O97" s="4">
@@ -9996,11 +9993,11 @@
         <v>140</v>
       </c>
       <c r="M98" s="10">
-        <f xml:space="preserve"> (L98 - K98)/(K98-J98)</f>
+        <f t="shared" si="7"/>
         <v>-0.8202247191011236</v>
       </c>
       <c r="N98" s="10">
-        <f>K98/L98</f>
+        <f t="shared" si="8"/>
         <v>1.6517857142857142</v>
       </c>
       <c r="O98" s="4">
@@ -10050,11 +10047,11 @@
         <v>35</v>
       </c>
       <c r="M99" s="10">
-        <f xml:space="preserve"> (L99 - K99)/(K99-J99)</f>
+        <f t="shared" si="7"/>
         <v>-0.22118380062305318</v>
       </c>
       <c r="N99" s="10">
-        <f>K99/L99</f>
+        <f t="shared" si="8"/>
         <v>1.0811428571428572</v>
       </c>
       <c r="O99" s="28">
@@ -10104,11 +10101,11 @@
         <v>105</v>
       </c>
       <c r="M100" s="10">
-        <f xml:space="preserve"> (L100 - K100)/(K100-J100)</f>
+        <f t="shared" si="7"/>
         <v>-0.85881688550049418</v>
       </c>
       <c r="N100" s="10">
-        <f>K100/L100</f>
+        <f t="shared" si="8"/>
         <v>1.5793333333333335</v>
       </c>
       <c r="O100" s="4">
@@ -10161,7 +10158,7 @@
         <v>0.99</v>
       </c>
       <c r="N101" s="10">
-        <f>K101/L101</f>
+        <f t="shared" si="8"/>
         <v>0.86769419927106661</v>
       </c>
       <c r="O101" s="4">
@@ -10215,7 +10212,7 @@
         <v>0.4</v>
       </c>
       <c r="N102" s="10">
-        <f>K102/L102</f>
+        <f t="shared" si="8"/>
         <v>1.1268279569892474</v>
       </c>
       <c r="O102" s="4">
@@ -10268,7 +10265,7 @@
         <v>2.66</v>
       </c>
       <c r="N103" s="10">
-        <f>K103/L103</f>
+        <f t="shared" si="8"/>
         <v>0.72242083758937692</v>
       </c>
       <c r="O103" s="4">
@@ -10321,7 +10318,7 @@
         <v>0.43</v>
       </c>
       <c r="N104" s="10">
-        <f>K104/L104</f>
+        <f t="shared" si="8"/>
         <v>0.81194223368598184</v>
       </c>
       <c r="O104" s="4">
@@ -10374,7 +10371,7 @@
         <v>0.15</v>
       </c>
       <c r="N105" s="10">
-        <f>K105/L105</f>
+        <f t="shared" si="8"/>
         <v>0.96678589678078697</v>
       </c>
       <c r="O105" s="28">
@@ -10427,7 +10424,7 @@
         <v>0.99</v>
       </c>
       <c r="N106" s="10">
-        <f>K106/L106</f>
+        <f t="shared" si="8"/>
         <v>0.59794821690278466</v>
       </c>
       <c r="O106" s="4">
@@ -10480,7 +10477,7 @@
         <v>1.26</v>
       </c>
       <c r="N107" s="10">
-        <f>K107/L107</f>
+        <f t="shared" si="8"/>
         <v>0.91479507122258152</v>
       </c>
       <c r="O107" s="4">
@@ -10771,7 +10768,7 @@
         <v>150</v>
       </c>
       <c r="M113" s="10">
-        <f xml:space="preserve"> (L113 - K113)/(K113-J113)</f>
+        <f t="shared" ref="M113:M124" si="9" xml:space="preserve"> (L113 - K113)/(K113-J113)</f>
         <v>-1.7220216606498195</v>
       </c>
       <c r="N113" s="10">
@@ -10826,7 +10823,7 @@
         <v>160</v>
       </c>
       <c r="M114" s="10">
-        <f xml:space="preserve"> (L114 - K114)/(K114-J114)</f>
+        <f t="shared" si="9"/>
         <v>-2.6813787305590582</v>
       </c>
       <c r="N114" s="11">
@@ -10881,7 +10878,7 @@
         <v>53</v>
       </c>
       <c r="M115" s="10">
-        <f xml:space="preserve"> (L115 - K115)/(K115-J115)</f>
+        <f t="shared" si="9"/>
         <v>-0.83147960903269291</v>
       </c>
       <c r="N115" s="10"/>
@@ -10932,11 +10929,11 @@
         <v>14</v>
       </c>
       <c r="M116" s="10">
-        <f xml:space="preserve"> (L116 - K116)/(K116-J116)</f>
+        <f t="shared" si="9"/>
         <v>-0.79338842975206614</v>
       </c>
       <c r="N116" s="10">
-        <f>K116/L116</f>
+        <f t="shared" ref="N116:N124" si="10">K116/L116</f>
         <v>1.9600000000000002</v>
       </c>
       <c r="O116" s="4">
@@ -10986,11 +10983,11 @@
         <v>200</v>
       </c>
       <c r="M117" s="10">
-        <f xml:space="preserve"> (L117 - K117)/(K117-J117)</f>
+        <f t="shared" si="9"/>
         <v>4.0041601664067117E-2</v>
       </c>
       <c r="N117" s="10">
-        <f>K117/L117</f>
+        <f t="shared" si="10"/>
         <v>0.99614999999999998</v>
       </c>
       <c r="O117" s="4">
@@ -11041,11 +11038,11 @@
         <v>7</v>
       </c>
       <c r="M118" s="10">
-        <f xml:space="preserve"> (L118 - K118)/(K118-J118)</f>
+        <f t="shared" si="9"/>
         <v>0.43540669856459341</v>
       </c>
       <c r="N118" s="10">
-        <f>K118/L118</f>
+        <f t="shared" si="10"/>
         <v>0.87</v>
       </c>
       <c r="O118" s="28">
@@ -11095,11 +11092,11 @@
         <v>80</v>
       </c>
       <c r="M119" s="10">
-        <f xml:space="preserve"> (L119 - K119)/(K119-J119)</f>
+        <f t="shared" si="9"/>
         <v>-1.4900359359686377</v>
       </c>
       <c r="N119" s="10">
-        <f>K119/L119</f>
+        <f t="shared" si="10"/>
         <v>0.42987500000000001</v>
       </c>
       <c r="O119" s="4">
@@ -11151,11 +11148,11 @@
         <v>90</v>
       </c>
       <c r="M120" s="10">
-        <f xml:space="preserve"> (L120 - K120)/(K120-J120)</f>
+        <f t="shared" si="9"/>
         <v>6.0224719101123547</v>
       </c>
       <c r="N120" s="10">
-        <f>K120/L120</f>
+        <f t="shared" si="10"/>
         <v>0.76177777777777778</v>
       </c>
       <c r="O120" s="4">
@@ -11208,11 +11205,11 @@
         <v>180</v>
       </c>
       <c r="M121" s="10">
-        <f xml:space="preserve"> (L121 - K121)/(K121-J121)</f>
+        <f t="shared" si="9"/>
         <v>-2.493651979088872</v>
       </c>
       <c r="N121" s="10">
-        <f>K121/L121</f>
+        <f t="shared" si="10"/>
         <v>0.629</v>
       </c>
       <c r="O121" s="4">
@@ -11262,11 +11259,11 @@
         <v>37.5</v>
       </c>
       <c r="M122" s="10">
-        <f xml:space="preserve"> (L122 - K122)/(K122-J122)</f>
+        <f t="shared" si="9"/>
         <v>-8.3769633507853478E-2</v>
       </c>
       <c r="N122" s="10">
-        <f>K122/L122</f>
+        <f t="shared" si="10"/>
         <v>1.0426666666666666</v>
       </c>
       <c r="O122" s="4">
@@ -11316,11 +11313,11 @@
         <v>70</v>
       </c>
       <c r="M123" s="10">
-        <f xml:space="preserve"> (L123 - K123)/(K123-J123)</f>
+        <f t="shared" si="9"/>
         <v>-0.72318339100346019</v>
       </c>
       <c r="N123" s="10">
-        <f>K123/L123</f>
+        <f t="shared" si="10"/>
         <v>1.4478571428571427</v>
       </c>
       <c r="O123" s="4">
@@ -11370,11 +11367,11 @@
         <v>48</v>
       </c>
       <c r="M124" s="10">
-        <f xml:space="preserve"> (L124 - K124)/(K124-J124)</f>
+        <f t="shared" si="9"/>
         <v>-0.83663467429038185</v>
       </c>
       <c r="N124" s="10">
-        <f>K124/L124</f>
+        <f t="shared" si="10"/>
         <v>1.8535416666666666</v>
       </c>
       <c r="O124" s="4">
@@ -11473,7 +11470,7 @@
         <v>-4.963041182682143E-2</v>
       </c>
       <c r="N126" s="10">
-        <f>K126/L126</f>
+        <f t="shared" ref="N126:N134" si="11">K126/L126</f>
         <v>1.0282</v>
       </c>
       <c r="O126" s="4">
@@ -11528,7 +11525,7 @@
         <v>-0.88228369629193637</v>
       </c>
       <c r="N127" s="10">
-        <f>K127/L127</f>
+        <f t="shared" si="11"/>
         <v>1.9368749999999999</v>
       </c>
       <c r="O127" s="4">
@@ -11582,7 +11579,7 @@
         <v>-5.2944785276073549</v>
       </c>
       <c r="N128" s="10">
-        <f>K128/L128</f>
+        <f t="shared" si="11"/>
         <v>0.78951219512195114</v>
       </c>
       <c r="O128" s="4">
@@ -11636,7 +11633,7 @@
         <v>1.2281639928698755</v>
       </c>
       <c r="N129" s="10">
-        <f>K129/L129</f>
+        <f t="shared" si="11"/>
         <v>0.8162666666666667</v>
       </c>
       <c r="O129" s="4">
@@ -11683,7 +11680,7 @@
       <c r="L130" s="10"/>
       <c r="M130" s="10"/>
       <c r="N130" s="10" t="e">
-        <f>K130/L130</f>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O130" s="4">
@@ -11737,7 +11734,7 @@
         <v>15.279069767441872</v>
       </c>
       <c r="N131" s="10">
-        <f>K131/L131</f>
+        <f t="shared" si="11"/>
         <v>0.85399999999999998</v>
       </c>
       <c r="O131" s="4">
@@ -11787,7 +11784,7 @@
         <v>-3</v>
       </c>
       <c r="N132" s="10">
-        <f>K132/L132</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O132" s="28">
@@ -11841,7 +11838,7 @@
         <v>10.627906976744212</v>
       </c>
       <c r="N133" s="10">
-        <f>K133/L133</f>
+        <f t="shared" si="11"/>
         <v>0.81719999999999993</v>
       </c>
       <c r="O133" s="4">
@@ -11895,7 +11892,7 @@
         <v>0.58730158730158755</v>
       </c>
       <c r="N134" s="10">
-        <f>K134/L134</f>
+        <f t="shared" si="11"/>
         <v>0.88615384615384607</v>
       </c>
       <c r="O134" s="4">
@@ -11986,7 +11983,7 @@
       <c r="L136" s="10"/>
       <c r="M136" s="10"/>
       <c r="N136" s="10" t="e">
-        <f>K136/L136</f>
+        <f t="shared" ref="N136:N142" si="12">K136/L136</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O136" s="4">
@@ -12036,11 +12033,11 @@
         <v>130</v>
       </c>
       <c r="M137" s="10">
-        <f xml:space="preserve"> (L137 - K137)/(K137-J137)</f>
+        <f t="shared" ref="M137:M142" si="13" xml:space="preserve"> (L137 - K137)/(K137-J137)</f>
         <v>-1.6301197227473221</v>
       </c>
       <c r="N137" s="10">
-        <f>K137/L137</f>
+        <f t="shared" si="12"/>
         <v>0.40300000000000002</v>
       </c>
       <c r="O137" s="4">
@@ -12090,11 +12087,11 @@
         <v>1100</v>
       </c>
       <c r="M138" s="10">
-        <f xml:space="preserve"> (L138 - K138)/(K138-J138)</f>
+        <f t="shared" si="13"/>
         <v>1.7616680475006921</v>
       </c>
       <c r="N138" s="10">
-        <f>K138/L138</f>
+        <f t="shared" si="12"/>
         <v>0.88401818181818181</v>
       </c>
       <c r="O138" s="4">
@@ -12142,11 +12139,11 @@
         <v>52.5</v>
       </c>
       <c r="M139" s="10">
-        <f xml:space="preserve"> (L139 - K139)/(K139-J139)</f>
+        <f t="shared" si="13"/>
         <v>-3.7173913043478208</v>
       </c>
       <c r="N139" s="10">
-        <f>K139/L139</f>
+        <f t="shared" si="12"/>
         <v>0.93485714285714283</v>
       </c>
       <c r="O139" s="4">
@@ -12197,11 +12194,11 @@
         <v>10</v>
       </c>
       <c r="M140" s="10">
-        <f xml:space="preserve"> (L140 - K140)/(K140-J140)</f>
+        <f t="shared" si="13"/>
         <v>-2.7094017094017095</v>
       </c>
       <c r="N140" s="10">
-        <f>K140/L140</f>
+        <f t="shared" si="12"/>
         <v>0.68300000000000005</v>
       </c>
       <c r="O140" s="4">
@@ -12252,11 +12249,11 @@
         <v>160</v>
       </c>
       <c r="M141" s="10">
-        <f xml:space="preserve"> (L141 - K141)/(K141-J141)</f>
+        <f t="shared" si="13"/>
         <v>-2.124859392575928</v>
       </c>
       <c r="N141" s="10">
-        <f>K141/L141</f>
+        <f t="shared" si="12"/>
         <v>0.52774999999999994</v>
       </c>
       <c r="O141" s="4">
@@ -12306,11 +12303,11 @@
         <v>250</v>
       </c>
       <c r="M142" s="10">
-        <f xml:space="preserve"> (L142 - K142)/(K142-J142)</f>
+        <f t="shared" si="13"/>
         <v>-1.930232558139535</v>
       </c>
       <c r="N142" s="10">
-        <f>K142/L142</f>
+        <f t="shared" si="12"/>
         <v>0.58499999999999996</v>
       </c>
       <c r="O142" s="4">
@@ -13325,7 +13322,7 @@
         <v>1.97</v>
       </c>
       <c r="N164" s="10">
-        <f>K164/L164</f>
+        <f t="shared" ref="N164:N172" si="14">K164/L164</f>
         <v>0.7544291675217184</v>
       </c>
       <c r="O164" s="4">
@@ -13375,11 +13372,11 @@
         <v>4</v>
       </c>
       <c r="M165" s="10">
-        <f xml:space="preserve"> (L165 - K165)/(K165-J165)</f>
+        <f t="shared" ref="M165:M171" si="15" xml:space="preserve"> (L165 - K165)/(K165-J165)</f>
         <v>-0.64539007092198586</v>
       </c>
       <c r="N165" s="10">
-        <f>K165/L165</f>
+        <f t="shared" si="14"/>
         <v>1.4550000000000001</v>
       </c>
       <c r="O165" s="4">
@@ -13429,11 +13426,11 @@
         <v>240</v>
       </c>
       <c r="M166" s="10">
-        <f xml:space="preserve"> (L166 - K166)/(K166-J166)</f>
+        <f t="shared" si="15"/>
         <v>-0.1694352159468438</v>
       </c>
       <c r="N166" s="10">
-        <f>K166/L166</f>
+        <f t="shared" si="14"/>
         <v>1.034</v>
       </c>
       <c r="O166" s="4">
@@ -13483,11 +13480,11 @@
         <v>400</v>
       </c>
       <c r="M167" s="10">
-        <f xml:space="preserve"> (L167 - K167)/(K167-J167)</f>
+        <f t="shared" si="15"/>
         <v>-7.1957868649318515</v>
       </c>
       <c r="N167" s="10">
-        <f>K167/L167</f>
+        <f t="shared" si="14"/>
         <v>0.70965</v>
       </c>
       <c r="O167" s="4">
@@ -13539,11 +13536,11 @@
         <v>250</v>
       </c>
       <c r="M168" s="10">
-        <f xml:space="preserve"> (L168 - K168)/(K168-J168)</f>
+        <f t="shared" si="15"/>
         <v>1.3337222870478416</v>
       </c>
       <c r="N168" s="10">
-        <f>K168/L168</f>
+        <f t="shared" si="14"/>
         <v>0.77139999999999997</v>
       </c>
       <c r="O168" s="4">
@@ -13593,11 +13590,11 @@
         <v>270</v>
       </c>
       <c r="M169" s="10">
-        <f xml:space="preserve"> (L169 - K169)/(K169-J169)</f>
+        <f t="shared" si="15"/>
         <v>0.86125211505922095</v>
       </c>
       <c r="N169" s="10">
-        <f>K169/L169</f>
+        <f t="shared" si="14"/>
         <v>0.90574074074074074</v>
       </c>
       <c r="O169" s="4">
@@ -13647,11 +13644,11 @@
         <v>33</v>
       </c>
       <c r="M170" s="10">
-        <f xml:space="preserve"> (L170 - K170)/(K170-J170)</f>
+        <f t="shared" si="15"/>
         <v>-2.9267822736030822</v>
       </c>
       <c r="N170" s="10">
-        <f>K170/L170</f>
+        <f t="shared" si="14"/>
         <v>0.53969696969696968</v>
       </c>
       <c r="O170" s="4">
@@ -13701,11 +13698,11 @@
         <v>600</v>
       </c>
       <c r="M171" s="10">
-        <f xml:space="preserve"> (L171 - K171)/(K171-J171)</f>
+        <f t="shared" si="15"/>
         <v>2.3288948069241053</v>
       </c>
       <c r="N171" s="10">
-        <f>K171/L171</f>
+        <f t="shared" si="14"/>
         <v>0.88339999999999996</v>
       </c>
       <c r="O171" s="4">
@@ -13752,7 +13749,7 @@
       <c r="L172" s="10"/>
       <c r="M172" s="10"/>
       <c r="N172" s="10" t="e">
-        <f>K172/L172</f>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O172" s="4">
@@ -14449,7 +14446,7 @@
         <v>65</v>
       </c>
       <c r="M189" s="10">
-        <f xml:space="preserve"> (L189 - K189)/(K189-J189)</f>
+        <f t="shared" ref="M189:M194" si="16" xml:space="preserve"> (L189 - K189)/(K189-J189)</f>
         <v>-1.8246289169873555</v>
       </c>
       <c r="N189" s="10"/>
@@ -14502,11 +14499,11 @@
         <v>32</v>
       </c>
       <c r="M190" s="10">
-        <f xml:space="preserve"> (L190 - K190)/(K190-J190)</f>
+        <f t="shared" si="16"/>
         <v>-2.1940298507462681</v>
       </c>
       <c r="N190" s="11">
-        <f>K190/L190</f>
+        <f t="shared" ref="N190:N197" si="17">K190/L190</f>
         <v>0.77031249999999996</v>
       </c>
       <c r="O190" s="4">
@@ -14556,11 +14553,11 @@
         <v>525</v>
       </c>
       <c r="M191" s="10">
-        <f xml:space="preserve"> (L191 - K191)/(K191-J191)</f>
+        <f t="shared" si="16"/>
         <v>-1.1496806812134115</v>
       </c>
       <c r="N191" s="10">
-        <f>K191/L191</f>
+        <f t="shared" si="17"/>
         <v>0.34163809523809524</v>
       </c>
       <c r="O191" s="4">
@@ -14612,11 +14609,11 @@
         <v>11</v>
       </c>
       <c r="M192" s="10">
-        <f xml:space="preserve"> (L192 - K192)/(K192-J192)</f>
+        <f t="shared" si="16"/>
         <v>-0.52772073921971252</v>
       </c>
       <c r="N192" s="10">
-        <f>K192/L192</f>
+        <f t="shared" si="17"/>
         <v>1.2336363636363636</v>
       </c>
       <c r="O192" s="4">
@@ -14668,11 +14665,11 @@
         <v>250</v>
       </c>
       <c r="M193" s="10">
-        <f xml:space="preserve"> (L193 - K193)/(K193-J193)</f>
+        <f t="shared" si="16"/>
         <v>-1.9220839096357769</v>
       </c>
       <c r="N193" s="10">
-        <f>K193/L193</f>
+        <f t="shared" si="17"/>
         <v>0.49972000000000005</v>
       </c>
       <c r="O193" s="4">
@@ -14722,11 +14719,11 @@
         <v>125</v>
       </c>
       <c r="M194" s="10">
-        <f xml:space="preserve"> (L194 - K194)/(K194-J194)</f>
+        <f t="shared" si="16"/>
         <v>1.0509296685529426E-2</v>
       </c>
       <c r="N194" s="10">
-        <f>K194/L194</f>
+        <f t="shared" si="17"/>
         <v>0.99584000000000006</v>
       </c>
       <c r="O194" s="4">
@@ -14773,7 +14770,7 @@
       <c r="L195" s="10"/>
       <c r="M195" s="10"/>
       <c r="N195" s="10" t="e">
-        <f>K195/L195</f>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O195" s="4">
@@ -14827,7 +14824,7 @@
         <v>4.4568245125348023E-2</v>
       </c>
       <c r="N196" s="10">
-        <f>K196/L196</f>
+        <f t="shared" si="17"/>
         <v>0.9893333333333334</v>
       </c>
       <c r="O196" s="4">
@@ -14881,7 +14878,7 @@
         <v>-1.925069380203515</v>
       </c>
       <c r="N197" s="10">
-        <f>K197/L197</f>
+        <f t="shared" si="17"/>
         <v>0.65316666666666667</v>
       </c>
       <c r="O197" s="4">
@@ -15035,11 +15032,11 @@
         <v>160</v>
       </c>
       <c r="M202" s="10">
-        <f xml:space="preserve"> (L202 - K202)/(K202-J202)</f>
+        <f t="shared" ref="M202:M221" si="18" xml:space="preserve"> (L202 - K202)/(K202-J202)</f>
         <v>-1.903546419697312</v>
       </c>
       <c r="N202" s="10">
-        <f>K202/L202</f>
+        <f t="shared" ref="N202:N208" si="19">K202/L202</f>
         <v>0.47331250000000002</v>
       </c>
       <c r="O202" s="4">
@@ -15089,11 +15086,11 @@
         <v>50</v>
       </c>
       <c r="M203" s="10">
-        <f xml:space="preserve"> (L203 - K203)/(K203-J203)</f>
+        <f t="shared" si="18"/>
         <v>2.6269430051813476</v>
       </c>
       <c r="N203" s="10">
-        <f>K203/L203</f>
+        <f t="shared" si="19"/>
         <v>0.89859999999999995</v>
       </c>
       <c r="O203" s="4">
@@ -15143,11 +15140,11 @@
         <v>280</v>
       </c>
       <c r="M204" s="10">
-        <f xml:space="preserve"> (L204 - K204)/(K204-J204)</f>
+        <f t="shared" si="18"/>
         <v>-0.18077553249590397</v>
       </c>
       <c r="N204" s="10">
-        <f>K204/L204</f>
+        <f t="shared" si="19"/>
         <v>1.0472857142857144</v>
       </c>
       <c r="O204" s="4">
@@ -15197,11 +15194,11 @@
         <v>130</v>
       </c>
       <c r="M205" s="10">
-        <f xml:space="preserve"> (L205 - K205)/(K205-J205)</f>
+        <f t="shared" si="18"/>
         <v>-0.75210708973723339</v>
       </c>
       <c r="N205" s="10">
-        <f>K205/L205</f>
+        <f t="shared" si="19"/>
         <v>1.1166923076923077</v>
       </c>
       <c r="O205" s="4">
@@ -15253,11 +15250,11 @@
         <v>200</v>
       </c>
       <c r="M206" s="10">
-        <f xml:space="preserve"> (L206 - K206)/(K206-J206)</f>
+        <f t="shared" si="18"/>
         <v>-1.6129328838492185</v>
       </c>
       <c r="N206" s="10">
-        <f>K206/L206</f>
+        <f t="shared" si="19"/>
         <v>0.73685</v>
       </c>
       <c r="O206" s="4">
@@ -15307,11 +15304,11 @@
         <v>90</v>
       </c>
       <c r="M207" s="10">
-        <f xml:space="preserve"> (L207 - K207)/(K207-J207)</f>
+        <f t="shared" si="18"/>
         <v>1.2598870056497189</v>
       </c>
       <c r="N207" s="10">
-        <f>K207/L207</f>
+        <f t="shared" si="19"/>
         <v>0.87611111111111106</v>
       </c>
       <c r="O207" s="4">
@@ -15361,11 +15358,11 @@
         <v>200</v>
       </c>
       <c r="M208" s="10">
-        <f xml:space="preserve"> (L208 - K208)/(K208-J208)</f>
+        <f t="shared" si="18"/>
         <v>-9.1885856079404444</v>
       </c>
       <c r="N208" s="10">
-        <f>K208/L208</f>
+        <f t="shared" si="19"/>
         <v>0.81484999999999996</v>
       </c>
       <c r="O208" s="4">
@@ -15415,7 +15412,7 @@
         <v>600</v>
       </c>
       <c r="M209" s="10">
-        <f xml:space="preserve"> (L209 - K209)/(K209-J209)</f>
+        <f t="shared" si="18"/>
         <v>-2.2588116817724071</v>
       </c>
       <c r="N209" s="10"/>
@@ -15466,7 +15463,7 @@
         <v>420</v>
       </c>
       <c r="M210" s="10">
-        <f xml:space="preserve"> (L210 - K210)/(K210-J210)</f>
+        <f t="shared" si="18"/>
         <v>-1.4589261128958237</v>
       </c>
       <c r="N210" s="10">
@@ -15520,7 +15517,7 @@
         <v>180</v>
       </c>
       <c r="M211" s="10">
-        <f xml:space="preserve"> (L211 - K211)/(K211-J211)</f>
+        <f t="shared" si="18"/>
         <v>-0.85184087710200762</v>
       </c>
       <c r="N211" s="10">
@@ -15574,11 +15571,11 @@
         <v>70</v>
       </c>
       <c r="M212" s="10">
-        <f xml:space="preserve"> (L212 - K212)/(K212-J212)</f>
+        <f t="shared" si="18"/>
         <v>-18.07317073170746</v>
       </c>
       <c r="N212" s="10">
-        <f>K212/L212</f>
+        <f t="shared" ref="N212:N228" si="20">K212/L212</f>
         <v>0.89414285714285724</v>
       </c>
       <c r="O212" s="4">
@@ -15631,11 +15628,11 @@
         <v>170</v>
       </c>
       <c r="M213" s="10">
-        <f xml:space="preserve"> (L213 - K213)/(K213-J213)</f>
+        <f t="shared" si="18"/>
         <v>-8.3863636363636385</v>
       </c>
       <c r="N213" s="10">
-        <f>K213/L213</f>
+        <f t="shared" si="20"/>
         <v>0.5658823529411765</v>
       </c>
       <c r="O213" s="4">
@@ -15685,11 +15682,11 @@
         <v>300</v>
       </c>
       <c r="M214" s="10">
-        <f xml:space="preserve"> (L214 - K214)/(K214-J214)</f>
+        <f t="shared" si="18"/>
         <v>-0.6428358830882791</v>
       </c>
       <c r="N214" s="10">
-        <f>K214/L214</f>
+        <f t="shared" si="20"/>
         <v>1.3599666666666668</v>
       </c>
       <c r="O214" s="4">
@@ -15744,11 +15741,11 @@
         <v>65</v>
       </c>
       <c r="M215" s="10">
-        <f xml:space="preserve"> (L215 - K215)/(K215-J215)</f>
+        <f t="shared" si="18"/>
         <v>-2.3586956521739131</v>
       </c>
       <c r="N215" s="10">
-        <f>K215/L215</f>
+        <f t="shared" si="20"/>
         <v>0.7329230769230769</v>
       </c>
       <c r="O215" s="4">
@@ -15801,11 +15798,11 @@
         <v>30</v>
       </c>
       <c r="M216" s="10">
-        <f xml:space="preserve"> (L216 - K216)/(K216-J216)</f>
+        <f t="shared" si="18"/>
         <v>-0.86376021798365121</v>
       </c>
       <c r="N216" s="10">
-        <f>K216/L216</f>
+        <f t="shared" si="20"/>
         <v>1.6340000000000001</v>
       </c>
       <c r="O216" s="4">
@@ -15857,11 +15854,11 @@
         <v>240</v>
       </c>
       <c r="M217" s="10">
-        <f xml:space="preserve"> (L217 - K217)/(K217-J217)</f>
+        <f t="shared" si="18"/>
         <v>-0.52623475068103753</v>
       </c>
       <c r="N217" s="10">
-        <f>K217/L217</f>
+        <f t="shared" si="20"/>
         <v>1.185125</v>
       </c>
       <c r="O217" s="4">
@@ -15911,11 +15908,11 @@
         <v>95</v>
       </c>
       <c r="M218" s="10">
-        <f xml:space="preserve"> (L218 - K218)/(K218-J218)</f>
+        <f t="shared" si="18"/>
         <v>1.631578947368423</v>
       </c>
       <c r="N218" s="10">
-        <f>K218/L218</f>
+        <f t="shared" si="20"/>
         <v>0.93473684210526309</v>
       </c>
       <c r="O218" s="4">
@@ -15965,11 +15962,11 @@
         <v>100</v>
       </c>
       <c r="M219" s="10">
-        <f xml:space="preserve"> (L219 - K219)/(K219-J219)</f>
+        <f t="shared" si="18"/>
         <v>-0.92193903438585534</v>
       </c>
       <c r="N219" s="10">
-        <f>K219/L219</f>
+        <f t="shared" si="20"/>
         <v>3.3620999999999999</v>
       </c>
       <c r="O219" s="4">
@@ -16021,11 +16018,11 @@
         <v>60</v>
       </c>
       <c r="M220" s="10">
-        <f xml:space="preserve"> (L220 - K220)/(K220-J220)</f>
+        <f t="shared" si="18"/>
         <v>-0.79398434281005348</v>
       </c>
       <c r="N220" s="10">
-        <f>K220/L220</f>
+        <f t="shared" si="20"/>
         <v>1.3211666666666666</v>
       </c>
       <c r="O220" s="4">
@@ -16075,11 +16072,11 @@
         <v>70</v>
       </c>
       <c r="M221" s="11">
-        <f xml:space="preserve"> (L221 - K221)/(K221-J221)</f>
+        <f t="shared" si="18"/>
         <v>0.24378109452736296</v>
       </c>
       <c r="N221" s="10">
-        <f>K221/L221</f>
+        <f t="shared" si="20"/>
         <v>0.95800000000000007</v>
       </c>
       <c r="O221" s="4">
@@ -16124,7 +16121,7 @@
       <c r="L222" s="10"/>
       <c r="M222" s="10"/>
       <c r="N222" s="10" t="e">
-        <f>K222/L222</f>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O222" s="4">
@@ -16174,11 +16171,11 @@
         <v>31</v>
       </c>
       <c r="M223" s="10">
-        <f xml:space="preserve"> (L223 - K223)/(K223-J223)</f>
+        <f t="shared" ref="M223:M243" si="21" xml:space="preserve"> (L223 - K223)/(K223-J223)</f>
         <v>-3.9702970297029658</v>
       </c>
       <c r="N223" s="10">
-        <f>K223/L223</f>
+        <f t="shared" si="20"/>
         <v>0.87064516129032254</v>
       </c>
       <c r="O223" s="4">
@@ -16228,11 +16225,11 @@
         <v>48</v>
       </c>
       <c r="M224" s="10">
-        <f xml:space="preserve"> (L224 - K224)/(K224-J224)</f>
+        <f t="shared" si="21"/>
         <v>0.21065375302663364</v>
       </c>
       <c r="N224" s="10">
-        <f>K224/L224</f>
+        <f t="shared" si="20"/>
         <v>0.98187500000000005</v>
       </c>
       <c r="O224" s="4">
@@ -16282,11 +16279,11 @@
         <v>55</v>
       </c>
       <c r="M225" s="10">
-        <f xml:space="preserve"> (L225 - K225)/(K225-J225)</f>
+        <f t="shared" si="21"/>
         <v>-0.29639401934916432</v>
       </c>
       <c r="N225" s="10">
-        <f>K225/L225</f>
+        <f t="shared" si="20"/>
         <v>1.0612727272727271</v>
       </c>
       <c r="O225" s="4">
@@ -16336,11 +16333,11 @@
         <v>130</v>
       </c>
       <c r="M226" s="10">
-        <f xml:space="preserve"> (L226 - K226)/(K226-J226)</f>
+        <f t="shared" si="21"/>
         <v>-2.9047619047619047</v>
       </c>
       <c r="N226" s="10">
-        <f>K226/L226</f>
+        <f t="shared" si="20"/>
         <v>0.76538461538461533</v>
       </c>
       <c r="O226" s="28">
@@ -16390,11 +16387,11 @@
         <v>20</v>
       </c>
       <c r="M227" s="10">
-        <f xml:space="preserve"> (L227 - K227)/(K227-J227)</f>
+        <f t="shared" si="21"/>
         <v>-4.267973856209152</v>
       </c>
       <c r="N227" s="10">
-        <f>K227/L227</f>
+        <f t="shared" si="20"/>
         <v>0.67349999999999999</v>
       </c>
       <c r="O227" s="4">
@@ -16445,11 +16442,11 @@
         <v>500</v>
       </c>
       <c r="M228" s="10">
-        <f xml:space="preserve"> (L228 - K228)/(K228-J228)</f>
+        <f t="shared" si="21"/>
         <v>-0.69913953908177395</v>
       </c>
       <c r="N228" s="10">
-        <f>K228/L228</f>
+        <f t="shared" si="20"/>
         <v>1.23238</v>
       </c>
       <c r="O228" s="4">
@@ -16499,7 +16496,7 @@
         <v>310</v>
       </c>
       <c r="M229" s="10">
-        <f xml:space="preserve"> (L229 - K229)/(K229-J229)</f>
+        <f t="shared" si="21"/>
         <v>-0.42916944153743702</v>
       </c>
       <c r="N229" s="10"/>
@@ -16552,7 +16549,7 @@
         <v>110</v>
       </c>
       <c r="M230" s="10">
-        <f xml:space="preserve"> (L230 - K230)/(K230-J230)</f>
+        <f t="shared" si="21"/>
         <v>-1.5625879043600563</v>
       </c>
       <c r="N230" s="10">
@@ -16606,7 +16603,7 @@
         <v>80</v>
       </c>
       <c r="M231" s="10">
-        <f xml:space="preserve"> (L231 - K231)/(K231-J231)</f>
+        <f t="shared" si="21"/>
         <v>-0.12203687445127309</v>
       </c>
       <c r="N231" s="10"/>
@@ -16659,11 +16656,11 @@
         <v>35</v>
       </c>
       <c r="M232" s="10">
-        <f xml:space="preserve"> (L232 - K232)/(K232-J232)</f>
+        <f t="shared" si="21"/>
         <v>3.4052863436123357</v>
       </c>
       <c r="N232" s="10">
-        <f>K232/L232</f>
+        <f t="shared" ref="N232:N247" si="22">K232/L232</f>
         <v>0.77914285714285714</v>
       </c>
       <c r="O232" s="4">
@@ -16709,11 +16706,11 @@
       </c>
       <c r="L233" s="10"/>
       <c r="M233" s="10">
-        <f xml:space="preserve"> (L233 - K233)/(K233-J233)</f>
+        <f t="shared" si="21"/>
         <v>-1</v>
       </c>
       <c r="N233" s="10" t="e">
-        <f>K233/L233</f>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O233" s="4">
@@ -16764,11 +16761,11 @@
         <v>90</v>
       </c>
       <c r="M234" s="10">
-        <f xml:space="preserve"> (L234 - K234)/(K234-J234)</f>
+        <f t="shared" si="21"/>
         <v>-1.7007708479327261</v>
       </c>
       <c r="N234" s="10">
-        <f>K234/L234</f>
+        <f t="shared" si="22"/>
         <v>0.73033333333333339</v>
       </c>
       <c r="O234" s="4">
@@ -16818,11 +16815,11 @@
         <v>525</v>
       </c>
       <c r="M235" s="10">
-        <f xml:space="preserve"> (L235 - K235)/(K235-J235)</f>
+        <f t="shared" si="21"/>
         <v>-1.5725447932102925</v>
       </c>
       <c r="N235" s="10">
-        <f>K235/L235</f>
+        <f t="shared" si="22"/>
         <v>0.55531428571428576</v>
       </c>
       <c r="O235" s="4">
@@ -16872,11 +16869,11 @@
         <v>24</v>
       </c>
       <c r="M236" s="10">
-        <f xml:space="preserve"> (L236 - K236)/(K236-J236)</f>
+        <f t="shared" si="21"/>
         <v>-0.39637826961770634</v>
       </c>
       <c r="N236" s="10">
-        <f>K236/L236</f>
+        <f t="shared" si="22"/>
         <v>1.1641666666666668</v>
       </c>
       <c r="O236" s="4">
@@ -16930,11 +16927,11 @@
         <v>350</v>
       </c>
       <c r="M237" s="10">
-        <f xml:space="preserve"> (L237 - K237)/(K237-J237)</f>
+        <f t="shared" si="21"/>
         <v>31.028469750889652</v>
       </c>
       <c r="N237" s="10">
-        <f>K237/L237</f>
+        <f t="shared" si="22"/>
         <v>0.75088571428571427</v>
       </c>
       <c r="O237" s="4">
@@ -16987,11 +16984,11 @@
         <v>60</v>
       </c>
       <c r="M238" s="10">
-        <f xml:space="preserve"> (L238 - K238)/(K238-J238)</f>
+        <f t="shared" si="21"/>
         <v>-0.78392394122731202</v>
       </c>
       <c r="N238" s="10">
-        <f>K238/L238</f>
+        <f t="shared" si="22"/>
         <v>1.907</v>
       </c>
       <c r="O238" s="4">
@@ -17039,11 +17036,11 @@
         <v>30</v>
       </c>
       <c r="M239" s="11">
-        <f xml:space="preserve"> (L239 - K239)/(K239-J239)</f>
+        <f t="shared" si="21"/>
         <v>-0.92479789434104154</v>
       </c>
       <c r="N239" s="10">
-        <f>K239/L239</f>
+        <f t="shared" si="22"/>
         <v>2.6396666666666664</v>
       </c>
       <c r="O239" s="4">
@@ -17096,11 +17093,11 @@
         <v>80</v>
       </c>
       <c r="M240" s="10">
-        <f xml:space="preserve"> (L240 - K240)/(K240-J240)</f>
+        <f t="shared" si="21"/>
         <v>-0.80758129690205882</v>
       </c>
       <c r="N240" s="10">
-        <f>K240/L240</f>
+        <f t="shared" si="22"/>
         <v>1.5246249999999999</v>
       </c>
       <c r="O240" s="4">
@@ -17150,11 +17147,11 @@
         <v>42</v>
       </c>
       <c r="M241" s="10">
-        <f xml:space="preserve"> (L241 - K241)/(K241-J241)</f>
+        <f t="shared" si="21"/>
         <v>-0.80582524271844658</v>
       </c>
       <c r="N241" s="10">
-        <f>K241/L241</f>
+        <f t="shared" si="22"/>
         <v>1.3952380952380952</v>
       </c>
       <c r="O241" s="4">
@@ -17204,11 +17201,11 @@
         <v>50</v>
       </c>
       <c r="M242" s="10">
-        <f xml:space="preserve"> (L242 - K242)/(K242-J242)</f>
+        <f t="shared" si="21"/>
         <v>-0.20279023418036873</v>
       </c>
       <c r="N242" s="10">
-        <f>K242/L242</f>
+        <f t="shared" si="22"/>
         <v>1.0813999999999999</v>
       </c>
       <c r="O242" s="4">
@@ -17258,11 +17255,11 @@
         <v>120</v>
       </c>
       <c r="M243" s="10">
-        <f xml:space="preserve"> (L243 - K243)/(K243-J243)</f>
+        <f t="shared" si="21"/>
         <v>-2.4827995255041517</v>
       </c>
       <c r="N243" s="10">
-        <f>K243/L243</f>
+        <f t="shared" si="22"/>
         <v>0.65116666666666667</v>
       </c>
       <c r="O243" s="4">
@@ -17309,7 +17306,7 @@
       <c r="L244" s="10"/>
       <c r="M244" s="10"/>
       <c r="N244" s="10" t="e">
-        <f>K244/L244</f>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O244" s="4">
@@ -17359,11 +17356,11 @@
         <v>110</v>
       </c>
       <c r="M245" s="10">
-        <f xml:space="preserve"> (L245 - K245)/(K245-J245)</f>
+        <f t="shared" ref="M245:M257" si="23" xml:space="preserve"> (L245 - K245)/(K245-J245)</f>
         <v>-0.60180514998672674</v>
       </c>
       <c r="N245" s="10">
-        <f>K245/L245</f>
+        <f t="shared" si="22"/>
         <v>1.2060909090909089</v>
       </c>
       <c r="O245" s="4">
@@ -17414,11 +17411,11 @@
         <v>18</v>
       </c>
       <c r="M246" s="10">
-        <f xml:space="preserve"> (L246 - K246)/(K246-J246)</f>
+        <f t="shared" si="23"/>
         <v>0.56250000000000022</v>
       </c>
       <c r="N246" s="10">
-        <f>K246/L246</f>
+        <f t="shared" si="22"/>
         <v>0.77999999999999992</v>
       </c>
       <c r="O246" s="4">
@@ -17467,11 +17464,11 @@
         <v>10</v>
       </c>
       <c r="M247" s="10">
-        <f xml:space="preserve"> (L247 - K247)/(K247-J247)</f>
+        <f t="shared" si="23"/>
         <v>-0.8729281767955801</v>
       </c>
       <c r="N247" s="10">
-        <f>K247/L247</f>
+        <f t="shared" si="22"/>
         <v>2.58</v>
       </c>
       <c r="O247" s="4">
@@ -17522,7 +17519,7 @@
         <v>650</v>
       </c>
       <c r="M248" s="10">
-        <f xml:space="preserve"> (L248 - K248)/(K248-J248)</f>
+        <f t="shared" si="23"/>
         <v>-0.76225147849861807</v>
       </c>
       <c r="N248" s="10"/>
@@ -17575,11 +17572,11 @@
         <v>380</v>
       </c>
       <c r="M249" s="10">
-        <f xml:space="preserve"> (L249 - K249)/(K249-J249)</f>
+        <f t="shared" si="23"/>
         <v>-1.199501246882793</v>
       </c>
       <c r="N249" s="10">
-        <f>K249/L249</f>
+        <f t="shared" ref="N249:N257" si="24">K249/L249</f>
         <v>0.36710526315789471</v>
       </c>
       <c r="O249" s="4">
@@ -17632,11 +17629,11 @@
         <v>170</v>
       </c>
       <c r="M250" s="10">
-        <f xml:space="preserve"> (L250 - K250)/(K250-J250)</f>
+        <f t="shared" si="23"/>
         <v>-0.70588235294117652</v>
       </c>
       <c r="N250" s="10">
-        <f>K250/L250</f>
+        <f t="shared" si="24"/>
         <v>1.2117647058823529</v>
       </c>
       <c r="O250" s="4">
@@ -17686,11 +17683,11 @@
         <v>150</v>
       </c>
       <c r="M251" s="10">
-        <f xml:space="preserve"> (L251 - K251)/(K251-J251)</f>
+        <f t="shared" si="23"/>
         <v>-0.77694130768158365</v>
       </c>
       <c r="N251" s="10">
-        <f>K251/L251</f>
+        <f t="shared" si="24"/>
         <v>1.3715333333333333</v>
       </c>
       <c r="O251" s="4">
@@ -17743,11 +17740,11 @@
         <v>210</v>
       </c>
       <c r="M252" s="10">
-        <f xml:space="preserve"> (L252 - K252)/(K252-J252)</f>
+        <f t="shared" si="23"/>
         <v>-0.81261261261261264</v>
       </c>
       <c r="N252" s="10">
-        <f>K252/L252</f>
+        <f t="shared" si="24"/>
         <v>1.536904761904762</v>
       </c>
       <c r="O252" s="4">
@@ -17800,11 +17797,11 @@
         <v>49</v>
       </c>
       <c r="M253" s="10">
-        <f xml:space="preserve"> (L253 - K253)/(K253-J253)</f>
+        <f t="shared" si="23"/>
         <v>-0.88520591189553732</v>
       </c>
       <c r="N253" s="10">
-        <f>K253/L253</f>
+        <f t="shared" si="24"/>
         <v>2.2589795918367348</v>
       </c>
       <c r="O253" s="4">
@@ -17856,11 +17853,11 @@
         <v>125</v>
       </c>
       <c r="M254" s="10">
-        <f xml:space="preserve"> (L254 - K254)/(K254-J254)</f>
+        <f t="shared" si="23"/>
         <v>-1.547945205479452</v>
       </c>
       <c r="N254" s="10">
-        <f>K254/L254</f>
+        <f t="shared" si="24"/>
         <v>0.77400000000000002</v>
       </c>
       <c r="O254" s="4">
@@ -17913,11 +17910,11 @@
         <v>105</v>
       </c>
       <c r="M255" s="10">
-        <f xml:space="preserve"> (L255 - K255)/(K255-J255)</f>
+        <f t="shared" si="23"/>
         <v>-0.92910818091592229</v>
       </c>
       <c r="N255" s="10">
-        <f>K255/L255</f>
+        <f t="shared" si="24"/>
         <v>2.2481904761904761</v>
       </c>
       <c r="O255" s="4">
@@ -17969,11 +17966,11 @@
         <v>45</v>
       </c>
       <c r="M256" s="10">
-        <f xml:space="preserve"> (L256 - K256)/(K256-J256)</f>
+        <f t="shared" si="23"/>
         <v>-0.79748886188740375</v>
       </c>
       <c r="N256" s="10">
-        <f>K256/L256</f>
+        <f t="shared" si="24"/>
         <v>1.4375555555555555</v>
       </c>
       <c r="O256" s="4">
@@ -18026,11 +18023,11 @@
         <v>98</v>
       </c>
       <c r="M257" s="10">
-        <f xml:space="preserve"> (L257 - K257)/(K257-J257)</f>
+        <f t="shared" si="23"/>
         <v>-0.73255531242402139</v>
       </c>
       <c r="N257" s="10">
-        <f>K257/L257</f>
+        <f t="shared" si="24"/>
         <v>1.3074489795918367</v>
       </c>
       <c r="O257" s="4">
@@ -18104,7 +18101,7 @@
         <v>20</v>
       </c>
       <c r="M259" s="10">
-        <f xml:space="preserve"> (L259 - K259)/(K259-J259)</f>
+        <f t="shared" ref="M259:M267" si="25" xml:space="preserve"> (L259 - K259)/(K259-J259)</f>
         <v>-0.91405242801890851</v>
       </c>
       <c r="N259" s="10"/>
@@ -18157,11 +18154,11 @@
         <v>400</v>
       </c>
       <c r="M260" s="10">
-        <f xml:space="preserve"> (L260 - K260)/(K260-J260)</f>
+        <f t="shared" si="25"/>
         <v>-0.90673207856889704</v>
       </c>
       <c r="N260" s="10">
-        <f>K260/L260</f>
+        <f t="shared" ref="N260:N265" si="26">K260/L260</f>
         <v>2.2152250000000002</v>
       </c>
       <c r="O260" s="4">
@@ -18214,11 +18211,11 @@
         <v>300</v>
       </c>
       <c r="M261" s="10">
-        <f xml:space="preserve"> (L261 - K261)/(K261-J261)</f>
+        <f t="shared" si="25"/>
         <v>-0.5761172338621775</v>
       </c>
       <c r="N261" s="10">
-        <f>K261/L261</f>
+        <f t="shared" si="26"/>
         <v>1.1585666666666667</v>
       </c>
       <c r="O261" s="4">
@@ -18270,11 +18267,11 @@
         <v>60</v>
       </c>
       <c r="M262" s="10">
-        <f xml:space="preserve"> (L262 - K262)/(K262-J262)</f>
+        <f t="shared" si="25"/>
         <v>-2.093247588424437</v>
       </c>
       <c r="N262" s="10">
-        <f>K262/L262</f>
+        <f t="shared" si="26"/>
         <v>0.45749999999999996</v>
       </c>
       <c r="O262" s="4">
@@ -18324,11 +18321,11 @@
         <v>120</v>
       </c>
       <c r="M263" s="10">
-        <f xml:space="preserve"> (L263 - K263)/(K263-J263)</f>
+        <f t="shared" si="25"/>
         <v>-1.7659900421294523</v>
       </c>
       <c r="N263" s="10">
-        <f>K263/L263</f>
+        <f t="shared" si="26"/>
         <v>0.23150000000000001</v>
       </c>
       <c r="O263" s="4">
@@ -18381,11 +18378,11 @@
         <v>26</v>
       </c>
       <c r="M264" s="10">
-        <f xml:space="preserve"> (L264 - K264)/(K264-J264)</f>
+        <f t="shared" si="25"/>
         <v>17.749999999999982</v>
       </c>
       <c r="N264" s="10">
-        <f>K264/L264</f>
+        <f t="shared" si="26"/>
         <v>0.89076923076923076</v>
       </c>
       <c r="O264" s="4">
@@ -18437,11 +18434,11 @@
         <v>35</v>
       </c>
       <c r="M265" s="10">
-        <f xml:space="preserve"> (L265 - K265)/(K265-J265)</f>
+        <f t="shared" si="25"/>
         <v>-8.8699878493317175E-2</v>
       </c>
       <c r="N265" s="10">
-        <f>K265/L265</f>
+        <f t="shared" si="26"/>
         <v>1.0417142857142858</v>
       </c>
       <c r="O265" s="4">
@@ -18491,7 +18488,7 @@
         <v>120</v>
       </c>
       <c r="M266" s="10">
-        <f xml:space="preserve"> (L266 - K266)/(K266-J266)</f>
+        <f t="shared" si="25"/>
         <v>-2.8990775908844268</v>
       </c>
       <c r="N266" s="10">
@@ -18545,11 +18542,11 @@
         <v>850</v>
       </c>
       <c r="M267" s="10">
-        <f xml:space="preserve"> (L267 - K267)/(K267-J267)</f>
+        <f t="shared" si="25"/>
         <v>-0.65746386243748722</v>
       </c>
       <c r="N267" s="10">
-        <f>K267/L267</f>
+        <f t="shared" ref="N267:N272" si="27">K267/L267</f>
         <v>1.2258117647058824</v>
       </c>
       <c r="O267" s="4">
@@ -18599,7 +18596,7 @@
       <c r="L268" s="10"/>
       <c r="M268" s="10"/>
       <c r="N268" s="10" t="e">
-        <f>K268/L268</f>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O268" s="4">
@@ -18649,11 +18646,11 @@
         <v>68.19</v>
       </c>
       <c r="M269" s="10">
-        <f xml:space="preserve"> (L269 - K269)/(K269-J269)</f>
+        <f t="shared" ref="M269:M279" si="28" xml:space="preserve"> (L269 - K269)/(K269-J269)</f>
         <v>-0.21269296740994992</v>
       </c>
       <c r="N269" s="10">
-        <f>K269/L269</f>
+        <f t="shared" si="27"/>
         <v>1.0181844845285233</v>
       </c>
       <c r="O269" s="4">
@@ -18704,11 +18701,11 @@
         <v>52.5</v>
       </c>
       <c r="M270" s="10">
-        <f xml:space="preserve"> (L270 - K270)/(K270-J270)</f>
+        <f t="shared" si="28"/>
         <v>-0.87268097489996355</v>
       </c>
       <c r="N270" s="10">
-        <f>K270/L270</f>
+        <f t="shared" si="27"/>
         <v>1.4569523809523808</v>
       </c>
       <c r="O270" s="4">
@@ -18758,11 +18755,11 @@
         <v>45</v>
       </c>
       <c r="M271" s="10">
-        <f xml:space="preserve"> (L271 - K271)/(K271-J271)</f>
+        <f t="shared" si="28"/>
         <v>-0.71781472684085512</v>
       </c>
       <c r="N271" s="10">
-        <f>K271/L271</f>
+        <f t="shared" si="27"/>
         <v>1.3357777777777777</v>
       </c>
       <c r="O271" s="4">
@@ -18814,11 +18811,11 @@
         <v>42</v>
       </c>
       <c r="M272" s="10">
-        <f xml:space="preserve"> (L272 - K272)/(K272-J272)</f>
+        <f t="shared" si="28"/>
         <v>-0.73175965665236054</v>
       </c>
       <c r="N272" s="10">
-        <f>K272/L272</f>
+        <f t="shared" si="27"/>
         <v>1.3247619047619048</v>
       </c>
       <c r="O272" s="4">
@@ -18866,7 +18863,7 @@
         <v>410</v>
       </c>
       <c r="M273" s="10">
-        <f xml:space="preserve"> (L273 - K273)/(K273-J273)</f>
+        <f t="shared" si="28"/>
         <v>-0.81827540061078141</v>
       </c>
       <c r="N273" s="10">
@@ -18920,7 +18917,7 @@
         <v>44</v>
       </c>
       <c r="M274" s="10">
-        <f xml:space="preserve"> (L274 - K274)/(K274-J274)</f>
+        <f t="shared" si="28"/>
         <v>-0.73827655310621243</v>
       </c>
       <c r="N274" s="10">
@@ -18976,7 +18973,7 @@
         <v>140</v>
       </c>
       <c r="M275" s="11">
-        <f xml:space="preserve"> (L275 - K275)/(K275-J275)</f>
+        <f t="shared" si="28"/>
         <v>-0.7122026093630085</v>
       </c>
       <c r="N275" s="10">
@@ -19031,7 +19028,7 @@
         <v>95</v>
       </c>
       <c r="M276" s="10">
-        <f xml:space="preserve"> (L276 - K276)/(K276-J276)</f>
+        <f t="shared" si="28"/>
         <v>3.1958041958041967</v>
       </c>
       <c r="N276" s="10"/>
@@ -19083,11 +19080,11 @@
         <v>100</v>
       </c>
       <c r="M277" s="10">
-        <f xml:space="preserve"> (L277 - K277)/(K277-J277)</f>
+        <f t="shared" si="28"/>
         <v>-0.4262033790245458</v>
       </c>
       <c r="N277" s="10">
-        <f>K277/L277</f>
+        <f t="shared" ref="N277:N301" si="29">K277/L277</f>
         <v>1.1337000000000002</v>
       </c>
       <c r="O277" s="4">
@@ -19137,11 +19134,11 @@
         <v>75.239999999999995</v>
       </c>
       <c r="M278" s="10">
-        <f xml:space="preserve"> (L278 - K278)/(K278-J278)</f>
+        <f t="shared" si="28"/>
         <v>-0.76569624693090166</v>
       </c>
       <c r="N278" s="10">
-        <f>K278/L278</f>
+        <f t="shared" si="29"/>
         <v>1.2901382243487507</v>
       </c>
       <c r="O278" s="4">
@@ -19195,11 +19192,11 @@
         <v>34</v>
       </c>
       <c r="M279" s="10">
-        <f xml:space="preserve"> (L279 - K279)/(K279-J279)</f>
+        <f t="shared" si="28"/>
         <v>-0.91670644391408129</v>
       </c>
       <c r="N279" s="10">
-        <f>K279/L279</f>
+        <f t="shared" si="29"/>
         <v>2.1297058823529409</v>
       </c>
       <c r="O279" s="4">
@@ -19244,7 +19241,7 @@
       <c r="L280" s="10"/>
       <c r="M280" s="10"/>
       <c r="N280" s="10" t="e">
-        <f>K280/L280</f>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O280" s="28">
@@ -19294,11 +19291,11 @@
         <v>180</v>
       </c>
       <c r="M281" s="10">
-        <f xml:space="preserve"> (L281 - K281)/(K281-J281)</f>
+        <f t="shared" ref="M281:M293" si="30" xml:space="preserve"> (L281 - K281)/(K281-J281)</f>
         <v>-0.54531676265535023</v>
       </c>
       <c r="N281" s="10">
-        <f>K281/L281</f>
+        <f t="shared" si="29"/>
         <v>1.0999444444444444</v>
       </c>
       <c r="O281" s="4">
@@ -19348,11 +19345,11 @@
         <v>100</v>
       </c>
       <c r="M282" s="10">
-        <f xml:space="preserve"> (L282 - K282)/(K282-J282)</f>
+        <f t="shared" si="30"/>
         <v>-2.7421602787456445</v>
       </c>
       <c r="N282" s="10">
-        <f>K282/L282</f>
+        <f t="shared" si="29"/>
         <v>0.52780000000000005</v>
       </c>
       <c r="O282" s="4">
@@ -19402,11 +19399,11 @@
         <v>85</v>
       </c>
       <c r="M283" s="10">
-        <f xml:space="preserve"> (L283 - K283)/(K283-J283)</f>
+        <f t="shared" si="30"/>
         <v>0.23927550047664503</v>
       </c>
       <c r="N283" s="10">
-        <f>K283/L283</f>
+        <f t="shared" si="29"/>
         <v>0.97047058823529408</v>
       </c>
       <c r="O283" s="4">
@@ -19456,11 +19453,11 @@
         <v>110</v>
       </c>
       <c r="M284" s="10">
-        <f xml:space="preserve"> (L284 - K284)/(K284-J284)</f>
+        <f t="shared" si="30"/>
         <v>-0.75675018243736325</v>
       </c>
       <c r="N284" s="10">
-        <f>K284/L284</f>
+        <f t="shared" si="29"/>
         <v>1.2828181818181819</v>
       </c>
       <c r="O284" s="4">
@@ -19510,11 +19507,11 @@
         <v>250</v>
       </c>
       <c r="M285" s="10">
-        <f xml:space="preserve"> (L285 - K285)/(K285-J285)</f>
+        <f t="shared" si="30"/>
         <v>-1.9398496240601504</v>
       </c>
       <c r="N285" s="10">
-        <f>K285/L285</f>
+        <f t="shared" si="29"/>
         <v>0.83487999999999996</v>
       </c>
       <c r="O285" s="4">
@@ -19564,11 +19561,11 @@
         <v>92</v>
       </c>
       <c r="M286" s="10">
-        <f xml:space="preserve"> (L286 - K286)/(K286-J286)</f>
+        <f t="shared" si="30"/>
         <v>-1.8888888888888888</v>
       </c>
       <c r="N286" s="10">
-        <f>K286/L286</f>
+        <f t="shared" si="29"/>
         <v>0.49184782608695654</v>
       </c>
       <c r="O286" s="4">
@@ -19620,11 +19617,11 @@
         <v>125</v>
       </c>
       <c r="M287" s="10">
-        <f xml:space="preserve"> (L287 - K287)/(K287-J287)</f>
+        <f t="shared" si="30"/>
         <v>-1.6610841780520054</v>
       </c>
       <c r="N287" s="10">
-        <f>K287/L287</f>
+        <f t="shared" si="29"/>
         <v>0.69847999999999999</v>
       </c>
       <c r="O287" s="4">
@@ -19674,11 +19671,11 @@
         <v>147.32</v>
       </c>
       <c r="M288" s="10">
-        <f xml:space="preserve"> (L288 - K288)/(K288-J288)</f>
+        <f t="shared" si="30"/>
         <v>-0.78362797847809396</v>
       </c>
       <c r="N288" s="10">
-        <f>K288/L288</f>
+        <f t="shared" si="29"/>
         <v>1.4152185718164541</v>
       </c>
       <c r="O288" s="4">
@@ -19730,11 +19727,11 @@
         <v>14</v>
       </c>
       <c r="M289" s="10">
-        <f xml:space="preserve"> (L289 - K289)/(K289-J289)</f>
+        <f t="shared" si="30"/>
         <v>-0.59158415841584155</v>
       </c>
       <c r="N289" s="10">
-        <f>K289/L289</f>
+        <f t="shared" si="29"/>
         <v>1.3414285714285714</v>
       </c>
       <c r="O289" s="4">
@@ -19784,11 +19781,11 @@
         <v>90</v>
       </c>
       <c r="M290" s="10">
-        <f xml:space="preserve"> (L290 - K290)/(K290-J290)</f>
+        <f t="shared" si="30"/>
         <v>-0.64028776978417268</v>
       </c>
       <c r="N290" s="10">
-        <f>K290/L290</f>
+        <f t="shared" si="29"/>
         <v>1.2966666666666666</v>
       </c>
       <c r="O290" s="4">
@@ -19838,11 +19835,11 @@
         <v>12</v>
       </c>
       <c r="M291" s="10">
-        <f xml:space="preserve"> (L291 - K291)/(K291-J291)</f>
+        <f t="shared" si="30"/>
         <v>-7.7490774907749374E-2</v>
       </c>
       <c r="N291" s="10">
-        <f>K291/L291</f>
+        <f t="shared" si="29"/>
         <v>1.0175000000000001</v>
       </c>
       <c r="O291" s="4">
@@ -19895,11 +19892,11 @@
         <v>110</v>
       </c>
       <c r="M292" s="10">
-        <f xml:space="preserve"> (L292 - K292)/(K292-J292)</f>
+        <f t="shared" si="30"/>
         <v>-1.3610108303249098</v>
       </c>
       <c r="N292" s="10">
-        <f>K292/L292</f>
+        <f t="shared" si="29"/>
         <v>0.623</v>
       </c>
       <c r="O292" s="4">
@@ -19949,11 +19946,11 @@
         <v>140</v>
       </c>
       <c r="M293" s="10">
-        <f xml:space="preserve"> (L293 - K293)/(K293-J293)</f>
+        <f t="shared" si="30"/>
         <v>-7.4102564102564008</v>
       </c>
       <c r="N293" s="10">
-        <f>K293/L293</f>
+        <f t="shared" si="29"/>
         <v>0.91742857142857137</v>
       </c>
       <c r="O293" s="4">
@@ -20002,7 +19999,7 @@
       <c r="L294" s="10"/>
       <c r="M294" s="10"/>
       <c r="N294" s="10" t="e">
-        <f>K294/L294</f>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O294" s="4">
@@ -20049,11 +20046,11 @@
         <v>85</v>
       </c>
       <c r="M295" s="10">
-        <f xml:space="preserve"> (L295 - K295)/(K295-J295)</f>
+        <f t="shared" ref="M295:M320" si="31" xml:space="preserve"> (L295 - K295)/(K295-J295)</f>
         <v>22.809523809523714</v>
       </c>
       <c r="N295" s="10">
-        <f>K295/L295</f>
+        <f t="shared" si="29"/>
         <v>0.88729411764705879</v>
       </c>
       <c r="O295" s="4">
@@ -20105,11 +20102,11 @@
         <v>400</v>
       </c>
       <c r="M296" s="10">
-        <f xml:space="preserve"> (L296 - K296)/(K296-J296)</f>
+        <f t="shared" si="31"/>
         <v>-0.15426251691474974</v>
       </c>
       <c r="N296" s="10">
-        <f>K296/L296</f>
+        <f t="shared" si="29"/>
         <v>1.0227999999999999</v>
       </c>
       <c r="O296" s="4">
@@ -20159,11 +20156,11 @@
         <v>110</v>
       </c>
       <c r="M297" s="10">
-        <f xml:space="preserve"> (L297 - K297)/(K297-J297)</f>
+        <f t="shared" si="31"/>
         <v>-1.5274725274725274</v>
       </c>
       <c r="N297" s="10">
-        <f>K297/L297</f>
+        <f t="shared" si="29"/>
         <v>0.68409090909090908</v>
       </c>
       <c r="O297" s="4">
@@ -20213,11 +20210,11 @@
         <v>170</v>
       </c>
       <c r="M298" s="10">
-        <f xml:space="preserve"> (L298 - K298)/(K298-J298)</f>
+        <f t="shared" si="31"/>
         <v>-0.60497728619395608</v>
       </c>
       <c r="N298" s="10">
-        <f>K298/L298</f>
+        <f t="shared" si="29"/>
         <v>1.1801764705882352</v>
       </c>
       <c r="O298" s="4">
@@ -20268,11 +20265,11 @@
         <v>45</v>
       </c>
       <c r="M299" s="10">
-        <f xml:space="preserve"> (L299 - K299)/(K299-J299)</f>
+        <f t="shared" si="31"/>
         <v>9.6892138939671163E-2</v>
       </c>
       <c r="N299" s="10">
-        <f>K299/L299</f>
+        <f t="shared" si="29"/>
         <v>0.97644444444444445</v>
       </c>
       <c r="O299" s="4">
@@ -20322,11 +20319,11 @@
         <v>40</v>
       </c>
       <c r="M300" s="10">
-        <f xml:space="preserve"> (L300 - K300)/(K300-J300)</f>
+        <f t="shared" si="31"/>
         <v>-0.59657085224407458</v>
       </c>
       <c r="N300" s="10">
-        <f>K300/L300</f>
+        <f t="shared" si="29"/>
         <v>1.29575</v>
       </c>
       <c r="O300" s="4">
@@ -20376,11 +20373,11 @@
         <v>42.5</v>
       </c>
       <c r="M301" s="10">
-        <f xml:space="preserve"> (L301 - K301)/(K301-J301)</f>
+        <f t="shared" si="31"/>
         <v>-4.395061728395067</v>
       </c>
       <c r="N301" s="10">
-        <f>K301/L301</f>
+        <f t="shared" si="29"/>
         <v>0.83247058823529418</v>
       </c>
       <c r="O301" s="4">
@@ -20431,7 +20428,7 @@
         <v>24</v>
       </c>
       <c r="M302" s="10">
-        <f xml:space="preserve"> (L302 - K302)/(K302-J302)</f>
+        <f t="shared" si="31"/>
         <v>-31.769230769231005</v>
       </c>
       <c r="N302" s="10"/>
@@ -20484,7 +20481,7 @@
         <v>200</v>
       </c>
       <c r="M303" s="11">
-        <f xml:space="preserve"> (L303 - K303)/(K303-J303)</f>
+        <f t="shared" si="31"/>
         <v>-0.74257765574051837</v>
       </c>
       <c r="N303" s="10">
@@ -20538,7 +20535,7 @@
         <v>70</v>
       </c>
       <c r="M304" s="10">
-        <f xml:space="preserve"> (L304 - K304)/(K304-J304)</f>
+        <f t="shared" si="31"/>
         <v>-8.9253187613843293E-2</v>
       </c>
       <c r="N304" s="10">
@@ -20592,7 +20589,7 @@
         <v>25</v>
       </c>
       <c r="M305" s="10">
-        <f xml:space="preserve"> (L305 - K305)/(K305-J305)</f>
+        <f t="shared" si="31"/>
         <v>-0.22135706340378183</v>
       </c>
       <c r="N305" s="10"/>
@@ -20643,7 +20640,7 @@
         <v>85</v>
       </c>
       <c r="M306" s="10">
-        <f xml:space="preserve"> (L306 - K306)/(K306-J306)</f>
+        <f t="shared" si="31"/>
         <v>-0.8672639787622366</v>
       </c>
       <c r="N306" s="10">
@@ -20699,7 +20696,7 @@
         <v>72.5</v>
       </c>
       <c r="M307" s="10">
-        <f xml:space="preserve"> (L307 - K307)/(K307-J307)</f>
+        <f t="shared" si="31"/>
         <v>-0.46004319654427661</v>
       </c>
       <c r="N307" s="10">
@@ -20755,7 +20752,7 @@
         <v>180</v>
       </c>
       <c r="M308" s="10">
-        <f xml:space="preserve"> (L308 - K308)/(K308-J308)</f>
+        <f t="shared" si="31"/>
         <v>-6.1020408163265243</v>
       </c>
       <c r="N308" s="10"/>
@@ -20806,7 +20803,7 @@
         <v>68</v>
       </c>
       <c r="M309" s="10">
-        <f xml:space="preserve"> (L309 - K309)/(K309-J309)</f>
+        <f t="shared" si="31"/>
         <v>0.35658914728682262</v>
       </c>
       <c r="N309" s="10">
@@ -20860,7 +20857,7 @@
         <v>80</v>
       </c>
       <c r="M310" s="10">
-        <f xml:space="preserve"> (L310 - K310)/(K310-J310)</f>
+        <f t="shared" si="31"/>
         <v>-1.8389261744966441</v>
       </c>
       <c r="N310" s="10">
@@ -20914,7 +20911,7 @@
         <v>60</v>
       </c>
       <c r="M311" s="10">
-        <f xml:space="preserve"> (L311 - K311)/(K311-J311)</f>
+        <f t="shared" si="31"/>
         <v>-0.93302973479774975</v>
       </c>
       <c r="N311" s="10"/>
@@ -20965,7 +20962,7 @@
         <v>3</v>
       </c>
       <c r="M312" s="10">
-        <f xml:space="preserve"> (L312 - K312)/(K312-J312)</f>
+        <f t="shared" si="31"/>
         <v>-2.6506276150627617</v>
       </c>
       <c r="N312" s="10">
@@ -21021,7 +21018,7 @@
         <v>100</v>
       </c>
       <c r="M313" s="10">
-        <f xml:space="preserve"> (L313 - K313)/(K313-J313)</f>
+        <f t="shared" si="31"/>
         <v>-1.329792615073343</v>
       </c>
       <c r="N313" s="10">
@@ -21078,7 +21075,7 @@
         <v>250</v>
       </c>
       <c r="M314" s="10">
-        <f xml:space="preserve"> (L314 - K314)/(K314-J314)</f>
+        <f t="shared" si="31"/>
         <v>-0.93403693931398413</v>
       </c>
       <c r="N314" s="10"/>
@@ -21132,11 +21129,11 @@
         <v>450</v>
       </c>
       <c r="M315" s="10">
-        <f xml:space="preserve"> (L315 - K315)/(K315-J315)</f>
+        <f t="shared" si="31"/>
         <v>-0.73891702783144486</v>
       </c>
       <c r="N315" s="10">
-        <f>K315/L315</f>
+        <f t="shared" ref="N315:N338" si="32">K315/L315</f>
         <v>1.3144666666666667</v>
       </c>
       <c r="O315" s="4">
@@ -21188,11 +21185,11 @@
         <v>65</v>
       </c>
       <c r="M316" s="10">
-        <f xml:space="preserve"> (L316 - K316)/(K316-J316)</f>
+        <f t="shared" si="31"/>
         <v>-4.0213675213675266</v>
       </c>
       <c r="N316" s="10">
-        <f>K316/L316</f>
+        <f t="shared" si="32"/>
         <v>0.85523076923076924</v>
       </c>
       <c r="O316" s="4">
@@ -21242,11 +21239,11 @@
         <v>800</v>
       </c>
       <c r="M317" s="10">
-        <f xml:space="preserve"> (L317 - K317)/(K317-J317)</f>
+        <f t="shared" si="31"/>
         <v>-0.57289597881564058</v>
       </c>
       <c r="N317" s="10">
-        <f>K317/L317</f>
+        <f t="shared" si="32"/>
         <v>1.3353375000000001</v>
       </c>
       <c r="O317" s="4">
@@ -21296,11 +21293,11 @@
         <v>11</v>
       </c>
       <c r="M318" s="11">
-        <f xml:space="preserve"> (L318 - K318)/(K318-J318)</f>
+        <f t="shared" si="31"/>
         <v>-0.88445984979780468</v>
       </c>
       <c r="N318" s="10">
-        <f>K318/L318</f>
+        <f t="shared" si="32"/>
         <v>2.3918181818181816</v>
       </c>
       <c r="O318" s="4">
@@ -21352,11 +21349,11 @@
         <v>50</v>
       </c>
       <c r="M319" s="10">
-        <f xml:space="preserve"> (L319 - K319)/(K319-J319)</f>
+        <f t="shared" si="31"/>
         <v>-0.85130111524163565</v>
       </c>
       <c r="N319" s="10">
-        <f>K319/L319</f>
+        <f t="shared" si="32"/>
         <v>1.9159999999999999</v>
       </c>
       <c r="O319" s="4">
@@ -21406,11 +21403,11 @@
         <v>16</v>
       </c>
       <c r="M320" s="10">
-        <f xml:space="preserve"> (L320 - K320)/(K320-J320)</f>
+        <f t="shared" si="31"/>
         <v>-0.80601357904946647</v>
       </c>
       <c r="N320" s="10">
-        <f>K320/L320</f>
+        <f t="shared" si="32"/>
         <v>1.5193749999999999</v>
       </c>
       <c r="O320" s="4">
@@ -21459,7 +21456,7 @@
       <c r="L321" s="10"/>
       <c r="M321" s="10"/>
       <c r="N321" s="10" t="e">
-        <f>K321/L321</f>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O321" s="4">
@@ -21509,11 +21506,11 @@
         <v>100</v>
       </c>
       <c r="M322" s="10">
-        <f xml:space="preserve"> (L322 - K322)/(K322-J322)</f>
+        <f t="shared" ref="M322:M333" si="33" xml:space="preserve"> (L322 - K322)/(K322-J322)</f>
         <v>-0.70396684428655998</v>
       </c>
       <c r="N322" s="10">
-        <f>K322/L322</f>
+        <f t="shared" si="32"/>
         <v>1.3566999999999998</v>
       </c>
       <c r="O322" s="4">
@@ -21566,11 +21563,11 @@
         <v>85</v>
       </c>
       <c r="M323" s="10">
-        <f xml:space="preserve"> (L323 - K323)/(K323-J323)</f>
+        <f t="shared" si="33"/>
         <v>-0.78448275862068972</v>
       </c>
       <c r="N323" s="10">
-        <f>K323/L323</f>
+        <f t="shared" si="32"/>
         <v>1.5995294117647059</v>
       </c>
       <c r="O323" s="4">
@@ -21620,11 +21617,11 @@
         <v>55</v>
       </c>
       <c r="M324" s="10">
-        <f xml:space="preserve"> (L324 - K324)/(K324-J324)</f>
+        <f t="shared" si="33"/>
         <v>-1.4697286012526096</v>
       </c>
       <c r="N324" s="10">
-        <f>K324/L324</f>
+        <f t="shared" si="32"/>
         <v>0.48799999999999999</v>
       </c>
       <c r="O324" s="4">
@@ -21675,11 +21672,11 @@
         <v>114</v>
       </c>
       <c r="M325" s="10">
-        <f xml:space="preserve"> (L325 - K325)/(K325-J325)</f>
+        <f t="shared" si="33"/>
         <v>-0.63682973723563341</v>
       </c>
       <c r="N325" s="10">
-        <f>K325/L325</f>
+        <f t="shared" si="32"/>
         <v>1.2614912280701756</v>
       </c>
       <c r="O325" s="4">
@@ -21729,11 +21726,11 @@
         <v>100</v>
       </c>
       <c r="M326" s="10">
-        <f xml:space="preserve"> (L326 - K326)/(K326-J326)</f>
+        <f t="shared" si="33"/>
         <v>-0.90932994831807057</v>
       </c>
       <c r="N326" s="10">
-        <f>K326/L326</f>
+        <f t="shared" si="32"/>
         <v>3.0057999999999998</v>
       </c>
       <c r="O326" s="4">
@@ -21785,11 +21782,11 @@
         <v>220</v>
       </c>
       <c r="M327" s="10">
-        <f xml:space="preserve"> (L327 - K327)/(K327-J327)</f>
+        <f t="shared" si="33"/>
         <v>-1.3093580819798918</v>
       </c>
       <c r="N327" s="10">
-        <f>K327/L327</f>
+        <f t="shared" si="32"/>
         <v>0.61522727272727273</v>
       </c>
       <c r="O327" s="4">
@@ -21841,11 +21838,11 @@
         <v>480</v>
       </c>
       <c r="M328" s="10">
-        <f xml:space="preserve"> (L328 - K328)/(K328-J328)</f>
+        <f t="shared" si="33"/>
         <v>-0.85015920584379101</v>
       </c>
       <c r="N328" s="10">
-        <f>K328/L328</f>
+        <f t="shared" si="32"/>
         <v>1.4728125000000001</v>
       </c>
       <c r="O328" s="4">
@@ -21895,11 +21892,11 @@
         <v>60</v>
       </c>
       <c r="M329" s="10">
-        <f xml:space="preserve"> (L329 - K329)/(K329-J329)</f>
+        <f t="shared" si="33"/>
         <v>-0.76019184652278182</v>
       </c>
       <c r="N329" s="10">
-        <f>K329/L329</f>
+        <f t="shared" si="32"/>
         <v>1.5283333333333333</v>
       </c>
       <c r="O329" s="4">
@@ -21951,11 +21948,11 @@
         <v>8.5</v>
       </c>
       <c r="M330" s="10">
-        <f xml:space="preserve"> (L330 - K330)/(K330-J330)</f>
+        <f t="shared" si="33"/>
         <v>-0.8493975903614458</v>
       </c>
       <c r="N330" s="10">
-        <f>K330/L330</f>
+        <f t="shared" si="32"/>
         <v>1.9952941176470589</v>
       </c>
       <c r="O330" s="4">
@@ -22008,11 +22005,11 @@
         <v>100</v>
       </c>
       <c r="M331" s="10">
-        <f xml:space="preserve"> (L331 - K331)/(K331-J331)</f>
+        <f t="shared" si="33"/>
         <v>0.20012001200120019</v>
       </c>
       <c r="N331" s="10">
-        <f>K331/L331</f>
+        <f t="shared" si="32"/>
         <v>0.93330000000000002</v>
       </c>
       <c r="O331" s="4">
@@ -22062,11 +22059,11 @@
         <v>2.5</v>
       </c>
       <c r="M332" s="10">
-        <f xml:space="preserve"> (L332 - K332)/(K332-J332)</f>
+        <f t="shared" si="33"/>
         <v>-0.88636363636363635</v>
       </c>
       <c r="N332" s="10">
-        <f>K332/L332</f>
+        <f t="shared" si="32"/>
         <v>2.56</v>
       </c>
       <c r="O332" s="4">
@@ -22116,11 +22113,11 @@
         <v>375</v>
       </c>
       <c r="M333" s="10">
-        <f xml:space="preserve"> (L333 - K333)/(K333-J333)</f>
+        <f t="shared" si="33"/>
         <v>-0.9461021041738531</v>
       </c>
       <c r="N333" s="10">
-        <f>K333/L333</f>
+        <f t="shared" si="32"/>
         <v>2.1702400000000002</v>
       </c>
       <c r="O333" s="4">
@@ -22167,7 +22164,7 @@
       <c r="L334" s="10"/>
       <c r="M334" s="10"/>
       <c r="N334" s="10" t="e">
-        <f>K334/L334</f>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O334" s="4">
@@ -22214,7 +22211,7 @@
       <c r="L335" s="10"/>
       <c r="M335" s="10"/>
       <c r="N335" s="10" t="e">
-        <f>K335/L335</f>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O335" s="4">
@@ -22268,7 +22265,7 @@
         <v>3.3010752688172058</v>
       </c>
       <c r="N336" s="10">
-        <f>K336/L336</f>
+        <f t="shared" si="32"/>
         <v>0.78071428571428569</v>
       </c>
       <c r="O336" s="4">
@@ -22324,7 +22321,7 @@
         <v>-0.7437879624516841</v>
       </c>
       <c r="N337" s="10">
-        <f>K337/L337</f>
+        <f t="shared" si="32"/>
         <v>1.2993333333333332</v>
       </c>
       <c r="O337" s="4">
@@ -22373,7 +22370,7 @@
       <c r="L338" s="10"/>
       <c r="M338" s="10"/>
       <c r="N338" s="10" t="e">
-        <f>K338/L338</f>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O338" s="4">
@@ -22426,7 +22423,7 @@
         <v>178</v>
       </c>
       <c r="M339" s="10">
-        <f xml:space="preserve"> (L339 - K339)/(K339-J339)</f>
+        <f t="shared" ref="M339:M357" si="34" xml:space="preserve"> (L339 - K339)/(K339-J339)</f>
         <v>1.0452099031216349</v>
       </c>
       <c r="N339" s="10"/>
@@ -22484,7 +22481,7 @@
         <v>73</v>
       </c>
       <c r="M340" s="10">
-        <f xml:space="preserve"> (L340 - K340)/(K340-J340)</f>
+        <f t="shared" si="34"/>
         <v>-0.85331866519985333</v>
       </c>
       <c r="N340" s="10">
@@ -22541,7 +22538,7 @@
         <v>102</v>
       </c>
       <c r="M341" s="10">
-        <f xml:space="preserve"> (L341 - K341)/(K341-J341)</f>
+        <f t="shared" si="34"/>
         <v>-0.96436570963143964</v>
       </c>
       <c r="N341" s="10">
@@ -22596,7 +22593,7 @@
         <v>200</v>
       </c>
       <c r="M342" s="10">
-        <f xml:space="preserve"> (L342 - K342)/(K342-J342)</f>
+        <f t="shared" si="34"/>
         <v>-0.30224444702872433</v>
       </c>
       <c r="N342" s="10"/>
@@ -22649,11 +22646,11 @@
         <v>12</v>
       </c>
       <c r="M343" s="10">
-        <f xml:space="preserve"> (L343 - K343)/(K343-J343)</f>
+        <f t="shared" si="34"/>
         <v>-0.97819450501526384</v>
       </c>
       <c r="N343" s="10">
-        <f>K343/L343</f>
+        <f t="shared" ref="N343:N351" si="35">K343/L343</f>
         <v>23.430000000000003</v>
       </c>
       <c r="O343" s="4">
@@ -22704,11 +22701,11 @@
         <v>85</v>
       </c>
       <c r="M344" s="10">
-        <f xml:space="preserve"> (L344 - K344)/(K344-J344)</f>
+        <f t="shared" si="34"/>
         <v>-0.75759534583063992</v>
       </c>
       <c r="N344" s="10">
-        <f>K344/L344</f>
+        <f t="shared" si="35"/>
         <v>1.5515294117647058</v>
       </c>
       <c r="O344" s="4">
@@ -22758,11 +22755,11 @@
         <v>108</v>
       </c>
       <c r="M345" s="10">
-        <f xml:space="preserve"> (L345 - K345)/(K345-J345)</f>
+        <f t="shared" si="34"/>
         <v>0.29846938775510162</v>
       </c>
       <c r="N345" s="10">
-        <f>K345/L345</f>
+        <f t="shared" si="35"/>
         <v>0.94583333333333341</v>
       </c>
       <c r="O345" s="4">
@@ -22815,11 +22812,11 @@
         <v>40</v>
       </c>
       <c r="M346" s="10">
-        <f xml:space="preserve"> (L346 - K346)/(K346-J346)</f>
+        <f t="shared" si="34"/>
         <v>-2.2482893450635089E-2</v>
       </c>
       <c r="N346" s="10">
-        <f>K346/L346</f>
+        <f t="shared" si="35"/>
         <v>1.0057499999999999</v>
       </c>
       <c r="O346" s="4">
@@ -22872,11 +22869,11 @@
         <v>320</v>
       </c>
       <c r="M347" s="10">
-        <f xml:space="preserve"> (L347 - K347)/(K347-J347)</f>
+        <f t="shared" si="34"/>
         <v>-0.73621735689791612</v>
       </c>
       <c r="N347" s="10">
-        <f>K347/L347</f>
+        <f t="shared" si="35"/>
         <v>1.4360937499999999</v>
       </c>
       <c r="O347" s="4">
@@ -22929,11 +22926,11 @@
         <v>55</v>
       </c>
       <c r="M348" s="10">
-        <f xml:space="preserve"> (L348 - K348)/(K348-J348)</f>
+        <f t="shared" si="34"/>
         <v>-5.8231511254019299</v>
       </c>
       <c r="N348" s="10">
-        <f>K348/L348</f>
+        <f t="shared" si="35"/>
         <v>0.67072727272727273</v>
       </c>
       <c r="O348" s="4">
@@ -22973,7 +22970,6 @@
       <c r="H349" t="s">
         <v>324</v>
       </c>
-      <c r="I349" s="55"/>
       <c r="J349" s="10">
         <v>8</v>
       </c>
@@ -22984,11 +22980,11 @@
         <v>12</v>
       </c>
       <c r="M349" s="10">
-        <f xml:space="preserve"> (L349 - K349)/(K349-J349)</f>
+        <f t="shared" si="34"/>
         <v>2.8461538461538494</v>
       </c>
       <c r="N349" s="10">
-        <f>K349/L349</f>
+        <f t="shared" si="35"/>
         <v>0.7533333333333333</v>
       </c>
       <c r="O349" s="4">
@@ -23040,11 +23036,11 @@
         <v>22</v>
       </c>
       <c r="M350" s="10">
-        <f xml:space="preserve"> (L350 - K350)/(K350-J350)</f>
+        <f t="shared" si="34"/>
         <v>0.61616161616161635</v>
       </c>
       <c r="N350" s="10">
-        <f>K350/L350</f>
+        <f t="shared" si="35"/>
         <v>0.86136363636363633</v>
       </c>
       <c r="O350" s="4">
@@ -23097,11 +23093,11 @@
         <v>180</v>
       </c>
       <c r="M351" s="10">
-        <f xml:space="preserve"> (L351 - K351)/(K351-J351)</f>
+        <f t="shared" si="34"/>
         <v>-0.40828402366863925</v>
       </c>
       <c r="N351" s="10">
-        <f>K351/L351</f>
+        <f t="shared" si="35"/>
         <v>1.0766666666666667</v>
       </c>
       <c r="O351" s="4">
@@ -23151,7 +23147,7 @@
         <v>180</v>
       </c>
       <c r="M352" s="10">
-        <f xml:space="preserve"> (L352 - K352)/(K352-J352)</f>
+        <f t="shared" si="34"/>
         <v>-1.5032712632108707</v>
       </c>
       <c r="N352" s="10"/>
@@ -23202,11 +23198,11 @@
         <v>250</v>
       </c>
       <c r="M353" s="10">
-        <f xml:space="preserve"> (L353 - K353)/(K353-J353)</f>
+        <f t="shared" si="34"/>
         <v>1.2075055187637964</v>
       </c>
       <c r="N353" s="10">
-        <f>K353/L353</f>
+        <f t="shared" ref="N353:N366" si="36">K353/L353</f>
         <v>0.78120000000000001</v>
       </c>
       <c r="O353" s="4">
@@ -23256,11 +23252,11 @@
         <v>22</v>
       </c>
       <c r="M354" s="10">
-        <f xml:space="preserve"> (L354 - K354)/(K354-J354)</f>
+        <f t="shared" si="34"/>
         <v>-1.5295007564296521</v>
       </c>
       <c r="N354" s="10">
-        <f>K354/L354</f>
+        <f t="shared" si="36"/>
         <v>0.54045454545454552</v>
       </c>
       <c r="O354" s="4">
@@ -23311,11 +23307,11 @@
         <v>4</v>
       </c>
       <c r="M355" s="10">
-        <f xml:space="preserve"> (L355 - K355)/(K355-J355)</f>
+        <f t="shared" si="34"/>
         <v>1.233009708737864</v>
       </c>
       <c r="N355" s="10">
-        <f>K355/L355</f>
+        <f t="shared" si="36"/>
         <v>0.6825</v>
       </c>
       <c r="O355" s="4">
@@ -23362,11 +23358,11 @@
         <v>35</v>
       </c>
       <c r="M356" s="10">
-        <f xml:space="preserve"> (L356 - K356)/(K356-J356)</f>
+        <f t="shared" si="34"/>
         <v>-1.1290322580645162</v>
       </c>
       <c r="N356" s="10">
-        <f>K356/L356</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="O356" s="4">
@@ -23421,11 +23417,11 @@
         <v>120</v>
       </c>
       <c r="M357" s="10">
-        <f xml:space="preserve"> (L357 - K357)/(K357-J357)</f>
+        <f t="shared" si="34"/>
         <v>-0.6875</v>
       </c>
       <c r="N357" s="10">
-        <f>K357/L357</f>
+        <f t="shared" si="36"/>
         <v>1.3666666666666667</v>
       </c>
       <c r="O357" s="4">
@@ -23474,7 +23470,7 @@
       <c r="L358" s="10"/>
       <c r="M358" s="10"/>
       <c r="N358" s="10" t="e">
-        <f>K358/L358</f>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O358" s="4">
@@ -23531,7 +23527,7 @@
         <v>-0.73890339425587459</v>
       </c>
       <c r="N359" s="10">
-        <f>K359/L359</f>
+        <f t="shared" si="36"/>
         <v>1.5306249999999999</v>
       </c>
       <c r="O359" s="4">
@@ -23587,7 +23583,7 @@
         <v>-0.55564959796868374</v>
       </c>
       <c r="N360" s="10">
-        <f>K360/L360</f>
+        <f t="shared" si="36"/>
         <v>1.1250476190476191</v>
       </c>
       <c r="O360" s="4">
@@ -23638,7 +23634,7 @@
       <c r="L361" s="10"/>
       <c r="M361" s="10"/>
       <c r="N361" s="10" t="e">
-        <f>K361/L361</f>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O361" s="4">
@@ -23688,11 +23684,11 @@
         <v>5.5</v>
       </c>
       <c r="M362" s="10">
-        <f xml:space="preserve"> (L362 - K362)/(K362-J362)</f>
+        <f t="shared" ref="M362:M372" si="37" xml:space="preserve"> (L362 - K362)/(K362-J362)</f>
         <v>-0.75822050290135401</v>
       </c>
       <c r="N362" s="10">
-        <f>K362/L362</f>
+        <f t="shared" si="36"/>
         <v>2.4254545454545453</v>
       </c>
       <c r="O362" s="4">
@@ -23744,11 +23740,11 @@
         <v>140</v>
       </c>
       <c r="M363" s="10">
-        <f xml:space="preserve"> (L363 - K363)/(K363-J363)</f>
+        <f t="shared" si="37"/>
         <v>-0.6787320625401585</v>
       </c>
       <c r="N363" s="10">
-        <f>K363/L363</f>
+        <f t="shared" si="36"/>
         <v>1.6790714285714285</v>
       </c>
       <c r="O363" s="4">
@@ -23798,11 +23794,11 @@
         <v>100</v>
       </c>
       <c r="M364" s="10">
-        <f xml:space="preserve"> (L364 - K364)/(K364-J364)</f>
+        <f t="shared" si="37"/>
         <v>-0.7768568696206567</v>
       </c>
       <c r="N364" s="10">
-        <f>K364/L364</f>
+        <f t="shared" si="36"/>
         <v>1.4874000000000001</v>
       </c>
       <c r="O364" s="4">
@@ -23852,11 +23848,11 @@
         <v>20</v>
       </c>
       <c r="M365" s="10">
-        <f xml:space="preserve"> (L365 - K365)/(K365-J365)</f>
+        <f t="shared" si="37"/>
         <v>-0.64114832535885169</v>
       </c>
       <c r="N365" s="10">
-        <f>K365/L365</f>
+        <f t="shared" si="36"/>
         <v>1.268</v>
       </c>
       <c r="O365" s="4">
@@ -23908,11 +23904,11 @@
         <v>65</v>
       </c>
       <c r="M366" s="10">
-        <f xml:space="preserve"> (L366 - K366)/(K366-J366)</f>
+        <f t="shared" si="37"/>
         <v>-0.50626661602734524</v>
       </c>
       <c r="N366" s="10">
-        <f>K366/L366</f>
+        <f t="shared" si="36"/>
         <v>1.2050769230769232</v>
       </c>
       <c r="O366" s="4">
@@ -23965,7 +23961,7 @@
         <v>140</v>
       </c>
       <c r="M367" s="10">
-        <f xml:space="preserve"> (L367 - K367)/(K367-J367)</f>
+        <f t="shared" si="37"/>
         <v>-0.86050404538268388</v>
       </c>
       <c r="N367" s="10"/>
@@ -24015,7 +24011,7 @@
         <v>12</v>
       </c>
       <c r="M368" s="10">
-        <f xml:space="preserve"> (L368 - K368)/(K368-J368)</f>
+        <f t="shared" si="37"/>
         <v>-0.33712121212121204</v>
       </c>
       <c r="N368" s="10"/>
@@ -24068,7 +24064,7 @@
         <v>35</v>
       </c>
       <c r="M369" s="10">
-        <f xml:space="preserve"> (L369 - K369)/(K369-J369)</f>
+        <f t="shared" si="37"/>
         <v>-0.80211081794195249</v>
       </c>
       <c r="N369" s="10">
@@ -24123,7 +24119,7 @@
         <v>9</v>
       </c>
       <c r="M370" s="10">
-        <f xml:space="preserve"> (L370 - K370)/(K370-J370)</f>
+        <f t="shared" si="37"/>
         <v>-0.65020576131687247</v>
       </c>
       <c r="N370" s="10">
@@ -24177,7 +24173,7 @@
         <v>160</v>
       </c>
       <c r="M371" s="10">
-        <f xml:space="preserve"> (L371 - K371)/(K371-J371)</f>
+        <f t="shared" si="37"/>
         <v>-0.89856429463171039</v>
       </c>
       <c r="N371" s="10">
@@ -24231,7 +24227,7 @@
         <v>230</v>
       </c>
       <c r="M372" s="10">
-        <f xml:space="preserve"> (L372 - K372)/(K372-J372)</f>
+        <f t="shared" si="37"/>
         <v>-0.83686786296900495</v>
       </c>
       <c r="N372" s="10"/>
@@ -24579,7 +24575,7 @@
         <v>250</v>
       </c>
       <c r="M379" s="10">
-        <f xml:space="preserve"> (L379 - K379)/(K379-J379)</f>
+        <f t="shared" ref="M379:M384" si="38" xml:space="preserve"> (L379 - K379)/(K379-J379)</f>
         <v>-3.1582733812949648</v>
       </c>
       <c r="N379" s="10">
@@ -24633,7 +24629,7 @@
         <v>230</v>
       </c>
       <c r="M380" s="10">
-        <f xml:space="preserve"> (L380 - K380)/(K380-J380)</f>
+        <f t="shared" si="38"/>
         <v>-0.28943628612032213</v>
       </c>
       <c r="N380" s="10">
@@ -24688,7 +24684,7 @@
         <v>26</v>
       </c>
       <c r="M381" s="11">
-        <f xml:space="preserve"> (L381 - K381)/(K381-J381)</f>
+        <f t="shared" si="38"/>
         <v>-1.4772004241781549</v>
       </c>
       <c r="N381" s="10"/>
@@ -24741,11 +24737,11 @@
         <v>36.619999999999997</v>
       </c>
       <c r="M382" s="10">
-        <f xml:space="preserve"> (L382 - K382)/(K382-J382)</f>
+        <f t="shared" si="38"/>
         <v>-2.0355220667384284</v>
       </c>
       <c r="N382" s="10">
-        <f>K382/L382</f>
+        <f t="shared" ref="N382:N388" si="39">K382/L382</f>
         <v>0.48361551064991815</v>
       </c>
       <c r="O382" s="4">
@@ -24797,11 +24793,11 @@
         <v>52.25</v>
       </c>
       <c r="M383" s="10">
-        <f xml:space="preserve"> (L383 - K383)/(K383-J383)</f>
+        <f t="shared" si="38"/>
         <v>-1.0554768649669499</v>
       </c>
       <c r="N383" s="10">
-        <f>K383/L383</f>
+        <f t="shared" si="39"/>
         <v>0.14430622009569377</v>
       </c>
       <c r="O383" s="4">
@@ -24853,11 +24849,11 @@
         <v>32.5</v>
       </c>
       <c r="M384" s="10">
-        <f xml:space="preserve"> (L384 - K384)/(K384-J384)</f>
+        <f t="shared" si="38"/>
         <v>1.0325203252032513</v>
       </c>
       <c r="N384" s="10">
-        <f>K384/L384</f>
+        <f t="shared" si="39"/>
         <v>0.92184615384615387</v>
       </c>
       <c r="O384" s="4">
@@ -24904,7 +24900,7 @@
       <c r="L385" s="10"/>
       <c r="M385" s="10"/>
       <c r="N385" s="10" t="e">
-        <f>K385/L385</f>
+        <f t="shared" si="39"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O385" s="4">
@@ -24961,7 +24957,7 @@
         <v>0.93236714975845381</v>
       </c>
       <c r="N386" s="10">
-        <f>K386/L386</f>
+        <f t="shared" si="39"/>
         <v>0.77942857142857147</v>
       </c>
       <c r="O386" s="4">
@@ -25017,7 +25013,7 @@
         <v>-1.372995151063036</v>
       </c>
       <c r="N387" s="10">
-        <f>K387/L387</f>
+        <f t="shared" si="39"/>
         <v>0.56694117647058817</v>
       </c>
       <c r="O387" s="4">
@@ -25073,7 +25069,7 @@
         <v>0.35527589545014504</v>
       </c>
       <c r="N388" s="10">
-        <f>K388/L388</f>
+        <f t="shared" si="39"/>
         <v>0.89514285714285713</v>
       </c>
       <c r="O388" s="4">
@@ -25169,11 +25165,11 @@
         <v>260</v>
       </c>
       <c r="M390" s="10">
-        <f xml:space="preserve"> (L390 - K390)/(K390-J390)</f>
+        <f t="shared" ref="M390:M395" si="40" xml:space="preserve"> (L390 - K390)/(K390-J390)</f>
         <v>-1.7859949982136474</v>
       </c>
       <c r="N390" s="10">
-        <f>K390/L390</f>
+        <f t="shared" ref="N390:N395" si="41">K390/L390</f>
         <v>0.80773076923076914</v>
       </c>
       <c r="O390" s="4">
@@ -25223,11 +25219,11 @@
         <v>120</v>
       </c>
       <c r="M391" s="10">
-        <f xml:space="preserve"> (L391 - K391)/(K391-J391)</f>
+        <f t="shared" si="40"/>
         <v>-0.72482113373692902</v>
       </c>
       <c r="N391" s="10">
-        <f>K391/L391</f>
+        <f t="shared" si="41"/>
         <v>1.2195</v>
       </c>
       <c r="O391" s="4">
@@ -25279,11 +25275,11 @@
         <v>70</v>
       </c>
       <c r="M392" s="10">
-        <f xml:space="preserve"> (L392 - K392)/(K392-J392)</f>
+        <f t="shared" si="40"/>
         <v>1.9723991507430993</v>
       </c>
       <c r="N392" s="10">
-        <f>K392/L392</f>
+        <f t="shared" si="41"/>
         <v>0.86728571428571433</v>
       </c>
       <c r="O392" s="4">
@@ -25338,11 +25334,11 @@
         <v>25</v>
       </c>
       <c r="M393" s="10">
-        <f xml:space="preserve"> (L393 - K393)/(K393-J393)</f>
+        <f t="shared" si="40"/>
         <v>-1.9823182711198428</v>
       </c>
       <c r="N393" s="10">
-        <f>K393/L393</f>
+        <f t="shared" si="41"/>
         <v>0.59640000000000004</v>
       </c>
       <c r="O393" s="4">
@@ -25394,11 +25390,11 @@
         <v>110</v>
       </c>
       <c r="M394" s="10">
-        <f xml:space="preserve"> (L394 - K394)/(K394-J394)</f>
+        <f t="shared" si="40"/>
         <v>-1.1665556295802797</v>
       </c>
       <c r="N394" s="10">
-        <f>K394/L394</f>
+        <f t="shared" si="41"/>
         <v>0.3632727272727273</v>
       </c>
       <c r="O394" s="4">
@@ -25448,11 +25444,11 @@
         <v>425</v>
       </c>
       <c r="M395" s="10">
-        <f xml:space="preserve"> (L395 - K395)/(K395-J395)</f>
+        <f t="shared" si="40"/>
         <v>-3.5728987993138959</v>
       </c>
       <c r="N395" s="10">
-        <f>K395/L395</f>
+        <f t="shared" si="41"/>
         <v>0.75494117647058834</v>
       </c>
       <c r="O395" s="4">
@@ -25795,7 +25791,7 @@
         <v>45</v>
       </c>
       <c r="M402" s="10">
-        <f xml:space="preserve"> (L402 - K402)/(K402-J402)</f>
+        <f t="shared" ref="M402:M409" si="42" xml:space="preserve"> (L402 - K402)/(K402-J402)</f>
         <v>-0.44102850754611517</v>
       </c>
       <c r="N402" s="10">
@@ -25849,7 +25845,7 @@
         <v>65</v>
       </c>
       <c r="M403" s="10">
-        <f xml:space="preserve"> (L403 - K403)/(K403-J403)</f>
+        <f t="shared" si="42"/>
         <v>-1.9014423076923077</v>
       </c>
       <c r="N403" s="10">
@@ -25903,7 +25899,7 @@
         <v>90</v>
       </c>
       <c r="M404" s="10">
-        <f xml:space="preserve"> (L404 - K404)/(K404-J404)</f>
+        <f t="shared" si="42"/>
         <v>9.6190737188270911E-2</v>
       </c>
       <c r="N404" s="10">
@@ -25962,7 +25958,7 @@
         <v>183</v>
       </c>
       <c r="M405" s="10">
-        <f xml:space="preserve"> (L405 - K405)/(K405-J405)</f>
+        <f t="shared" si="42"/>
         <v>-0.91327551701134091</v>
       </c>
       <c r="N405" s="10"/>
@@ -26016,7 +26012,7 @@
         <v>50</v>
       </c>
       <c r="M406" s="10">
-        <f xml:space="preserve"> (L406 - K406)/(K406-J406)</f>
+        <f t="shared" si="42"/>
         <v>12.513513513513606</v>
       </c>
       <c r="N406" s="10">
@@ -26072,7 +26068,7 @@
         <v>100</v>
       </c>
       <c r="M407" s="10">
-        <f xml:space="preserve"> (L407 - K407)/(K407-J407)</f>
+        <f t="shared" si="42"/>
         <v>-2.2422360248447211</v>
       </c>
       <c r="N407" s="10">
@@ -26126,7 +26122,7 @@
         <v>60</v>
       </c>
       <c r="M408" s="10">
-        <f xml:space="preserve"> (L408 - K408)/(K408-J408)</f>
+        <f t="shared" si="42"/>
         <v>-3.0161290322580649</v>
       </c>
       <c r="N408" s="10">
@@ -26181,7 +26177,7 @@
         <v>18</v>
       </c>
       <c r="M409" s="10">
-        <f xml:space="preserve"> (L409 - K409)/(K409-J409)</f>
+        <f t="shared" si="42"/>
         <v>-0.14346895074946497</v>
       </c>
       <c r="N409" s="10">
@@ -26843,11 +26839,11 @@
         <v>50</v>
       </c>
       <c r="M422" s="10">
-        <f xml:space="preserve"> (L422 - K422)/(K422-J422)</f>
+        <f t="shared" ref="M422:M429" si="43" xml:space="preserve"> (L422 - K422)/(K422-J422)</f>
         <v>-0.97376322770603152</v>
       </c>
       <c r="N422" s="10">
-        <f>K422/L422</f>
+        <f t="shared" ref="N422:N437" si="44">K422/L422</f>
         <v>7.6805999999999992</v>
       </c>
       <c r="O422" s="4">
@@ -26898,11 +26894,11 @@
         <v>80</v>
       </c>
       <c r="M423" s="10">
-        <f xml:space="preserve"> (L423 - K423)/(K423-J423)</f>
+        <f t="shared" si="43"/>
         <v>-18.241379310344879</v>
       </c>
       <c r="N423" s="10">
-        <f>K423/L423</f>
+        <f t="shared" si="44"/>
         <v>0.73550000000000004</v>
       </c>
       <c r="O423" s="4">
@@ -26952,11 +26948,11 @@
         <v>80</v>
       </c>
       <c r="M424" s="10">
-        <f xml:space="preserve"> (L424 - K424)/(K424-J424)</f>
+        <f t="shared" si="43"/>
         <v>-0.48132780082987553</v>
       </c>
       <c r="N424" s="10">
-        <f>K424/L424</f>
+        <f t="shared" si="44"/>
         <v>1.1160000000000001</v>
       </c>
       <c r="O424" s="4">
@@ -27006,11 +27002,11 @@
         <v>220</v>
       </c>
       <c r="M425" s="10">
-        <f xml:space="preserve"> (L425 - K425)/(K425-J425)</f>
+        <f t="shared" si="43"/>
         <v>-8.4626865671642122</v>
       </c>
       <c r="N425" s="10">
-        <f>K425/L425</f>
+        <f t="shared" si="44"/>
         <v>0.92268181818181827</v>
       </c>
       <c r="O425" s="4">
@@ -27060,11 +27056,11 @@
         <v>44</v>
       </c>
       <c r="M426" s="10">
-        <f xml:space="preserve"> (L426 - K426)/(K426-J426)</f>
+        <f t="shared" si="43"/>
         <v>-0.43449575871819035</v>
       </c>
       <c r="N426" s="10">
-        <f>K426/L426</f>
+        <f t="shared" si="44"/>
         <v>1.2095454545454545</v>
       </c>
       <c r="O426" s="4">
@@ -27114,11 +27110,11 @@
         <v>240</v>
       </c>
       <c r="M427" s="10">
-        <f xml:space="preserve"> (L427 - K427)/(K427-J427)</f>
+        <f t="shared" si="43"/>
         <v>-4.9525691699604728</v>
       </c>
       <c r="N427" s="10">
-        <f>K427/L427</f>
+        <f t="shared" si="44"/>
         <v>0.89558333333333329</v>
       </c>
       <c r="O427" s="4">
@@ -27170,11 +27166,11 @@
         <v>97</v>
       </c>
       <c r="M428" s="10">
-        <f xml:space="preserve"> (L428 - K428)/(K428-J428)</f>
+        <f t="shared" si="43"/>
         <v>-0.47589098532494756</v>
       </c>
       <c r="N428" s="10">
-        <f>K428/L428</f>
+        <f t="shared" si="44"/>
         <v>1.0936082474226805</v>
       </c>
       <c r="O428" s="4">
@@ -27224,11 +27220,11 @@
         <v>425</v>
       </c>
       <c r="M429" s="10">
-        <f xml:space="preserve"> (L429 - K429)/(K429-J429)</f>
+        <f t="shared" si="43"/>
         <v>-1.2616294280780702</v>
       </c>
       <c r="N429" s="10">
-        <f>K429/L429</f>
+        <f t="shared" si="44"/>
         <v>0.43268235294117646</v>
       </c>
       <c r="O429" s="4">
@@ -27275,7 +27271,7 @@
       <c r="L430" s="10"/>
       <c r="M430" s="10"/>
       <c r="N430" s="10" t="e">
-        <f>K430/L430</f>
+        <f t="shared" si="44"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O430" s="4">
@@ -27327,11 +27323,11 @@
         <v>49</v>
       </c>
       <c r="M431" s="10">
-        <f xml:space="preserve"> (L431 - K431)/(K431-J431)</f>
+        <f t="shared" ref="M431:M437" si="45" xml:space="preserve"> (L431 - K431)/(K431-J431)</f>
         <v>-1.1818582122413035</v>
       </c>
       <c r="N431" s="10">
-        <f>K431/L431</f>
+        <f t="shared" si="44"/>
         <v>0.45224489795918366</v>
       </c>
       <c r="O431" s="4">
@@ -27383,11 +27379,11 @@
         <v>107</v>
       </c>
       <c r="M432" s="10">
-        <f xml:space="preserve"> (L432 - K432)/(K432-J432)</f>
+        <f t="shared" si="45"/>
         <v>-1.9421265141318969</v>
       </c>
       <c r="N432" s="10">
-        <f>K432/L432</f>
+        <f t="shared" si="44"/>
         <v>0.86514018691588779</v>
       </c>
       <c r="O432" s="4">
@@ -27437,11 +27433,11 @@
         <v>16</v>
       </c>
       <c r="M433" s="10">
-        <f xml:space="preserve"> (L433 - K433)/(K433-J433)</f>
+        <f t="shared" si="45"/>
         <v>-2.0869565217391304</v>
       </c>
       <c r="N433" s="10">
-        <f>K433/L433</f>
+        <f t="shared" si="44"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="O433" s="4">
@@ -27491,11 +27487,11 @@
         <v>300</v>
       </c>
       <c r="M434" s="10">
-        <f xml:space="preserve"> (L434 - K434)/(K434-J434)</f>
+        <f t="shared" si="45"/>
         <v>-0.59648945828709776</v>
       </c>
       <c r="N434" s="10">
-        <f>K434/L434</f>
+        <f t="shared" si="44"/>
         <v>1.1971000000000001</v>
       </c>
       <c r="O434" s="4">
@@ -27545,11 +27541,11 @@
         <v>55</v>
       </c>
       <c r="M435" s="10">
-        <f xml:space="preserve"> (L435 - K435)/(K435-J435)</f>
+        <f t="shared" si="45"/>
         <v>-1.5485463521667582</v>
       </c>
       <c r="N435" s="10">
-        <f>K435/L435</f>
+        <f t="shared" si="44"/>
         <v>0.48672727272727273</v>
       </c>
       <c r="O435" s="4">
@@ -27602,11 +27598,11 @@
         <v>66</v>
       </c>
       <c r="M436" s="10">
-        <f xml:space="preserve"> (L436 - K436)/(K436-J436)</f>
+        <f t="shared" si="45"/>
         <v>-1.3229278794402584</v>
       </c>
       <c r="N436" s="10">
-        <f>K436/L436</f>
+        <f t="shared" si="44"/>
         <v>0.62757575757575756</v>
       </c>
       <c r="O436" s="4">
@@ -27658,11 +27654,11 @@
         <v>43</v>
       </c>
       <c r="M437" s="10">
-        <f xml:space="preserve"> (L437 - K437)/(K437-J437)</f>
+        <f t="shared" si="45"/>
         <v>-14.043478260869541</v>
       </c>
       <c r="N437" s="10">
-        <f>K437/L437</f>
+        <f t="shared" si="44"/>
         <v>0.84976744186046504</v>
       </c>
       <c r="O437" s="4">
@@ -27758,11 +27754,11 @@
         <v>7.32</v>
       </c>
       <c r="M439" s="10">
-        <f xml:space="preserve"> (L439 - K439)/(K439-J439)</f>
+        <f t="shared" ref="M439:M448" si="46" xml:space="preserve"> (L439 - K439)/(K439-J439)</f>
         <v>-1.1487179487179486</v>
       </c>
       <c r="N439" s="10">
-        <f>K439/L439</f>
+        <f t="shared" ref="N439:N448" si="47">K439/L439</f>
         <v>0.38797814207650272</v>
       </c>
       <c r="O439" s="4">
@@ -27819,11 +27815,11 @@
         <v>55</v>
       </c>
       <c r="M440" s="10">
-        <f xml:space="preserve"> (L440 - K440)/(K440-J440)</f>
+        <f t="shared" si="46"/>
         <v>-1.4180602006688963</v>
       </c>
       <c r="N440" s="10">
-        <f>K440/L440</f>
+        <f t="shared" si="47"/>
         <v>0.38327272727272726</v>
       </c>
       <c r="O440" s="4">
@@ -27877,11 +27873,11 @@
         <v>40</v>
       </c>
       <c r="M441" s="10">
-        <f xml:space="preserve"> (L441 - K441)/(K441-J441)</f>
+        <f t="shared" si="46"/>
         <v>-1.1569365976145638</v>
       </c>
       <c r="N441" s="10">
-        <f>K441/L441</f>
+        <f t="shared" si="47"/>
         <v>0.53925000000000001</v>
       </c>
       <c r="O441" s="4">
@@ -27935,11 +27931,11 @@
         <v>90</v>
       </c>
       <c r="M442" s="10">
-        <f xml:space="preserve"> (L442 - K442)/(K442-J442)</f>
+        <f t="shared" si="46"/>
         <v>1765.6666666665997</v>
       </c>
       <c r="N442" s="10">
-        <f>K442/L442</f>
+        <f t="shared" si="47"/>
         <v>0.41144444444444445</v>
       </c>
       <c r="O442" s="4">
@@ -27989,11 +27985,11 @@
         <v>277</v>
       </c>
       <c r="M443" s="10">
-        <f xml:space="preserve"> (L443 - K443)/(K443-J443)</f>
+        <f t="shared" si="46"/>
         <v>-1.2403506291531174</v>
       </c>
       <c r="N443" s="10">
-        <f>K443/L443</f>
+        <f t="shared" si="47"/>
         <v>0.68328519855595671</v>
       </c>
       <c r="O443" s="4">
@@ -28046,11 +28042,11 @@
         <v>190</v>
       </c>
       <c r="M444" s="10">
-        <f xml:space="preserve"> (L444 - K444)/(K444-J444)</f>
+        <f t="shared" si="46"/>
         <v>-1.4683109584764282</v>
       </c>
       <c r="N444" s="10">
-        <f>K444/L444</f>
+        <f t="shared" si="47"/>
         <v>0.50494736842105259</v>
       </c>
       <c r="O444" s="4">
@@ -28098,11 +28094,11 @@
         <v>76.819999999999993</v>
       </c>
       <c r="M445" s="10">
-        <f xml:space="preserve"> (L445 - K445)/(K445-J445)</f>
+        <f t="shared" si="46"/>
         <v>-0.45280437756497965</v>
       </c>
       <c r="N445" s="10">
-        <f>K445/L445</f>
+        <f t="shared" si="47"/>
         <v>1.0861754751366832</v>
       </c>
       <c r="O445" s="28">
@@ -28154,11 +28150,11 @@
         <v>105</v>
       </c>
       <c r="M446" s="10">
-        <f xml:space="preserve"> (L446 - K446)/(K446-J446)</f>
+        <f t="shared" si="46"/>
         <v>-1.4288939051918734</v>
       </c>
       <c r="N446" s="10">
-        <f>K446/L446</f>
+        <f t="shared" si="47"/>
         <v>0.69857142857142851</v>
       </c>
       <c r="O446" s="4">
@@ -28210,11 +28206,11 @@
         <v>4</v>
       </c>
       <c r="M447" s="10">
-        <f xml:space="preserve"> (L447 - K447)/(K447-J447)</f>
+        <f t="shared" si="46"/>
         <v>-0.78654592496765841</v>
       </c>
       <c r="N447" s="10">
-        <f>K447/L447</f>
+        <f t="shared" si="47"/>
         <v>2.52</v>
       </c>
       <c r="O447" s="4">
@@ -28264,11 +28260,11 @@
         <v>77.5</v>
       </c>
       <c r="M448" s="10">
-        <f xml:space="preserve"> (L448 - K448)/(K448-J448)</f>
+        <f t="shared" si="46"/>
         <v>-0.48777348777348795</v>
       </c>
       <c r="N448" s="10">
-        <f>K448/L448</f>
+        <f t="shared" si="47"/>
         <v>1.0489032258064517</v>
       </c>
       <c r="O448" s="4">
@@ -28373,7 +28369,7 @@
         <v>-24.364485981308455</v>
       </c>
       <c r="N450" s="10">
-        <f>K450/L450</f>
+        <f t="shared" ref="N450:N456" si="48">K450/L450</f>
         <v>0.60894999999999999</v>
       </c>
       <c r="O450" s="4">
@@ -28429,7 +28425,7 @@
         <v>-0.5657460482890394</v>
       </c>
       <c r="N451" s="10">
-        <f>K451/L451</f>
+        <f t="shared" si="48"/>
         <v>1.2035624999999999</v>
       </c>
       <c r="O451" s="4">
@@ -28485,7 +28481,7 @@
         <v>-3.0172135556750943</v>
       </c>
       <c r="N452" s="10">
-        <f>K452/L452</f>
+        <f t="shared" si="48"/>
         <v>0.50142222222222221</v>
       </c>
       <c r="O452" s="4">
@@ -28539,7 +28535,7 @@
         <v>-1.5141388174807198</v>
       </c>
       <c r="N453" s="10">
-        <f>K453/L453</f>
+        <f t="shared" si="48"/>
         <v>0.7818518518518518</v>
       </c>
       <c r="O453" s="4">
@@ -28593,7 +28589,7 @@
         <v>-0.88496130516628324</v>
       </c>
       <c r="N454" s="10">
-        <f>K454/L454</f>
+        <f t="shared" si="48"/>
         <v>1.3899539170506912</v>
       </c>
       <c r="O454" s="4">
@@ -28640,7 +28636,7 @@
       <c r="L455" s="10"/>
       <c r="M455" s="10"/>
       <c r="N455" s="10" t="e">
-        <f>K455/L455</f>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O455" s="4">
@@ -28690,11 +28686,11 @@
         <v>160</v>
       </c>
       <c r="M456" s="10">
-        <f xml:space="preserve"> (L456 - K456)/(K456-J456)</f>
+        <f t="shared" ref="M456:M468" si="49" xml:space="preserve"> (L456 - K456)/(K456-J456)</f>
         <v>-0.34640522875817042</v>
       </c>
       <c r="N456" s="10">
-        <f>K456/L456</f>
+        <f t="shared" si="48"/>
         <v>1.0331250000000001</v>
       </c>
       <c r="O456" s="4">
@@ -28746,7 +28742,7 @@
         <v>30</v>
       </c>
       <c r="M457" s="10">
-        <f xml:space="preserve"> (L457 - K457)/(K457-J457)</f>
+        <f t="shared" si="49"/>
         <v>-0.72390944229707344</v>
       </c>
       <c r="N457" s="10">
@@ -28804,11 +28800,11 @@
         <v>34</v>
       </c>
       <c r="M458" s="10">
-        <f xml:space="preserve"> (L458 - K458)/(K458-J458)</f>
+        <f t="shared" si="49"/>
         <v>0.24999999999999889</v>
       </c>
       <c r="N458" s="10">
-        <f>K458/L458</f>
+        <f t="shared" ref="N458:N468" si="50">K458/L458</f>
         <v>0.9882352941176471</v>
       </c>
       <c r="O458" s="28">
@@ -28817,7 +28813,6 @@
       <c r="P458" s="28">
         <v>0.01</v>
       </c>
-      <c r="Q458" s="55"/>
       <c r="R458" t="s">
         <v>324</v>
       </c>
@@ -28860,11 +28855,11 @@
         <v>425</v>
       </c>
       <c r="M459" s="10">
-        <f xml:space="preserve"> (L459 - K459)/(K459-J459)</f>
+        <f t="shared" si="49"/>
         <v>-0.72934935585146699</v>
       </c>
       <c r="N459" s="10">
-        <f>K459/L459</f>
+        <f t="shared" si="50"/>
         <v>1.3170352941176471</v>
       </c>
       <c r="O459" s="4">
@@ -28916,11 +28911,11 @@
         <v>20</v>
       </c>
       <c r="M460" s="10">
-        <f xml:space="preserve"> (L460 - K460)/(K460-J460)</f>
+        <f t="shared" si="49"/>
         <v>-3.3219814241486065</v>
       </c>
       <c r="N460" s="10">
-        <f>K460/L460</f>
+        <f t="shared" si="50"/>
         <v>0.46349999999999997</v>
       </c>
       <c r="O460" s="4">
@@ -28972,11 +28967,11 @@
         <v>55</v>
       </c>
       <c r="M461" s="10">
-        <f xml:space="preserve"> (L461 - K461)/(K461-J461)</f>
+        <f t="shared" si="49"/>
         <v>-1.7288629737609329</v>
       </c>
       <c r="N461" s="10">
-        <f>K461/L461</f>
+        <f t="shared" si="50"/>
         <v>0.35309090909090912</v>
       </c>
       <c r="O461" s="4">
@@ -29028,11 +29023,11 @@
         <v>105</v>
       </c>
       <c r="M462" s="10">
-        <f xml:space="preserve"> (L462 - K462)/(K462-J462)</f>
+        <f t="shared" si="49"/>
         <v>-1.1796945193171609</v>
       </c>
       <c r="N462" s="10">
-        <f>K462/L462</f>
+        <f t="shared" si="50"/>
         <v>0.12466666666666666</v>
       </c>
       <c r="O462" s="4">
@@ -29081,11 +29076,11 @@
         <v>80</v>
       </c>
       <c r="M463" s="10">
-        <f xml:space="preserve"> (L463 - K463)/(K463-J463)</f>
+        <f t="shared" si="49"/>
         <v>-0.39819458375125372</v>
       </c>
       <c r="N463" s="10">
-        <f>K463/L463</f>
+        <f t="shared" si="50"/>
         <v>1.0992500000000001</v>
       </c>
       <c r="O463" s="4">
@@ -29136,11 +29131,11 @@
         <v>400</v>
       </c>
       <c r="M464" s="10">
-        <f xml:space="preserve"> (L464 - K464)/(K464-J464)</f>
+        <f t="shared" si="49"/>
         <v>-25.630541871921167</v>
       </c>
       <c r="N464" s="10">
-        <f>K464/L464</f>
+        <f t="shared" si="50"/>
         <v>0.73985000000000001</v>
       </c>
       <c r="O464" s="4">
@@ -29190,11 +29185,11 @@
         <v>115</v>
       </c>
       <c r="M465" s="10">
-        <f xml:space="preserve"> (L465 - K465)/(K465-J465)</f>
+        <f t="shared" si="49"/>
         <v>-1.2283452580301415</v>
       </c>
       <c r="N465" s="10">
-        <f>K465/L465</f>
+        <f t="shared" si="50"/>
         <v>0.29834782608695654</v>
       </c>
       <c r="O465" s="4">
@@ -29248,11 +29243,11 @@
         <v>18</v>
       </c>
       <c r="M466" s="10">
-        <f xml:space="preserve"> (L466 - K466)/(K466-J466)</f>
+        <f t="shared" si="49"/>
         <v>3.7619047619047428</v>
       </c>
       <c r="N466" s="10">
-        <f>K466/L466</f>
+        <f t="shared" si="50"/>
         <v>0.95611111111111113</v>
       </c>
       <c r="O466" s="4">
@@ -29304,11 +29299,11 @@
         <v>135</v>
       </c>
       <c r="M467" s="10">
-        <f xml:space="preserve"> (L467 - K467)/(K467-J467)</f>
+        <f t="shared" si="49"/>
         <v>0.48104265402843643</v>
       </c>
       <c r="N467" s="10">
-        <f>K467/L467</f>
+        <f t="shared" si="50"/>
         <v>0.93985185185185183</v>
       </c>
       <c r="O467" s="4">
@@ -29360,11 +29355,11 @@
         <v>55</v>
       </c>
       <c r="M468" s="10">
-        <f xml:space="preserve"> (L468 - K468)/(K468-J468)</f>
+        <f t="shared" si="49"/>
         <v>-1.6849315068493151</v>
       </c>
       <c r="N468" s="10">
-        <f>K468/L468</f>
+        <f t="shared" si="50"/>
         <v>0.59745454545454546</v>
       </c>
       <c r="O468" s="4">
@@ -29924,7 +29919,7 @@
       <c r="L480" s="10"/>
       <c r="M480" s="10"/>
       <c r="N480" s="10" t="e">
-        <f>K480/L480</f>
+        <f t="shared" ref="N480:N486" si="51">K480/L480</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O480" s="4">
@@ -29974,11 +29969,11 @@
         <v>85</v>
       </c>
       <c r="M481" s="10">
-        <f xml:space="preserve"> (L481 - K481)/(K481-J481)</f>
+        <f t="shared" ref="M481:M486" si="52" xml:space="preserve"> (L481 - K481)/(K481-J481)</f>
         <v>-0.75818152506851522</v>
       </c>
       <c r="N481" s="10">
-        <f>K481/L481</f>
+        <f t="shared" si="51"/>
         <v>1.5532941176470589</v>
       </c>
       <c r="O481" s="4">
@@ -30028,11 +30023,11 @@
         <v>200</v>
       </c>
       <c r="M482" s="10">
-        <f xml:space="preserve"> (L482 - K482)/(K482-J482)</f>
+        <f t="shared" si="52"/>
         <v>65.666666666666671</v>
       </c>
       <c r="N482" s="10">
-        <f>K482/L482</f>
+        <f t="shared" si="51"/>
         <v>0.75375000000000003</v>
       </c>
       <c r="O482" s="4">
@@ -30083,11 +30078,11 @@
         <v>90</v>
       </c>
       <c r="M483" s="10">
-        <f xml:space="preserve"> (L483 - K483)/(K483-J483)</f>
+        <f t="shared" si="52"/>
         <v>0.73076923076922984</v>
       </c>
       <c r="N483" s="10">
-        <f>K483/L483</f>
+        <f t="shared" si="51"/>
         <v>0.95777777777777784</v>
       </c>
       <c r="O483" s="4">
@@ -30137,11 +30132,11 @@
         <v>500</v>
       </c>
       <c r="M484" s="10">
-        <f xml:space="preserve"> (L484 - K484)/(K484-J484)</f>
+        <f t="shared" si="52"/>
         <v>-4.1259768677711772</v>
       </c>
       <c r="N484" s="10">
-        <f>K484/L484</f>
+        <f t="shared" si="51"/>
         <v>0.73602000000000001</v>
       </c>
       <c r="O484" s="4">
@@ -30194,11 +30189,11 @@
         <v>17</v>
       </c>
       <c r="M485" s="11">
-        <f xml:space="preserve"> (L485 - K485)/(K485-J485)</f>
+        <f t="shared" si="52"/>
         <v>-0.60606060606060597</v>
       </c>
       <c r="N485" s="10">
-        <f>K485/L485</f>
+        <f t="shared" si="51"/>
         <v>1.1176470588235294</v>
       </c>
       <c r="O485" s="4">
@@ -30250,11 +30245,11 @@
         <v>240</v>
       </c>
       <c r="M486" s="10">
-        <f xml:space="preserve"> (L486 - K486)/(K486-J486)</f>
+        <f t="shared" si="52"/>
         <v>-0.16544961402044661</v>
       </c>
       <c r="N486" s="10">
-        <f>K486/L486</f>
+        <f t="shared" si="51"/>
         <v>1.0330416666666666</v>
       </c>
       <c r="O486" s="4">
@@ -30754,7 +30749,7 @@
         <v>460</v>
       </c>
       <c r="M497" s="10">
-        <f xml:space="preserve"> (L497 - K497)/(K497-J497)</f>
+        <f t="shared" ref="M497:M514" si="53" xml:space="preserve"> (L497 - K497)/(K497-J497)</f>
         <v>-4.3076074972436631</v>
       </c>
       <c r="N497" s="10">
@@ -30808,7 +30803,7 @@
         <v>25</v>
       </c>
       <c r="M498" s="10">
-        <f xml:space="preserve"> (L498 - K498)/(K498-J498)</f>
+        <f t="shared" si="53"/>
         <v>12.51351351351351</v>
       </c>
       <c r="N498" s="10">
@@ -30864,7 +30859,7 @@
         <v>350</v>
       </c>
       <c r="M499" s="10">
-        <f xml:space="preserve"> (L499 - K499)/(K499-J499)</f>
+        <f t="shared" si="53"/>
         <v>2.111387678904793</v>
       </c>
       <c r="N499" s="10"/>
@@ -30920,11 +30915,11 @@
         <v>700</v>
       </c>
       <c r="M500" s="10">
-        <f xml:space="preserve"> (L500 - K500)/(K500-J500)</f>
+        <f t="shared" si="53"/>
         <v>-1.196800031488005</v>
       </c>
       <c r="N500" s="10">
-        <f>K500/L500</f>
+        <f t="shared" ref="N500:N513" si="54">K500/L500</f>
         <v>0.13124285714285716</v>
       </c>
       <c r="O500" s="4">
@@ -30976,11 +30971,11 @@
         <v>50</v>
       </c>
       <c r="M501" s="10">
-        <f xml:space="preserve"> (L501 - K501)/(K501-J501)</f>
+        <f t="shared" si="53"/>
         <v>-4.0978934324659226</v>
       </c>
       <c r="N501" s="10">
-        <f>K501/L501</f>
+        <f t="shared" si="54"/>
         <v>0.33860000000000001</v>
       </c>
       <c r="O501" s="4">
@@ -31031,11 +31026,11 @@
         <v>275</v>
       </c>
       <c r="M502" s="10">
-        <f xml:space="preserve"> (L502 - K502)/(K502-J502)</f>
+        <f t="shared" si="53"/>
         <v>-2.1715089034676662</v>
       </c>
       <c r="N502" s="10">
-        <f>K502/L502</f>
+        <f t="shared" si="54"/>
         <v>0.49447272727272723</v>
       </c>
       <c r="O502" s="4">
@@ -31085,11 +31080,11 @@
         <v>7.5</v>
       </c>
       <c r="M503" s="10">
-        <f xml:space="preserve"> (L503 - K503)/(K503-J503)</f>
+        <f t="shared" si="53"/>
         <v>-2.0975609756097562</v>
       </c>
       <c r="N503" s="10">
-        <f>K503/L503</f>
+        <f t="shared" si="54"/>
         <v>0.19733333333333333</v>
       </c>
       <c r="O503" s="4">
@@ -31139,11 +31134,11 @@
         <v>650</v>
       </c>
       <c r="M504" s="10">
-        <f xml:space="preserve"> (L504 - K504)/(K504-J504)</f>
+        <f t="shared" si="53"/>
         <v>-1.5955216769890423</v>
       </c>
       <c r="N504" s="10">
-        <f>K504/L504</f>
+        <f t="shared" si="54"/>
         <v>0.38172307692307694</v>
       </c>
       <c r="O504" s="4">
@@ -31195,11 +31190,11 @@
         <v>5</v>
       </c>
       <c r="M505" s="10">
-        <f xml:space="preserve"> (L505 - K505)/(K505-J505)</f>
+        <f t="shared" si="53"/>
         <v>-1.5352463628325699E-2</v>
       </c>
       <c r="N505" s="10">
-        <f>K505/L505</f>
+        <f t="shared" si="54"/>
         <v>0.23599999999999999</v>
       </c>
       <c r="O505" s="4">
@@ -31251,11 +31246,11 @@
         <v>95</v>
       </c>
       <c r="M506" s="10">
-        <f xml:space="preserve"> (L506 - K506)/(K506-J506)</f>
+        <f t="shared" si="53"/>
         <v>-1.9615384615384615</v>
       </c>
       <c r="N506" s="10">
-        <f>K506/L506</f>
+        <f t="shared" si="54"/>
         <v>0.4631578947368421</v>
       </c>
       <c r="O506" s="4">
@@ -31307,11 +31302,11 @@
         <v>240</v>
       </c>
       <c r="M507" s="10">
-        <f xml:space="preserve"> (L507 - K507)/(K507-J507)</f>
+        <f t="shared" si="53"/>
         <v>-1.7384842610541862</v>
       </c>
       <c r="N507" s="10">
-        <f>K507/L507</f>
+        <f t="shared" si="54"/>
         <v>0.21529166666666669</v>
       </c>
       <c r="O507" s="4">
@@ -31363,11 +31358,11 @@
         <v>220</v>
       </c>
       <c r="M508" s="10">
-        <f xml:space="preserve"> (L508 - K508)/(K508-J508)</f>
+        <f t="shared" si="53"/>
         <v>-1.5631264782070053</v>
       </c>
       <c r="N508" s="10">
-        <f>K508/L508</f>
+        <f t="shared" si="54"/>
         <v>0.3691363636363636</v>
       </c>
       <c r="O508" s="4">
@@ -31417,11 +31412,11 @@
         <v>450</v>
       </c>
       <c r="M509" s="10">
-        <f xml:space="preserve"> (L509 - K509)/(K509-J509)</f>
+        <f t="shared" si="53"/>
         <v>-1.2925950934053565</v>
       </c>
       <c r="N509" s="10">
-        <f>K509/L509</f>
+        <f t="shared" si="54"/>
         <v>0.36188888888888887</v>
       </c>
       <c r="O509" s="4">
@@ -31471,11 +31466,11 @@
         <v>5</v>
       </c>
       <c r="M510" s="10">
-        <f xml:space="preserve"> (L510 - K510)/(K510-J510)</f>
+        <f t="shared" si="53"/>
         <v>-1.3973509933774835</v>
       </c>
       <c r="N510" s="10">
-        <f>K510/L510</f>
+        <f t="shared" si="54"/>
         <v>0.156</v>
       </c>
       <c r="O510" s="4">
@@ -31525,11 +31520,11 @@
         <v>180</v>
       </c>
       <c r="M511" s="10">
-        <f xml:space="preserve"> (L511 - K511)/(K511-J511)</f>
+        <f t="shared" si="53"/>
         <v>-0.59899749373433586</v>
       </c>
       <c r="N511" s="10">
-        <f>K511/L511</f>
+        <f t="shared" si="54"/>
         <v>1.3319444444444444</v>
       </c>
       <c r="O511" s="4">
@@ -31579,11 +31574,11 @@
         <v>330</v>
       </c>
       <c r="M512" s="10">
-        <f xml:space="preserve"> (L512 - K512)/(K512-J512)</f>
+        <f t="shared" si="53"/>
         <v>-1.644122383252818</v>
       </c>
       <c r="N512" s="10">
-        <f>K512/L512</f>
+        <f t="shared" si="54"/>
         <v>0.1336969696969697</v>
       </c>
       <c r="O512" s="4">
@@ -31633,11 +31628,11 @@
         <v>2</v>
       </c>
       <c r="M513" s="10">
-        <f xml:space="preserve"> (L513 - K513)/(K513-J513)</f>
+        <f t="shared" si="53"/>
         <v>0.26315789473684209</v>
       </c>
       <c r="N513" s="10">
-        <f>K513/L513</f>
+        <f t="shared" si="54"/>
         <v>0.875</v>
       </c>
       <c r="O513" s="4">
@@ -31685,7 +31680,7 @@
         <v>35</v>
       </c>
       <c r="M514" s="10">
-        <f xml:space="preserve"> (L514 - K514)/(K514-J514)</f>
+        <f t="shared" si="53"/>
         <v>-1.6523157208088715</v>
       </c>
       <c r="O514" s="4">
